--- a/reports/updated_estimate.xlsx
+++ b/reports/updated_estimate.xlsx
@@ -4388,15 +4388,15 @@
       </c>
       <c r="D8" s="214" t="n">
         <f aca="false">2*ROUND('Server size'!C22,1)</f>
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="E8" s="214" t="n">
         <f aca="false">ROUNDUP('Data size'!D30/50,0)*50</f>
-        <v>2050</v>
+        <v>50</v>
       </c>
       <c r="F8" s="214" t="n">
         <f aca="false">ROUNDUP('DMS size'!D21/100,0)*100</f>
-        <v>5900</v>
+        <v>100</v>
       </c>
       <c r="H8" s="215" t="n">
         <v>2</v>
@@ -4422,15 +4422,15 @@
       </c>
       <c r="D9" s="214" t="n">
         <f aca="false">2*ROUND('Server size'!D22,1)</f>
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="E9" s="214" t="n">
         <f aca="false">ROUNDUP('Data size'!H30/50,0)*50</f>
-        <v>2250</v>
+        <v>50</v>
       </c>
       <c r="F9" s="214" t="n">
         <f aca="false">ROUNDUP('DMS size'!H21/100,0)*100</f>
-        <v>6500</v>
+        <v>100</v>
       </c>
       <c r="H9" s="215" t="n">
         <v>4</v>
@@ -4456,15 +4456,15 @@
       </c>
       <c r="D10" s="214" t="n">
         <f aca="false">2*'Server size'!E22</f>
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="E10" s="214" t="n">
         <f aca="false">ROUNDUP('Data size'!L30/50,0)*50</f>
-        <v>2500</v>
+        <v>50</v>
       </c>
       <c r="F10" s="214" t="n">
         <f aca="false">ROUNDUP('DMS size'!L21/100,0)*100</f>
-        <v>7200</v>
+        <v>100</v>
       </c>
       <c r="H10" s="215" t="n">
         <v>6</v>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="N10" s="217" t="n">
         <f aca="false">VLOOKUP(E4,B8:F12,3,FALSE())</f>
-        <v>132</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4490,15 +4490,15 @@
       </c>
       <c r="D11" s="214" t="n">
         <f aca="false">2*ROUND('Server size'!F22,1)</f>
-        <v>124</v>
+        <v>56</v>
       </c>
       <c r="E11" s="214" t="n">
         <f aca="false">ROUNDUP('Data size'!P30/50,0)*50</f>
-        <v>2750</v>
+        <v>50</v>
       </c>
       <c r="F11" s="214" t="n">
         <f aca="false">ROUNDUP('DMS size'!P21/100,0)*100</f>
-        <v>7900</v>
+        <v>100</v>
       </c>
       <c r="G11" s="219"/>
       <c r="H11" s="215" t="n">
@@ -4511,9 +4511,9 @@
       <c r="M11" s="218" t="s">
         <v>318</v>
       </c>
-      <c r="N11" s="217" t="e">
+      <c r="N11" s="217" t="n">
         <f aca="false">VLOOKUP(N10,H8:I39,2,FALSE())</f>
-        <v>#N/A</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4526,15 +4526,15 @@
       </c>
       <c r="D12" s="214" t="n">
         <f aca="false">2*ROUND('Server size'!G22,1)</f>
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="E12" s="214" t="n">
         <f aca="false">ROUNDUP('Data size'!T30/50,0)*50</f>
-        <v>3000</v>
+        <v>50</v>
       </c>
       <c r="F12" s="214" t="n">
         <f aca="false">ROUNDUP('DMS size'!T21/100,0)*100</f>
-        <v>8700</v>
+        <v>100</v>
       </c>
       <c r="G12" s="219"/>
       <c r="H12" s="215" t="n">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="N12" s="217" t="n">
         <f aca="false">VLOOKUP(E4,B8:F12,4,FALSE())</f>
-        <v>3000</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="N13" s="217" t="n">
         <f aca="false">VLOOKUP(E4,B8:F12,5,FALSE())</f>
-        <v>8700</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="N17" s="226" t="n">
         <f aca="false">N12/100</f>
-        <v>30</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5619,24 +5619,24 @@
       <c r="E13" s="251" t="s">
         <v>375</v>
       </c>
-      <c r="F13" s="260" t="e">
+      <c r="F13" s="260" t="n">
         <f aca="false">'Cloud sizing inputs'!N11</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G13" s="260" t="e">
+        <v>64</v>
+      </c>
+      <c r="G13" s="260" t="n">
         <f aca="false">F13*8</f>
-        <v>#N/A</v>
+        <v>512</v>
       </c>
       <c r="H13" s="260" t="n">
         <v>300</v>
       </c>
-      <c r="I13" s="260" t="e">
+      <c r="I13" s="260" t="n">
         <f aca="false">F13*C13</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J13" s="252" t="e">
+        <v>128</v>
+      </c>
+      <c r="J13" s="252" t="n">
         <f aca="false">G13*C13</f>
-        <v>#N/A</v>
+        <v>1024</v>
       </c>
       <c r="K13" s="255" t="n">
         <f aca="false">H13*C13/1024</f>
@@ -5672,20 +5672,20 @@
       </c>
       <c r="D15" s="263" t="n">
         <f aca="false">ROUNDUP('Cloud sizing inputs'!N17/5,0)*5</f>
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E15" s="264"/>
       <c r="F15" s="260"/>
       <c r="G15" s="260"/>
       <c r="H15" s="260" t="n">
         <f aca="false">'Cloud sizing inputs'!N12</f>
-        <v>3000</v>
+        <v>50</v>
       </c>
       <c r="I15" s="260"/>
       <c r="J15" s="252"/>
       <c r="K15" s="255" t="n">
         <f aca="false">H15/1024</f>
-        <v>2.9296875</v>
+        <v>0.048828125</v>
       </c>
     </row>
     <row r="16" s="256" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5732,25 +5732,25 @@
         <f aca="false">E13</f>
         <v>Reserved</v>
       </c>
-      <c r="F18" s="252" t="e">
+      <c r="F18" s="252" t="n">
         <f aca="false">F13</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G18" s="252" t="e">
+        <v>64</v>
+      </c>
+      <c r="G18" s="252" t="n">
         <f aca="false">G13</f>
-        <v>#N/A</v>
+        <v>512</v>
       </c>
       <c r="H18" s="252" t="n">
         <f aca="false">H13</f>
         <v>300</v>
       </c>
-      <c r="I18" s="252" t="e">
+      <c r="I18" s="252" t="n">
         <f aca="false">F18*C18</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J18" s="252" t="e">
+        <v>64</v>
+      </c>
+      <c r="J18" s="252" t="n">
         <f aca="false">G18*C18</f>
-        <v>#N/A</v>
+        <v>512</v>
       </c>
       <c r="K18" s="255" t="n">
         <f aca="false">H18*C18/1024</f>
@@ -5789,20 +5789,20 @@
       </c>
       <c r="D20" s="263" t="n">
         <f aca="false">D15</f>
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E20" s="266"/>
       <c r="F20" s="260"/>
       <c r="G20" s="252"/>
       <c r="H20" s="252" t="n">
         <f aca="false">H15</f>
-        <v>3000</v>
+        <v>50</v>
       </c>
       <c r="I20" s="260"/>
       <c r="J20" s="252"/>
       <c r="K20" s="255" t="n">
         <f aca="false">H20/1024</f>
-        <v>2.9296875</v>
+        <v>0.048828125</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5849,13 +5849,13 @@
       <c r="G23" s="245"/>
       <c r="H23" s="260" t="n">
         <f aca="false">'Cloud sizing inputs'!N13</f>
-        <v>8700</v>
+        <v>100</v>
       </c>
       <c r="I23" s="245"/>
       <c r="J23" s="245"/>
       <c r="K23" s="255" t="n">
         <f aca="false">H23/1024</f>
-        <v>8.49609375</v>
+        <v>0.09765625</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5899,15 +5899,15 @@
         <v>375</v>
       </c>
       <c r="F26" s="245"/>
-      <c r="G26" s="252" t="e">
+      <c r="G26" s="252" t="n">
         <f aca="false">IF(F13&lt;33,16,32)</f>
-        <v>#N/A</v>
+        <v>32</v>
       </c>
       <c r="H26" s="252"/>
       <c r="I26" s="245"/>
-      <c r="J26" s="245" t="e">
+      <c r="J26" s="245" t="n">
         <f aca="false">G26*C26</f>
-        <v>#N/A</v>
+        <v>96</v>
       </c>
       <c r="K26" s="245"/>
       <c r="L26" s="273"/>
@@ -6084,7 +6084,7 @@
       <c r="J35" s="245"/>
       <c r="K35" s="253" t="n">
         <f aca="false">K15*5/2</f>
-        <v>7.32421875</v>
+        <v>0.1220703125</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6403,23 +6403,23 @@
       </c>
       <c r="C4" s="287" t="n">
         <f aca="false">'Customer Volumes'!D4</f>
-        <v>4650</v>
+        <v>1500</v>
       </c>
       <c r="D4" s="287" t="n">
         <f aca="false">'Customer Volumes'!E4</f>
-        <v>4882.5</v>
+        <v>1650</v>
       </c>
       <c r="E4" s="287" t="n">
         <f aca="false">'Customer Volumes'!F4</f>
-        <v>5126.625</v>
+        <v>1815</v>
       </c>
       <c r="F4" s="287" t="n">
         <f aca="false">'Customer Volumes'!G4</f>
-        <v>5382.95625</v>
+        <v>1996.5</v>
       </c>
       <c r="G4" s="287" t="n">
         <f aca="false">'Customer Volumes'!H4</f>
-        <v>5652.1040625</v>
+        <v>2196.15</v>
       </c>
       <c r="H4" s="215"/>
     </row>
@@ -6442,23 +6442,23 @@
       </c>
       <c r="C6" s="291" t="n">
         <f aca="false">'Services Calculation'!D28</f>
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="D6" s="291" t="n">
         <f aca="false">'Services Calculation'!E28</f>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E6" s="291" t="n">
         <f aca="false">'Services Calculation'!F28</f>
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="F6" s="291" t="n">
         <f aca="false">'Services Calculation'!G28</f>
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="G6" s="291" t="n">
         <f aca="false">'Services Calculation'!H28</f>
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="H6" s="215"/>
     </row>
@@ -6469,23 +6469,23 @@
       </c>
       <c r="C7" s="291" t="n">
         <f aca="false">'Services Calculation'!D29</f>
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="D7" s="291" t="n">
         <f aca="false">'Services Calculation'!E29</f>
-        <v>179</v>
+        <v>93</v>
       </c>
       <c r="E7" s="291" t="n">
         <f aca="false">'Services Calculation'!F29</f>
-        <v>187</v>
+        <v>98</v>
       </c>
       <c r="F7" s="291" t="n">
         <f aca="false">'Services Calculation'!G29</f>
-        <v>194.629386685225</v>
+        <v>102.59057040625</v>
       </c>
       <c r="G7" s="291" t="n">
         <f aca="false">'Services Calculation'!H29</f>
-        <v>204</v>
+        <v>109</v>
       </c>
       <c r="H7" s="215"/>
     </row>
@@ -6496,23 +6496,23 @@
       </c>
       <c r="C8" s="292" t="n">
         <f aca="false">C6/16</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D8" s="292" t="n">
         <f aca="false">D6/16</f>
-        <v>6.25</v>
+        <v>3.125</v>
       </c>
       <c r="E8" s="292" t="n">
         <f aca="false">E6/16</f>
-        <v>6.5</v>
+        <v>3.3125</v>
       </c>
       <c r="F8" s="292" t="n">
         <f aca="false">F6/16</f>
-        <v>6.75</v>
+        <v>3.5</v>
       </c>
       <c r="G8" s="292" t="n">
         <f aca="false">G6/16</f>
-        <v>7.0625</v>
+        <v>3.6875</v>
       </c>
       <c r="H8" s="215"/>
     </row>
@@ -6523,23 +6523,23 @@
       </c>
       <c r="C9" s="292" t="n">
         <f aca="false">C7/32</f>
-        <v>5.375</v>
+        <v>2.75</v>
       </c>
       <c r="D9" s="292" t="n">
         <f aca="false">D7/32</f>
-        <v>5.59375</v>
+        <v>2.90625</v>
       </c>
       <c r="E9" s="292" t="n">
         <f aca="false">E7/32</f>
-        <v>5.84375</v>
+        <v>3.0625</v>
       </c>
       <c r="F9" s="292" t="n">
         <f aca="false">F7/32</f>
-        <v>6.08216833391328</v>
+        <v>3.20595532519531</v>
       </c>
       <c r="G9" s="292" t="n">
         <f aca="false">G7/32</f>
-        <v>6.375</v>
+        <v>3.40625</v>
       </c>
       <c r="H9" s="215"/>
     </row>
@@ -6588,23 +6588,23 @@
       </c>
       <c r="C12" s="291" t="n">
         <f aca="false">ROUNDUP(C4/C11, 0)</f>
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D12" s="291" t="n">
         <f aca="false">ROUNDUP(D4/D11, 0)</f>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E12" s="291" t="n">
         <f aca="false">ROUNDUP(E4/E11, 0)</f>
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F12" s="291" t="n">
         <f aca="false">ROUNDUP(F4/F11, 0)</f>
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G12" s="291" t="n">
         <f aca="false">ROUNDUP(G4/G11, 0)</f>
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H12" s="215"/>
     </row>
@@ -6671,23 +6671,23 @@
       </c>
       <c r="C15" s="291" t="n">
         <f aca="false">ROUND(C12+C13+C14,0)</f>
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D15" s="291" t="n">
         <f aca="false">ROUND(D12+D13+D14,0)</f>
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E15" s="291" t="n">
         <f aca="false">ROUND(E12+E13+E14,0)</f>
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F15" s="291" t="n">
         <f aca="false">ROUND(F12+F13+F14,0)</f>
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G15" s="291" t="n">
         <f aca="false">ROUND(G12+G13+G14,0)</f>
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H15" s="215"/>
     </row>
@@ -6717,23 +6717,23 @@
       </c>
       <c r="C18" s="303" t="n">
         <f aca="false">ROUND(ROUND(MAX(C8,C9),0)*1.42,0)</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D18" s="303" t="n">
         <f aca="false">ROUND(ROUND(MAX(D8,D9),0)*1.42,0)</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E18" s="303" t="n">
         <f aca="false">ROUND(ROUND(MAX(E8,E9),0)*1.42,0)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F18" s="303" t="n">
         <f aca="false">ROUND(ROUND(MAX(F8,F9),0)*1.42,0)</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G18" s="303" t="n">
         <f aca="false">ROUND(ROUND(MAX(G8,G9),0)*1.42,0)</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H18" s="304" t="s">
         <v>428</v>
@@ -6765,23 +6765,23 @@
       </c>
       <c r="C21" s="313" t="n">
         <f aca="false">C15</f>
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D21" s="313" t="n">
         <f aca="false">D15</f>
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E21" s="313" t="n">
         <f aca="false">E15</f>
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F21" s="313" t="n">
         <f aca="false">F15</f>
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G21" s="313" t="n">
         <f aca="false">G15</f>
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H21" s="215"/>
     </row>
@@ -6791,23 +6791,23 @@
       </c>
       <c r="C22" s="313" t="n">
         <f aca="false">C21*2</f>
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D22" s="313" t="n">
         <f aca="false">D21*2</f>
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="E22" s="313" t="n">
         <f aca="false">E21*2</f>
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="F22" s="313" t="n">
         <f aca="false">F21*2</f>
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="G22" s="313" t="n">
         <f aca="false">G21*2</f>
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H22" s="215" t="s">
         <v>430</v>
@@ -6819,23 +6819,23 @@
       </c>
       <c r="C23" s="313" t="n">
         <f aca="false">C22*8</f>
-        <v>448</v>
+        <v>192</v>
       </c>
       <c r="D23" s="313" t="n">
         <f aca="false">D22*8</f>
-        <v>464</v>
+        <v>208</v>
       </c>
       <c r="E23" s="313" t="n">
         <f aca="false">E22*8</f>
-        <v>480</v>
+        <v>224</v>
       </c>
       <c r="F23" s="313" t="n">
         <f aca="false">F22*8</f>
-        <v>496</v>
+        <v>224</v>
       </c>
       <c r="G23" s="313" t="n">
         <f aca="false">G22*8</f>
-        <v>528</v>
+        <v>240</v>
       </c>
       <c r="H23" s="215" t="s">
         <v>432</v>
@@ -6847,23 +6847,23 @@
       </c>
       <c r="C24" s="313" t="n">
         <f aca="false">C22*8</f>
-        <v>448</v>
+        <v>192</v>
       </c>
       <c r="D24" s="313" t="n">
         <f aca="false">D22*8</f>
-        <v>464</v>
+        <v>208</v>
       </c>
       <c r="E24" s="313" t="n">
         <f aca="false">E22*8</f>
-        <v>480</v>
+        <v>224</v>
       </c>
       <c r="F24" s="313" t="n">
         <f aca="false">F22*8</f>
-        <v>496</v>
+        <v>224</v>
       </c>
       <c r="G24" s="313" t="n">
         <f aca="false">G22*8</f>
-        <v>528</v>
+        <v>240</v>
       </c>
       <c r="H24" s="215" t="s">
         <v>432</v>
@@ -6875,23 +6875,23 @@
       </c>
       <c r="C25" s="313" t="n">
         <f aca="false">C22*4</f>
-        <v>224</v>
+        <v>96</v>
       </c>
       <c r="D25" s="313" t="n">
         <f aca="false">D22*4</f>
-        <v>232</v>
+        <v>104</v>
       </c>
       <c r="E25" s="313" t="n">
         <f aca="false">E22*4</f>
-        <v>240</v>
+        <v>112</v>
       </c>
       <c r="F25" s="313" t="n">
         <f aca="false">F22*4</f>
-        <v>248</v>
+        <v>112</v>
       </c>
       <c r="G25" s="313" t="n">
         <f aca="false">G22*4</f>
-        <v>264</v>
+        <v>120</v>
       </c>
       <c r="H25" s="215" t="s">
         <v>435</v>
@@ -6926,23 +6926,23 @@
       </c>
       <c r="C28" s="313" t="n">
         <f aca="false">IF(C27="No", 0, C21)</f>
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D28" s="313" t="n">
         <f aca="false">IF(C27="No", 0, D21)</f>
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E28" s="313" t="n">
         <f aca="false">IF(C27="No", 0, E21)</f>
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F28" s="313" t="n">
         <f aca="false">IF(C27="No", 0, F21)</f>
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G28" s="313" t="n">
         <f aca="false">IF(C27="No", 0, G21)</f>
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H28" s="267" t="s">
         <v>437</v>
@@ -6954,23 +6954,23 @@
       </c>
       <c r="C29" s="313" t="n">
         <f aca="false">IF(C27="No", 0, C22)</f>
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D29" s="313" t="n">
         <f aca="false">IF(C27="No", 0, D22)</f>
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="E29" s="313" t="n">
         <f aca="false">IF(C27="No", 0, E22)</f>
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="F29" s="313" t="n">
         <f aca="false">IF(C27="No", 0, F22)</f>
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="G29" s="313" t="n">
         <f aca="false">IF(C27="No", 0, G22)</f>
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H29" s="267"/>
     </row>
@@ -6980,23 +6980,23 @@
       </c>
       <c r="C30" s="313" t="n">
         <f aca="false">C29*8</f>
-        <v>448</v>
+        <v>192</v>
       </c>
       <c r="D30" s="313" t="n">
         <f aca="false">D29*8</f>
-        <v>464</v>
+        <v>208</v>
       </c>
       <c r="E30" s="313" t="n">
         <f aca="false">E29*8</f>
-        <v>480</v>
+        <v>224</v>
       </c>
       <c r="F30" s="313" t="n">
         <f aca="false">F29*8</f>
-        <v>496</v>
+        <v>224</v>
       </c>
       <c r="G30" s="313" t="n">
         <f aca="false">G29*8</f>
-        <v>528</v>
+        <v>240</v>
       </c>
       <c r="H30" s="267"/>
     </row>
@@ -7006,23 +7006,23 @@
       </c>
       <c r="C31" s="313" t="n">
         <f aca="false">C29*8</f>
-        <v>448</v>
+        <v>192</v>
       </c>
       <c r="D31" s="313" t="n">
         <f aca="false">D29*8</f>
-        <v>464</v>
+        <v>208</v>
       </c>
       <c r="E31" s="313" t="n">
         <f aca="false">E29*8</f>
-        <v>480</v>
+        <v>224</v>
       </c>
       <c r="F31" s="313" t="n">
         <f aca="false">F29*8</f>
-        <v>496</v>
+        <v>224</v>
       </c>
       <c r="G31" s="313" t="n">
         <f aca="false">G29*8</f>
-        <v>528</v>
+        <v>240</v>
       </c>
       <c r="H31" s="267"/>
     </row>
@@ -7032,23 +7032,23 @@
       </c>
       <c r="C32" s="313" t="n">
         <f aca="false">C29*4</f>
-        <v>224</v>
+        <v>96</v>
       </c>
       <c r="D32" s="313" t="n">
         <f aca="false">D29*4</f>
-        <v>232</v>
+        <v>104</v>
       </c>
       <c r="E32" s="313" t="n">
         <f aca="false">E29*4</f>
-        <v>240</v>
+        <v>112</v>
       </c>
       <c r="F32" s="313" t="n">
         <f aca="false">F29*4</f>
-        <v>248</v>
+        <v>112</v>
       </c>
       <c r="G32" s="313" t="n">
         <f aca="false">G29*4</f>
-        <v>264</v>
+        <v>120</v>
       </c>
       <c r="H32" s="267"/>
     </row>
@@ -7072,23 +7072,23 @@
       </c>
       <c r="C35" s="313" t="n">
         <f aca="false">CEILING('Data size'!D30,100)</f>
-        <v>2100</v>
+        <v>100</v>
       </c>
       <c r="D35" s="313" t="n">
         <f aca="false">CEILING('Data size'!H30,100)</f>
-        <v>2300</v>
+        <v>100</v>
       </c>
       <c r="E35" s="313" t="n">
         <f aca="false">CEILING('Data size'!L30,100)</f>
-        <v>2500</v>
+        <v>100</v>
       </c>
       <c r="F35" s="313" t="n">
         <f aca="false">CEILING('Data size'!P30,100)</f>
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="G35" s="313" t="n">
         <f aca="false">CEILING('Data size'!T30,100)</f>
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="H35" s="215" t="s">
         <v>442</v>
@@ -7100,23 +7100,23 @@
       </c>
       <c r="C36" s="313" t="n">
         <f aca="false">CEILING('DMS size'!D21,100)</f>
-        <v>5900</v>
+        <v>100</v>
       </c>
       <c r="D36" s="313" t="n">
         <f aca="false">CEILING('DMS size'!H21,100)</f>
-        <v>6500</v>
+        <v>100</v>
       </c>
       <c r="E36" s="313" t="n">
         <f aca="false">CEILING('DMS size'!L21,100)</f>
-        <v>7200</v>
+        <v>100</v>
       </c>
       <c r="F36" s="313" t="n">
         <f aca="false">CEILING('DMS size'!P21,100)</f>
-        <v>7900</v>
+        <v>100</v>
       </c>
       <c r="G36" s="313" t="n">
         <f aca="false">CEILING('DMS size'!T21,100)</f>
-        <v>8700</v>
+        <v>100</v>
       </c>
       <c r="H36" s="215" t="s">
         <v>442</v>
@@ -7180,23 +7180,23 @@
       </c>
       <c r="C3" s="317" t="n">
         <f aca="false">'Customer Volumes'!D3</f>
-        <v>15500</v>
+        <v>5000</v>
       </c>
       <c r="D3" s="317" t="n">
         <f aca="false">'Customer Volumes'!E3</f>
-        <v>16275</v>
+        <v>5500</v>
       </c>
       <c r="E3" s="317" t="n">
         <f aca="false">'Customer Volumes'!F3</f>
-        <v>17088.75</v>
+        <v>6050</v>
       </c>
       <c r="F3" s="317" t="n">
         <f aca="false">'Customer Volumes'!G3</f>
-        <v>17943.1875</v>
+        <v>6655</v>
       </c>
       <c r="G3" s="317" t="n">
         <f aca="false">'Customer Volumes'!H3</f>
-        <v>18840.346875</v>
+        <v>7320.5</v>
       </c>
     </row>
     <row r="4" s="80" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7205,23 +7205,23 @@
       </c>
       <c r="C4" s="317" t="n">
         <f aca="false">'Customer Volumes'!D4</f>
-        <v>4650</v>
+        <v>1500</v>
       </c>
       <c r="D4" s="317" t="n">
         <f aca="false">'Customer Volumes'!E4</f>
-        <v>4882.5</v>
+        <v>1650</v>
       </c>
       <c r="E4" s="317" t="n">
         <f aca="false">'Customer Volumes'!F4</f>
-        <v>5126.625</v>
+        <v>1815</v>
       </c>
       <c r="F4" s="317" t="n">
         <f aca="false">'Customer Volumes'!G4</f>
-        <v>5382.95625</v>
+        <v>1996.5</v>
       </c>
       <c r="G4" s="317" t="n">
         <f aca="false">'Customer Volumes'!H4</f>
-        <v>5652.1040625</v>
+        <v>2196.15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7393,23 +7393,23 @@
       </c>
       <c r="C14" s="322" t="n">
         <f aca="false">C3*(1-C13)*C12</f>
-        <v>77500.0000000001</v>
+        <v>25000</v>
       </c>
       <c r="D14" s="322" t="n">
         <f aca="false">D3*(1-D13)*D12</f>
-        <v>81375.0000000001</v>
+        <v>27500</v>
       </c>
       <c r="E14" s="322" t="n">
         <f aca="false">E3*(1-E13)*E12</f>
-        <v>85443.7500000001</v>
+        <v>30250</v>
       </c>
       <c r="F14" s="322" t="n">
         <f aca="false">F3*(1-F13)*F12</f>
-        <v>89715.9375000001</v>
+        <v>33275</v>
       </c>
       <c r="G14" s="322" t="n">
         <f aca="false">G3*(1-G13)*G12</f>
-        <v>94201.7343750001</v>
+        <v>36602.5</v>
       </c>
       <c r="H14" s="320" t="s">
         <v>215</v>
@@ -7421,23 +7421,23 @@
       </c>
       <c r="C15" s="319" t="n">
         <f aca="false">C4*C8+C14</f>
-        <v>310000</v>
+        <v>100000</v>
       </c>
       <c r="D15" s="319" t="n">
         <f aca="false">D4*D8+D14</f>
-        <v>325500</v>
+        <v>110000</v>
       </c>
       <c r="E15" s="319" t="n">
         <f aca="false">E4*E8+E14</f>
-        <v>341775</v>
+        <v>121000</v>
       </c>
       <c r="F15" s="319" t="n">
         <f aca="false">F4*F8+F14</f>
-        <v>358863.75</v>
+        <v>133100</v>
       </c>
       <c r="G15" s="319" t="n">
         <f aca="false">G4*G8+G14</f>
-        <v>376806.9375</v>
+        <v>146410</v>
       </c>
       <c r="H15" s="320" t="s">
         <v>215</v>
@@ -7449,23 +7449,23 @@
       </c>
       <c r="C16" s="323" t="n">
         <f aca="false">C15*8/C11</f>
-        <v>225454.545454546</v>
+        <v>72727.2727272728</v>
       </c>
       <c r="D16" s="323" t="n">
         <f aca="false">D15*8/D11</f>
-        <v>236727.272727273</v>
+        <v>80000</v>
       </c>
       <c r="E16" s="323" t="n">
         <f aca="false">E15*8/E11</f>
-        <v>248563.636363636</v>
+        <v>88000</v>
       </c>
       <c r="F16" s="323" t="n">
         <f aca="false">F15*8/F11</f>
-        <v>260991.818181818</v>
+        <v>96800</v>
       </c>
       <c r="G16" s="323" t="n">
         <f aca="false">G15*8/G11</f>
-        <v>274041.409090909</v>
+        <v>106480</v>
       </c>
       <c r="H16" s="320" t="s">
         <v>455</v>
@@ -7629,23 +7629,23 @@
       </c>
       <c r="C24" s="322" t="n">
         <f aca="false">C22*(1-C23)*C3</f>
-        <v>15500</v>
+        <v>5000.00000000001</v>
       </c>
       <c r="D24" s="322" t="n">
         <f aca="false">D22*(1-D23)*D3</f>
-        <v>16275</v>
+        <v>5500.00000000001</v>
       </c>
       <c r="E24" s="322" t="n">
         <f aca="false">E22*(1-E23)*E3</f>
-        <v>17088.75</v>
+        <v>6050.00000000001</v>
       </c>
       <c r="F24" s="322" t="n">
         <f aca="false">F22*(1-F23)*F3</f>
-        <v>17943.1875</v>
+        <v>6655.00000000001</v>
       </c>
       <c r="G24" s="322" t="n">
         <f aca="false">G22*(1-G23)*G3</f>
-        <v>18840.346875</v>
+        <v>7320.50000000001</v>
       </c>
       <c r="H24" s="320" t="s">
         <v>215</v>
@@ -7657,23 +7657,23 @@
       </c>
       <c r="C25" s="319" t="n">
         <f aca="false">C4*C18+C24</f>
-        <v>9315500</v>
+        <v>3005000</v>
       </c>
       <c r="D25" s="319" t="n">
         <f aca="false">D4*D18+D24</f>
-        <v>9781275</v>
+        <v>3305500</v>
       </c>
       <c r="E25" s="319" t="n">
         <f aca="false">E4*E18+E24</f>
-        <v>10270338.75</v>
+        <v>3636050</v>
       </c>
       <c r="F25" s="319" t="n">
         <f aca="false">F4*F18+F24</f>
-        <v>10783855.6875</v>
+        <v>3999655</v>
       </c>
       <c r="G25" s="319" t="n">
         <f aca="false">G4*G18+G24</f>
-        <v>11323048.471875</v>
+        <v>4399620.5</v>
       </c>
       <c r="H25" s="320" t="s">
         <v>215</v>
@@ -7685,23 +7685,23 @@
       </c>
       <c r="C26" s="323" t="n">
         <f aca="false">C25*8/C21</f>
-        <v>3922315.78947368</v>
+        <v>1265263.15789474</v>
       </c>
       <c r="D26" s="323" t="n">
         <f aca="false">D25*8/D21</f>
-        <v>4118431.57894737</v>
+        <v>1391789.47368421</v>
       </c>
       <c r="E26" s="323" t="n">
         <f aca="false">E25*8/E21</f>
-        <v>4324353.15789474</v>
+        <v>1530968.42105263</v>
       </c>
       <c r="F26" s="323" t="n">
         <f aca="false">F25*8/F21</f>
-        <v>4540570.81578947</v>
+        <v>1684065.2631579</v>
       </c>
       <c r="G26" s="323" t="n">
         <f aca="false">G25*8/G21</f>
-        <v>4767599.35657895</v>
+        <v>1852471.78947368</v>
       </c>
       <c r="H26" s="320" t="s">
         <v>455</v>
@@ -7724,23 +7724,23 @@
       </c>
       <c r="C28" s="325" t="n">
         <f aca="false">C16+C26</f>
-        <v>4147770.33492823</v>
+        <v>1337990.43062201</v>
       </c>
       <c r="D28" s="325" t="n">
         <f aca="false">D16+D26</f>
-        <v>4355158.85167464</v>
+        <v>1471789.47368421</v>
       </c>
       <c r="E28" s="325" t="n">
         <f aca="false">E16+E26</f>
-        <v>4572916.79425837</v>
+        <v>1618968.42105263</v>
       </c>
       <c r="F28" s="325" t="n">
         <f aca="false">F16+F26</f>
-        <v>4801562.63397129</v>
+        <v>1780865.2631579</v>
       </c>
       <c r="G28" s="325" t="n">
         <f aca="false">G16+G26</f>
-        <v>5041640.76566986</v>
+        <v>1958951.78947368</v>
       </c>
       <c r="H28" s="320" t="s">
         <v>455</v>
@@ -7750,23 +7750,23 @@
       <c r="B29" s="324"/>
       <c r="C29" s="325" t="n">
         <f aca="false">C28/1024</f>
-        <v>4050.55696770335</v>
+        <v>1306.63127990431</v>
       </c>
       <c r="D29" s="325" t="n">
         <f aca="false">D28/1024</f>
-        <v>4253.08481608852</v>
+        <v>1437.29440789474</v>
       </c>
       <c r="E29" s="325" t="n">
         <f aca="false">E28/1024</f>
-        <v>4465.73905689294</v>
+        <v>1581.02384868421</v>
       </c>
       <c r="F29" s="325" t="n">
         <f aca="false">F28/1024</f>
-        <v>4689.02600973759</v>
+        <v>1739.12623355263</v>
       </c>
       <c r="G29" s="325" t="n">
         <f aca="false">G28/1024</f>
-        <v>4923.47731022447</v>
+        <v>1913.0388569079</v>
       </c>
       <c r="H29" s="320" t="s">
         <v>457</v>
@@ -7776,23 +7776,23 @@
       <c r="B30" s="324"/>
       <c r="C30" s="325" t="n">
         <f aca="false">C29/1024</f>
-        <v>3.9556220387728</v>
+        <v>1.27600710928155</v>
       </c>
       <c r="D30" s="325" t="n">
         <f aca="false">D29/1024</f>
-        <v>4.15340314071144</v>
+        <v>1.4036078202097</v>
       </c>
       <c r="E30" s="325" t="n">
         <f aca="false">E29/1024</f>
-        <v>4.36107329774702</v>
+        <v>1.54396860223067</v>
       </c>
       <c r="F30" s="325" t="n">
         <f aca="false">F29/1024</f>
-        <v>4.57912696263437</v>
+        <v>1.69836546245374</v>
       </c>
       <c r="G30" s="325" t="n">
         <f aca="false">G29/1024</f>
-        <v>4.80808331076608</v>
+        <v>1.86820200869912</v>
       </c>
       <c r="H30" s="320" t="s">
         <v>458</v>
@@ -10390,26 +10390,26 @@
         <v>78</v>
       </c>
       <c r="D3" s="48" t="n">
-        <v>15500</v>
+        <v>5000</v>
       </c>
       <c r="E3" s="49" t="n">
         <f aca="false">D3*(1+I3)</f>
-        <v>16275</v>
+        <v>5500</v>
       </c>
       <c r="F3" s="49" t="n">
         <f aca="false">E3*(1+$I$3)</f>
-        <v>17088.75</v>
+        <v>6050</v>
       </c>
       <c r="G3" s="49" t="n">
         <f aca="false">F3*(1+$I$3)</f>
-        <v>17943.1875</v>
+        <v>6655</v>
       </c>
       <c r="H3" s="49" t="n">
         <f aca="false">G3*(1+$I$3)</f>
-        <v>18840.346875</v>
+        <v>7320.5</v>
       </c>
       <c r="I3" s="50" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J3" s="51" t="s">
         <v>79</v>
@@ -10424,26 +10424,26 @@
         <v>80</v>
       </c>
       <c r="D4" s="48" t="n">
-        <v>4650</v>
+        <v>1500</v>
       </c>
       <c r="E4" s="53" t="n">
         <f aca="false">E3*0.3</f>
-        <v>4882.5</v>
+        <v>1650</v>
       </c>
       <c r="F4" s="53" t="n">
         <f aca="false">F3*0.3</f>
-        <v>5126.625</v>
+        <v>1815</v>
       </c>
       <c r="G4" s="53" t="n">
         <f aca="false">G3*0.3</f>
-        <v>5382.95625</v>
+        <v>1996.5</v>
       </c>
       <c r="H4" s="53" t="n">
         <f aca="false">H3*0.3</f>
-        <v>5652.1040625</v>
+        <v>2196.15</v>
       </c>
       <c r="I4" s="50" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J4" s="51" t="s">
         <v>79</v>
@@ -10458,26 +10458,26 @@
         <v>81</v>
       </c>
       <c r="D5" s="55" t="n">
-        <v>25786541</v>
+        <v>22500</v>
       </c>
       <c r="E5" s="56" t="n">
         <f aca="false">D5*(1+I5)</f>
-        <v>28365195.1</v>
+        <v>25875</v>
       </c>
       <c r="F5" s="56" t="n">
         <f aca="false">E5*(1+I5)</f>
-        <v>31201714.61</v>
+        <v>29756.25</v>
       </c>
       <c r="G5" s="56" t="n">
         <f aca="false">F5*(1+I5)</f>
-        <v>34321886.071</v>
+        <v>34219.6875</v>
       </c>
       <c r="H5" s="56" t="n">
         <f aca="false">G5*(1+I5)</f>
-        <v>37754074.6781</v>
+        <v>39352.640625</v>
       </c>
       <c r="I5" s="50" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="J5" s="51" t="s">
         <v>79</v>
@@ -10522,26 +10522,26 @@
         <v>84</v>
       </c>
       <c r="D7" s="48" t="n">
-        <v>10700000</v>
+        <v>240000</v>
       </c>
       <c r="E7" s="53" t="n">
         <f aca="false">D7*(1+I7)</f>
-        <v>11770000</v>
+        <v>252000</v>
       </c>
       <c r="F7" s="53" t="n">
         <f aca="false">E7*(1+I7)</f>
-        <v>12947000</v>
+        <v>264600</v>
       </c>
       <c r="G7" s="53" t="n">
         <f aca="false">F7*(1+I7)</f>
-        <v>14241700</v>
+        <v>277830</v>
       </c>
       <c r="H7" s="53" t="n">
         <f aca="false">G7*(1+I7)</f>
-        <v>15665870</v>
+        <v>291721.5</v>
       </c>
       <c r="I7" s="50" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J7" s="51" t="s">
         <v>79</v>
@@ -10586,26 +10586,26 @@
         <v>87</v>
       </c>
       <c r="D9" s="58" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="E9" s="59" t="n">
         <f aca="false">D9*(1+I9)</f>
-        <v>21000</v>
+        <v>18000</v>
       </c>
       <c r="F9" s="59" t="n">
         <f aca="false">E9*(1+I9)</f>
-        <v>22050</v>
+        <v>21600</v>
       </c>
       <c r="G9" s="59" t="n">
         <f aca="false">F9*(1+I9)</f>
-        <v>23152.5</v>
+        <v>25920</v>
       </c>
       <c r="H9" s="59" t="n">
         <f aca="false">G9*(1+I9)</f>
-        <v>24310.125</v>
+        <v>31104</v>
       </c>
       <c r="I9" s="50" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="J9" s="51" t="s">
         <v>79</v>
@@ -10710,26 +10710,26 @@
         <v>94</v>
       </c>
       <c r="D13" s="60" t="n">
-        <v>4050</v>
+        <v>750</v>
       </c>
       <c r="E13" s="61" t="n">
         <f aca="false">D13*(1+I13)</f>
-        <v>4252.5</v>
+        <v>825</v>
       </c>
       <c r="F13" s="61" t="n">
         <f aca="false">E13*(1+I13)</f>
-        <v>4465.125</v>
+        <v>907.5</v>
       </c>
       <c r="G13" s="61" t="n">
         <f aca="false">F13*(1+I13)</f>
-        <v>4688.38125</v>
+        <v>998.25</v>
       </c>
       <c r="H13" s="61" t="n">
         <f aca="false">G13*(1+I13)</f>
-        <v>4922.8003125</v>
+        <v>1098.075</v>
       </c>
       <c r="I13" s="50" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J13" s="51" t="s">
         <v>79</v>
@@ -10960,23 +10960,23 @@
       </c>
       <c r="D21" s="60" t="n">
         <f aca="false">0.05*(D7+D9)</f>
-        <v>536000</v>
+        <v>12750</v>
       </c>
       <c r="E21" s="61" t="n">
         <f aca="false">0.05*(E7+E9)</f>
-        <v>589550</v>
+        <v>13500</v>
       </c>
       <c r="F21" s="61" t="n">
         <f aca="false">0.05*(F7+F9)</f>
-        <v>648452.5</v>
+        <v>14310</v>
       </c>
       <c r="G21" s="61" t="n">
         <f aca="false">0.05*(G7+G9)</f>
-        <v>713242.625</v>
+        <v>15187.5</v>
       </c>
       <c r="H21" s="61" t="n">
         <f aca="false">0.05*(H7+H9)</f>
-        <v>784509.00625</v>
+        <v>16141.275</v>
       </c>
       <c r="I21" s="61"/>
       <c r="J21" s="63" t="s">
@@ -10995,23 +10995,23 @@
       </c>
       <c r="D22" s="60" t="n">
         <f aca="false">0.1*(D5+D7+D9)</f>
-        <v>3650654.1</v>
+        <v>27750</v>
       </c>
       <c r="E22" s="61" t="n">
         <f aca="false">0.1*(E5+E7+E9)</f>
-        <v>4015619.51</v>
+        <v>29587.5</v>
       </c>
       <c r="F22" s="61" t="n">
         <f aca="false">0.1*(F5+F7+F9)</f>
-        <v>4417076.461</v>
+        <v>31595.625</v>
       </c>
       <c r="G22" s="61" t="n">
         <f aca="false">0.1*(G5+G7+G9)</f>
-        <v>4858673.8571</v>
+        <v>33796.96875</v>
       </c>
       <c r="H22" s="61" t="n">
         <f aca="false">0.1*(H5+H7+H9)</f>
-        <v>5344425.48031</v>
+        <v>36217.8140625</v>
       </c>
       <c r="I22" s="61"/>
       <c r="J22" s="63" t="s">
@@ -11030,23 +11030,23 @@
       </c>
       <c r="D23" s="60" t="n">
         <f aca="false">0.1*(D5+D7+D9)</f>
-        <v>3650654.1</v>
+        <v>27750</v>
       </c>
       <c r="E23" s="61" t="n">
         <f aca="false">0.1*(E5+E7+E9)</f>
-        <v>4015619.51</v>
+        <v>29587.5</v>
       </c>
       <c r="F23" s="61" t="n">
         <f aca="false">0.1*(F5+F7+F9)</f>
-        <v>4417076.461</v>
+        <v>31595.625</v>
       </c>
       <c r="G23" s="61" t="n">
         <f aca="false">0.1*(G5+G7+G9)</f>
-        <v>4858673.8571</v>
+        <v>33796.96875</v>
       </c>
       <c r="H23" s="61" t="n">
         <f aca="false">0.1*(H5+H7+H9)</f>
-        <v>5344425.48031</v>
+        <v>36217.8140625</v>
       </c>
       <c r="I23" s="61"/>
       <c r="J23" s="63" t="s">
@@ -11065,23 +11065,23 @@
       </c>
       <c r="D24" s="60" t="n">
         <f aca="false">D7+D9</f>
-        <v>10720000</v>
+        <v>255000</v>
       </c>
       <c r="E24" s="61" t="n">
         <f aca="false">E7+E9</f>
-        <v>11791000</v>
+        <v>270000</v>
       </c>
       <c r="F24" s="61" t="n">
         <f aca="false">F7+F9</f>
-        <v>12969050</v>
+        <v>286200</v>
       </c>
       <c r="G24" s="61" t="n">
         <f aca="false">G7+G9</f>
-        <v>14264852.5</v>
+        <v>303750</v>
       </c>
       <c r="H24" s="61" t="n">
         <f aca="false">H7+H9</f>
-        <v>15690180.125</v>
+        <v>322825.5</v>
       </c>
       <c r="I24" s="61"/>
       <c r="J24" s="63" t="s">
@@ -11150,23 +11150,23 @@
       </c>
       <c r="D27" s="60" t="n">
         <f aca="false">0.01*(D5+D7+D9)</f>
-        <v>365065.41</v>
+        <v>2775</v>
       </c>
       <c r="E27" s="61" t="n">
         <f aca="false">0.01*(E5+E7+E9)</f>
-        <v>401561.951</v>
+        <v>2958.75</v>
       </c>
       <c r="F27" s="61" t="n">
         <f aca="false">0.01*(F5+F7+F9)</f>
-        <v>441707.6461</v>
+        <v>3159.5625</v>
       </c>
       <c r="G27" s="61" t="n">
         <f aca="false">0.01*(G5+G7+G9)</f>
-        <v>485867.38571</v>
+        <v>3379.696875</v>
       </c>
       <c r="H27" s="61" t="n">
         <f aca="false">0.01*(H5+H7+H9)</f>
-        <v>534442.548031</v>
+        <v>3621.78140625</v>
       </c>
       <c r="I27" s="61"/>
       <c r="J27" s="63" t="s">
@@ -11690,27 +11690,27 @@
       </c>
       <c r="D3" s="51" t="n">
         <f aca="false">'Customer Volumes'!D3</f>
-        <v>15500</v>
+        <v>5000</v>
       </c>
       <c r="E3" s="51" t="n">
         <f aca="false">'Customer Volumes'!E3</f>
-        <v>16275</v>
+        <v>5500</v>
       </c>
       <c r="F3" s="51" t="n">
         <f aca="false">'Customer Volumes'!F3</f>
-        <v>17088.75</v>
+        <v>6050</v>
       </c>
       <c r="G3" s="51" t="n">
         <f aca="false">'Customer Volumes'!G3</f>
-        <v>17943.1875</v>
+        <v>6655</v>
       </c>
       <c r="H3" s="51" t="n">
         <f aca="false">'Customer Volumes'!H3</f>
-        <v>18840.346875</v>
+        <v>7320.5</v>
       </c>
       <c r="I3" s="82" t="n">
         <f aca="false">'Customer Volumes'!I3</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J3" s="51" t="s">
         <v>79</v>
@@ -11726,27 +11726,27 @@
       </c>
       <c r="D4" s="51" t="n">
         <f aca="false">'Customer Volumes'!D4</f>
-        <v>4650</v>
+        <v>1500</v>
       </c>
       <c r="E4" s="51" t="n">
         <f aca="false">'Customer Volumes'!E4</f>
-        <v>4882.5</v>
+        <v>1650</v>
       </c>
       <c r="F4" s="51" t="n">
         <f aca="false">'Customer Volumes'!F4</f>
-        <v>5126.625</v>
+        <v>1815</v>
       </c>
       <c r="G4" s="51" t="n">
         <f aca="false">'Customer Volumes'!G4</f>
-        <v>5382.95625</v>
+        <v>1996.5</v>
       </c>
       <c r="H4" s="51" t="n">
         <f aca="false">'Customer Volumes'!H4</f>
-        <v>5652.1040625</v>
+        <v>2196.15</v>
       </c>
       <c r="I4" s="82" t="n">
         <f aca="false">'Customer Volumes'!I4</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J4" s="51" t="s">
         <v>79</v>
@@ -11762,27 +11762,27 @@
       </c>
       <c r="D5" s="51" t="n">
         <f aca="false">'Customer Volumes'!D5/200/8</f>
-        <v>16116.588125</v>
+        <v>14.0625</v>
       </c>
       <c r="E5" s="51" t="n">
         <f aca="false">'Customer Volumes'!E5/200/8</f>
-        <v>17728.2469375</v>
+        <v>16.171875</v>
       </c>
       <c r="F5" s="51" t="n">
         <f aca="false">'Customer Volumes'!F5/200/8</f>
-        <v>19501.07163125</v>
+        <v>18.59765625</v>
       </c>
       <c r="G5" s="51" t="n">
         <f aca="false">'Customer Volumes'!G5/200/8</f>
-        <v>21451.178794375</v>
+        <v>21.3873046875</v>
       </c>
       <c r="H5" s="51" t="n">
         <f aca="false">'Customer Volumes'!H5/200/8</f>
-        <v>23596.2966738125</v>
+        <v>24.595400390625</v>
       </c>
       <c r="I5" s="82" t="n">
         <f aca="false">'Customer Volumes'!I5</f>
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="J5" s="51" t="s">
         <v>79</v>
@@ -11828,23 +11828,23 @@
       </c>
       <c r="D7" s="51" t="n">
         <f aca="false">'Customer Volumes'!D7/200/8</f>
-        <v>6687.5</v>
+        <v>150</v>
       </c>
       <c r="E7" s="51" t="n">
         <f aca="false">'Customer Volumes'!E7/200/8</f>
-        <v>7356.25</v>
+        <v>157.5</v>
       </c>
       <c r="F7" s="51" t="n">
         <f aca="false">'Customer Volumes'!F7/200/8</f>
-        <v>8091.875</v>
+        <v>165.375</v>
       </c>
       <c r="G7" s="51" t="n">
         <f aca="false">'Customer Volumes'!G7/200/8</f>
-        <v>8901.0625</v>
+        <v>173.64375</v>
       </c>
       <c r="H7" s="51" t="n">
         <f aca="false">'Customer Volumes'!H7/200/8</f>
-        <v>9791.16875</v>
+        <v>182.3259375</v>
       </c>
       <c r="I7" s="85"/>
       <c r="J7" s="51" t="s">
@@ -11891,23 +11891,23 @@
       </c>
       <c r="D9" s="51" t="n">
         <f aca="false">'Customer Volumes'!D9/200/8</f>
-        <v>12.5</v>
+        <v>9.375</v>
       </c>
       <c r="E9" s="51" t="n">
         <f aca="false">'Customer Volumes'!E9/200/8</f>
-        <v>13.125</v>
+        <v>11.25</v>
       </c>
       <c r="F9" s="51" t="n">
         <f aca="false">'Customer Volumes'!F9/200/8</f>
-        <v>13.78125</v>
+        <v>13.5</v>
       </c>
       <c r="G9" s="51" t="n">
         <f aca="false">'Customer Volumes'!G9/200/8</f>
-        <v>14.4703125</v>
+        <v>16.2</v>
       </c>
       <c r="H9" s="51" t="n">
         <f aca="false">'Customer Volumes'!H9/200/8</f>
-        <v>15.193828125</v>
+        <v>19.44</v>
       </c>
       <c r="I9" s="85" t="n">
         <v>0.15</v>
@@ -12140,23 +12140,23 @@
       </c>
       <c r="D17" s="63" t="n">
         <f aca="false">(D5+D7+D9)*2</f>
-        <v>45633.17625</v>
+        <v>346.875</v>
       </c>
       <c r="E17" s="63" t="n">
         <f aca="false">(E5+E7+E9)*2</f>
-        <v>50195.243875</v>
+        <v>369.84375</v>
       </c>
       <c r="F17" s="63" t="n">
         <f aca="false">(F5+F7+F9)*2</f>
-        <v>55213.4557625</v>
+        <v>394.9453125</v>
       </c>
       <c r="G17" s="63" t="n">
         <f aca="false">(G5+G7+G9)*2</f>
-        <v>60733.42321375</v>
+        <v>422.462109375</v>
       </c>
       <c r="H17" s="63" t="n">
         <f aca="false">(H5+H7+H9)*2</f>
-        <v>66805.318503875</v>
+        <v>452.72267578125</v>
       </c>
       <c r="I17" s="63"/>
       <c r="J17" s="63" t="s">
@@ -12205,23 +12205,23 @@
       </c>
       <c r="D19" s="63" t="n">
         <f aca="false">D4</f>
-        <v>4650</v>
+        <v>1500</v>
       </c>
       <c r="E19" s="63" t="n">
         <f aca="false">E4</f>
-        <v>4882.5</v>
+        <v>1650</v>
       </c>
       <c r="F19" s="63" t="n">
         <f aca="false">F4</f>
-        <v>5126.625</v>
+        <v>1815</v>
       </c>
       <c r="G19" s="63" t="n">
         <f aca="false">G4</f>
-        <v>5382.95625</v>
+        <v>1996.5</v>
       </c>
       <c r="H19" s="63" t="n">
         <f aca="false">H4</f>
-        <v>5652.1040625</v>
+        <v>2196.15</v>
       </c>
       <c r="I19" s="63"/>
       <c r="J19" s="63" t="s">
@@ -12270,23 +12270,23 @@
       </c>
       <c r="D21" s="63" t="n">
         <f aca="false">D5/10</f>
-        <v>1611.6588125</v>
+        <v>1.40625</v>
       </c>
       <c r="E21" s="63" t="n">
         <f aca="false">E5/10</f>
-        <v>1772.82469375</v>
+        <v>1.6171875</v>
       </c>
       <c r="F21" s="63" t="n">
         <f aca="false">F5/10</f>
-        <v>1950.107163125</v>
+        <v>1.859765625</v>
       </c>
       <c r="G21" s="63" t="n">
         <f aca="false">G5/10</f>
-        <v>2145.1178794375</v>
+        <v>2.13873046875</v>
       </c>
       <c r="H21" s="63" t="n">
         <f aca="false">H5/10</f>
-        <v>2359.62966738125</v>
+        <v>2.4595400390625</v>
       </c>
       <c r="I21" s="63"/>
       <c r="J21" s="63" t="s">
@@ -12305,23 +12305,23 @@
       </c>
       <c r="D22" s="63" t="n">
         <f aca="false">0.1*(D7+D9+D5)</f>
-        <v>2281.6588125</v>
+        <v>17.34375</v>
       </c>
       <c r="E22" s="63" t="n">
         <f aca="false">0.1*(E7+E9+E5)</f>
-        <v>2509.76219375</v>
+        <v>18.4921875</v>
       </c>
       <c r="F22" s="63" t="n">
         <f aca="false">0.1*(F7+F9+F5)</f>
-        <v>2760.672788125</v>
+        <v>19.747265625</v>
       </c>
       <c r="G22" s="63" t="n">
         <f aca="false">0.1*(G7+G9+G5)</f>
-        <v>3036.6711606875</v>
+        <v>21.12310546875</v>
       </c>
       <c r="H22" s="63" t="n">
         <f aca="false">0.1*(H7+H9+H5)</f>
-        <v>3340.26592519375</v>
+        <v>22.6361337890625</v>
       </c>
       <c r="I22" s="63"/>
       <c r="J22" s="63" t="s">
@@ -12340,23 +12340,23 @@
       </c>
       <c r="D23" s="63" t="n">
         <f aca="false">0.1*(D7+D9+D5)</f>
-        <v>2281.6588125</v>
+        <v>17.34375</v>
       </c>
       <c r="E23" s="63" t="n">
         <f aca="false">0.1*(E7+E9+E5)</f>
-        <v>2509.76219375</v>
+        <v>18.4921875</v>
       </c>
       <c r="F23" s="63" t="n">
         <f aca="false">0.1*(F7+F9+F5)</f>
-        <v>2760.672788125</v>
+        <v>19.747265625</v>
       </c>
       <c r="G23" s="63" t="n">
         <f aca="false">0.1*(G7+G9+G5)</f>
-        <v>3036.6711606875</v>
+        <v>21.12310546875</v>
       </c>
       <c r="H23" s="63" t="n">
         <f aca="false">0.1*(H7+H9+H5)</f>
-        <v>3340.26592519375</v>
+        <v>22.6361337890625</v>
       </c>
       <c r="I23" s="63"/>
       <c r="J23" s="63" t="s">
@@ -12375,23 +12375,23 @@
       </c>
       <c r="D24" s="63" t="n">
         <f aca="false">D7+D9</f>
-        <v>6700</v>
+        <v>159.375</v>
       </c>
       <c r="E24" s="63" t="n">
         <f aca="false">E7+E9</f>
-        <v>7369.375</v>
+        <v>168.75</v>
       </c>
       <c r="F24" s="63" t="n">
         <f aca="false">F7+F9</f>
-        <v>8105.65625</v>
+        <v>178.875</v>
       </c>
       <c r="G24" s="63" t="n">
         <f aca="false">G7+G9</f>
-        <v>8915.5328125</v>
+        <v>189.84375</v>
       </c>
       <c r="H24" s="63" t="n">
         <f aca="false">H7+H9</f>
-        <v>9806.36257812501</v>
+        <v>201.7659375</v>
       </c>
       <c r="I24" s="63"/>
       <c r="J24" s="63" t="s">
@@ -12440,23 +12440,23 @@
       </c>
       <c r="D26" s="63" t="n">
         <f aca="false">D21+D22+D24</f>
-        <v>10593.317625</v>
+        <v>178.125</v>
       </c>
       <c r="E26" s="63" t="n">
         <f aca="false">E21+E22+E24</f>
-        <v>11651.9618875</v>
+        <v>188.859375</v>
       </c>
       <c r="F26" s="63" t="n">
         <f aca="false">F21+F22+F24</f>
-        <v>12816.43620125</v>
+        <v>200.48203125</v>
       </c>
       <c r="G26" s="63" t="n">
         <f aca="false">G21+G22+G24</f>
-        <v>14097.321852625</v>
+        <v>213.1055859375</v>
       </c>
       <c r="H26" s="63" t="n">
         <f aca="false">H21+H22+H24</f>
-        <v>15506.2581707</v>
+        <v>226.861611328125</v>
       </c>
       <c r="I26" s="63"/>
       <c r="J26" s="63" t="s">
@@ -12475,23 +12475,23 @@
       </c>
       <c r="D27" s="63" t="n">
         <f aca="false">0.1*(D7+D9+D5)</f>
-        <v>2281.6588125</v>
+        <v>17.34375</v>
       </c>
       <c r="E27" s="63" t="n">
         <f aca="false">0.1*(E7+E9+E5)</f>
-        <v>2509.76219375</v>
+        <v>18.4921875</v>
       </c>
       <c r="F27" s="63" t="n">
         <f aca="false">0.1*(F7+F9+F5)</f>
-        <v>2760.672788125</v>
+        <v>19.747265625</v>
       </c>
       <c r="G27" s="63" t="n">
         <f aca="false">0.1*(G7+G9+G5)</f>
-        <v>3036.6711606875</v>
+        <v>21.12310546875</v>
       </c>
       <c r="H27" s="63" t="n">
         <f aca="false">0.1*(H7+H9+H5)</f>
-        <v>3340.26592519375</v>
+        <v>22.6361337890625</v>
       </c>
       <c r="I27" s="63"/>
       <c r="J27" s="63" t="s">
@@ -12731,63 +12731,63 @@
       </c>
       <c r="H4" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D4</f>
-        <v>4650</v>
+        <v>1500</v>
       </c>
       <c r="I4" s="93" t="n">
         <f aca="false">H4/D4*E4</f>
-        <v>55.8</v>
+        <v>18</v>
       </c>
       <c r="J4" s="93" t="n">
         <f aca="false">H4/D4*F4</f>
-        <v>102.3</v>
+        <v>33</v>
       </c>
       <c r="K4" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!E4</f>
-        <v>4882.5</v>
+        <v>1650</v>
       </c>
       <c r="L4" s="93" t="n">
         <f aca="false">K4/D4*E4</f>
-        <v>58.59</v>
+        <v>19.8</v>
       </c>
       <c r="M4" s="93" t="n">
         <f aca="false">K4/D4*F4</f>
-        <v>107.415</v>
+        <v>36.3</v>
       </c>
       <c r="N4" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!F4</f>
-        <v>5126.625</v>
+        <v>1815</v>
       </c>
       <c r="O4" s="93" t="n">
         <f aca="false">N4/D4*E4</f>
-        <v>61.5195</v>
+        <v>21.78</v>
       </c>
       <c r="P4" s="93" t="n">
         <f aca="false">N4/D4*F4</f>
-        <v>112.78575</v>
+        <v>39.93</v>
       </c>
       <c r="Q4" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!G4</f>
-        <v>5382.95625</v>
+        <v>1996.5</v>
       </c>
       <c r="R4" s="93" t="n">
         <f aca="false">Q4/D4*E4</f>
-        <v>64.595475</v>
+        <v>23.958</v>
       </c>
       <c r="S4" s="93" t="n">
         <f aca="false">Q4/D4*F4</f>
-        <v>118.4250375</v>
+        <v>43.923</v>
       </c>
       <c r="T4" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!H4</f>
-        <v>5652.1040625</v>
+        <v>2196.15</v>
       </c>
       <c r="U4" s="93" t="n">
         <f aca="false">T4/D4*E4</f>
-        <v>67.82524875</v>
+        <v>26.3538</v>
       </c>
       <c r="V4" s="93" t="n">
         <f aca="false">T4/D4*F4</f>
-        <v>124.346289375</v>
+        <v>48.3153</v>
       </c>
       <c r="W4" s="94"/>
     </row>
@@ -13116,63 +13116,63 @@
       </c>
       <c r="H9" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$19</f>
-        <v>4650</v>
+        <v>1500</v>
       </c>
       <c r="I9" s="93" t="n">
         <f aca="false">H9/D9*E9</f>
-        <v>7.75</v>
+        <v>2.5</v>
       </c>
       <c r="J9" s="93" t="n">
         <f aca="false">H9/D9*F9</f>
-        <v>7.75</v>
+        <v>2.5</v>
       </c>
       <c r="K9" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$19</f>
-        <v>4882.5</v>
+        <v>1650</v>
       </c>
       <c r="L9" s="93" t="n">
         <f aca="false">K9/D9*E9</f>
-        <v>8.1375</v>
+        <v>2.75</v>
       </c>
       <c r="M9" s="93" t="n">
         <f aca="false">K9/D9*F9</f>
-        <v>8.1375</v>
+        <v>2.75</v>
       </c>
       <c r="N9" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$19</f>
-        <v>5126.625</v>
+        <v>1815</v>
       </c>
       <c r="O9" s="93" t="n">
         <f aca="false">N9/D9*E9</f>
-        <v>8.544375</v>
+        <v>3.025</v>
       </c>
       <c r="P9" s="93" t="n">
         <f aca="false">N9/D9*F9</f>
-        <v>8.544375</v>
+        <v>3.025</v>
       </c>
       <c r="Q9" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$19</f>
-        <v>5382.95625</v>
+        <v>1996.5</v>
       </c>
       <c r="R9" s="93" t="n">
         <f aca="false">Q9/D9*E9</f>
-        <v>8.97159375</v>
+        <v>3.3275</v>
       </c>
       <c r="S9" s="93" t="n">
         <f aca="false">Q9/D9*F9</f>
-        <v>8.97159375</v>
+        <v>3.3275</v>
       </c>
       <c r="T9" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$19</f>
-        <v>5652.1040625</v>
+        <v>2196.15</v>
       </c>
       <c r="U9" s="93" t="n">
         <f aca="false">T9/D9*E9</f>
-        <v>9.4201734375</v>
+        <v>3.66025</v>
       </c>
       <c r="V9" s="93" t="n">
         <f aca="false">T9/D9*F9</f>
-        <v>9.4201734375</v>
+        <v>3.66025</v>
       </c>
       <c r="W9" s="94"/>
     </row>
@@ -13267,63 +13267,63 @@
       </c>
       <c r="H11" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$27</f>
-        <v>2281.6588125</v>
+        <v>17.34375</v>
       </c>
       <c r="I11" s="93" t="n">
         <f aca="false">H11/D11*E11</f>
-        <v>0.22816588125</v>
+        <v>0.001734375</v>
       </c>
       <c r="J11" s="93" t="n">
         <f aca="false">H11/D11*F11</f>
-        <v>0.22816588125</v>
+        <v>0.001734375</v>
       </c>
       <c r="K11" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$27</f>
-        <v>2509.76219375</v>
+        <v>18.4921875</v>
       </c>
       <c r="L11" s="93" t="n">
         <f aca="false">K11/D11*E11</f>
-        <v>0.250976219375</v>
+        <v>0.00184921875</v>
       </c>
       <c r="M11" s="93" t="n">
         <f aca="false">K11/D11*F11</f>
-        <v>0.250976219375</v>
+        <v>0.00184921875</v>
       </c>
       <c r="N11" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$27</f>
-        <v>2760.672788125</v>
+        <v>19.747265625</v>
       </c>
       <c r="O11" s="93" t="n">
         <f aca="false">N11/D11*E11</f>
-        <v>0.2760672788125</v>
+        <v>0.0019747265625</v>
       </c>
       <c r="P11" s="93" t="n">
         <f aca="false">N11/D11*F11</f>
-        <v>0.2760672788125</v>
+        <v>0.0019747265625</v>
       </c>
       <c r="Q11" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$27</f>
-        <v>3036.6711606875</v>
+        <v>21.12310546875</v>
       </c>
       <c r="R11" s="93" t="n">
         <f aca="false">Q11/D11*E11</f>
-        <v>0.30366711606875</v>
+        <v>0.002112310546875</v>
       </c>
       <c r="S11" s="93" t="n">
         <f aca="false">Q11/D11*F11</f>
-        <v>0.30366711606875</v>
+        <v>0.002112310546875</v>
       </c>
       <c r="T11" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$27</f>
-        <v>3340.26592519375</v>
+        <v>22.6361337890625</v>
       </c>
       <c r="U11" s="93" t="n">
         <f aca="false">T11/D11*E11</f>
-        <v>0.334026592519375</v>
+        <v>0.00226361337890625</v>
       </c>
       <c r="V11" s="93" t="n">
         <f aca="false">T11/D11*F11</f>
-        <v>0.334026592519375</v>
+        <v>0.00226361337890625</v>
       </c>
       <c r="W11" s="94"/>
     </row>
@@ -13408,63 +13408,63 @@
       </c>
       <c r="H13" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$22</f>
-        <v>2281.6588125</v>
+        <v>17.34375</v>
       </c>
       <c r="I13" s="93" t="n">
         <f aca="false">H13/D13*E13</f>
-        <v>0.22816588125</v>
+        <v>0.001734375</v>
       </c>
       <c r="J13" s="93" t="n">
         <f aca="false">H13/D13*F13</f>
-        <v>0.22816588125</v>
+        <v>0.001734375</v>
       </c>
       <c r="K13" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$22</f>
-        <v>2509.76219375</v>
+        <v>18.4921875</v>
       </c>
       <c r="L13" s="93" t="n">
         <f aca="false">K13/D13*E13</f>
-        <v>0.250976219375</v>
+        <v>0.00184921875</v>
       </c>
       <c r="M13" s="93" t="n">
         <f aca="false">K13/D13*F13</f>
-        <v>0.250976219375</v>
+        <v>0.00184921875</v>
       </c>
       <c r="N13" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$22</f>
-        <v>2760.672788125</v>
+        <v>19.747265625</v>
       </c>
       <c r="O13" s="93" t="n">
         <f aca="false">N13/D13*E13</f>
-        <v>0.2760672788125</v>
+        <v>0.0019747265625</v>
       </c>
       <c r="P13" s="93" t="n">
         <f aca="false">N13/D13*F13</f>
-        <v>0.2760672788125</v>
+        <v>0.0019747265625</v>
       </c>
       <c r="Q13" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$22</f>
-        <v>3036.6711606875</v>
+        <v>21.12310546875</v>
       </c>
       <c r="R13" s="93" t="n">
         <f aca="false">Q13/D13*E13</f>
-        <v>0.30366711606875</v>
+        <v>0.002112310546875</v>
       </c>
       <c r="S13" s="93" t="n">
         <f aca="false">Q13/D13*F13</f>
-        <v>0.30366711606875</v>
+        <v>0.002112310546875</v>
       </c>
       <c r="T13" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$22</f>
-        <v>3340.26592519375</v>
+        <v>22.6361337890625</v>
       </c>
       <c r="U13" s="93" t="n">
         <f aca="false">T13/D13*E13</f>
-        <v>0.334026592519375</v>
+        <v>0.00226361337890625</v>
       </c>
       <c r="V13" s="93" t="n">
         <f aca="false">T13/D13*F13</f>
-        <v>0.334026592519375</v>
+        <v>0.00226361337890625</v>
       </c>
       <c r="W13" s="94"/>
     </row>
@@ -13486,63 +13486,63 @@
       </c>
       <c r="H14" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$24</f>
-        <v>6700</v>
+        <v>159.375</v>
       </c>
       <c r="I14" s="93" t="n">
         <f aca="false">H14/D14*E14</f>
-        <v>1.34</v>
+        <v>0.031875</v>
       </c>
       <c r="J14" s="93" t="n">
         <f aca="false">H14/D14*F14</f>
-        <v>3.35</v>
+        <v>0.0796875</v>
       </c>
       <c r="K14" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$24</f>
-        <v>7369.375</v>
+        <v>168.75</v>
       </c>
       <c r="L14" s="93" t="n">
         <f aca="false">K14/D14*E14</f>
-        <v>1.473875</v>
+        <v>0.03375</v>
       </c>
       <c r="M14" s="93" t="n">
         <f aca="false">K14/D14*F14</f>
-        <v>3.6846875</v>
+        <v>0.084375</v>
       </c>
       <c r="N14" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$24</f>
-        <v>8105.65625</v>
+        <v>178.875</v>
       </c>
       <c r="O14" s="93" t="n">
         <f aca="false">N14/D14*E14</f>
-        <v>1.62113125</v>
+        <v>0.035775</v>
       </c>
       <c r="P14" s="93" t="n">
         <f aca="false">N14/D14*F14</f>
-        <v>4.052828125</v>
+        <v>0.0894375</v>
       </c>
       <c r="Q14" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$24</f>
-        <v>8915.5328125</v>
+        <v>189.84375</v>
       </c>
       <c r="R14" s="93" t="n">
         <f aca="false">Q14/D14*E14</f>
-        <v>1.7831065625</v>
+        <v>0.03796875</v>
       </c>
       <c r="S14" s="93" t="n">
         <f aca="false">Q14/D14*F14</f>
-        <v>4.45776640625</v>
+        <v>0.094921875</v>
       </c>
       <c r="T14" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$24</f>
-        <v>9806.36257812501</v>
+        <v>201.7659375</v>
       </c>
       <c r="U14" s="93" t="n">
         <f aca="false">T14/D14*E14</f>
-        <v>1.961272515625</v>
+        <v>0.0403531875</v>
       </c>
       <c r="V14" s="93" t="n">
         <f aca="false">T14/D14*F14</f>
-        <v>4.9031812890625</v>
+        <v>0.10088296875</v>
       </c>
       <c r="W14" s="94"/>
     </row>
@@ -13564,63 +13564,63 @@
       </c>
       <c r="H15" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$22</f>
-        <v>2281.6588125</v>
+        <v>17.34375</v>
       </c>
       <c r="I15" s="93" t="n">
         <f aca="false">H15/D15*E15</f>
-        <v>0.22816588125</v>
+        <v>0.001734375</v>
       </c>
       <c r="J15" s="93" t="n">
         <f aca="false">H15/D15*F15</f>
-        <v>0.22816588125</v>
+        <v>0.001734375</v>
       </c>
       <c r="K15" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$22</f>
-        <v>2509.76219375</v>
+        <v>18.4921875</v>
       </c>
       <c r="L15" s="93" t="n">
         <f aca="false">K15/D15*E15</f>
-        <v>0.250976219375</v>
+        <v>0.00184921875</v>
       </c>
       <c r="M15" s="93" t="n">
         <f aca="false">K15/D15*F15</f>
-        <v>0.250976219375</v>
+        <v>0.00184921875</v>
       </c>
       <c r="N15" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$22</f>
-        <v>2760.672788125</v>
+        <v>19.747265625</v>
       </c>
       <c r="O15" s="93" t="n">
         <f aca="false">N15/D15*E15</f>
-        <v>0.2760672788125</v>
+        <v>0.0019747265625</v>
       </c>
       <c r="P15" s="93" t="n">
         <f aca="false">N15/D15*F15</f>
-        <v>0.2760672788125</v>
+        <v>0.0019747265625</v>
       </c>
       <c r="Q15" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$22</f>
-        <v>3036.6711606875</v>
+        <v>21.12310546875</v>
       </c>
       <c r="R15" s="93" t="n">
         <f aca="false">Q15/D15*E15</f>
-        <v>0.30366711606875</v>
+        <v>0.002112310546875</v>
       </c>
       <c r="S15" s="93" t="n">
         <f aca="false">Q15/D15*F15</f>
-        <v>0.30366711606875</v>
+        <v>0.002112310546875</v>
       </c>
       <c r="T15" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$22</f>
-        <v>3340.26592519375</v>
+        <v>22.6361337890625</v>
       </c>
       <c r="U15" s="93" t="n">
         <f aca="false">T15/D15*E15</f>
-        <v>0.334026592519375</v>
+        <v>0.00226361337890625</v>
       </c>
       <c r="V15" s="93" t="n">
         <f aca="false">T15/D15*F15</f>
-        <v>0.334026592519375</v>
+        <v>0.00226361337890625</v>
       </c>
       <c r="W15" s="94"/>
     </row>
@@ -13642,63 +13642,63 @@
       </c>
       <c r="H16" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$26</f>
-        <v>10593.317625</v>
+        <v>178.125</v>
       </c>
       <c r="I16" s="93" t="n">
         <f aca="false">H16/D16*E16</f>
-        <v>2.118663525</v>
+        <v>0.035625</v>
       </c>
       <c r="J16" s="93" t="n">
         <f aca="false">H16/D16*F16</f>
-        <v>4.23732705</v>
+        <v>0.07125</v>
       </c>
       <c r="K16" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$26</f>
-        <v>11651.9618875</v>
+        <v>188.859375</v>
       </c>
       <c r="L16" s="93" t="n">
         <f aca="false">K16/D16*E16</f>
-        <v>2.3303923775</v>
+        <v>0.037771875</v>
       </c>
       <c r="M16" s="93" t="n">
         <f aca="false">K16/D16*F16</f>
-        <v>4.660784755</v>
+        <v>0.07554375</v>
       </c>
       <c r="N16" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$26</f>
-        <v>12816.43620125</v>
+        <v>200.48203125</v>
       </c>
       <c r="O16" s="93" t="n">
         <f aca="false">N16/D16*E16</f>
-        <v>2.56328724025</v>
+        <v>0.04009640625</v>
       </c>
       <c r="P16" s="93" t="n">
         <f aca="false">N16/D16*F16</f>
-        <v>5.1265744805</v>
+        <v>0.0801928125</v>
       </c>
       <c r="Q16" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$26</f>
-        <v>14097.321852625</v>
+        <v>213.1055859375</v>
       </c>
       <c r="R16" s="93" t="n">
         <f aca="false">Q16/D16*E16</f>
-        <v>2.819464370525</v>
+        <v>0.0426211171875</v>
       </c>
       <c r="S16" s="93" t="n">
         <f aca="false">Q16/D16*F16</f>
-        <v>5.63892874105</v>
+        <v>0.085242234375</v>
       </c>
       <c r="T16" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$26</f>
-        <v>15506.2581707</v>
+        <v>226.861611328125</v>
       </c>
       <c r="U16" s="93" t="n">
         <f aca="false">T16/D16*E16</f>
-        <v>3.10125163414</v>
+        <v>0.045372322265625</v>
       </c>
       <c r="V16" s="93" t="n">
         <f aca="false">T16/D16*F16</f>
-        <v>6.20250326828</v>
+        <v>0.09074464453125</v>
       </c>
       <c r="W16" s="94"/>
     </row>
@@ -13720,63 +13720,63 @@
       </c>
       <c r="H17" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$21</f>
-        <v>1611.6588125</v>
+        <v>1.40625</v>
       </c>
       <c r="I17" s="93" t="n">
         <f aca="false">H17/D17*E17</f>
-        <v>0.3223317625</v>
+        <v>0.00028125</v>
       </c>
       <c r="J17" s="93" t="n">
         <f aca="false">H17/D17*F17</f>
-        <v>0.3223317625</v>
+        <v>0.00028125</v>
       </c>
       <c r="K17" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$21</f>
-        <v>1772.82469375</v>
+        <v>1.6171875</v>
       </c>
       <c r="L17" s="93" t="n">
         <f aca="false">K17/D17*E17</f>
-        <v>0.35456493875</v>
+        <v>0.0003234375</v>
       </c>
       <c r="M17" s="93" t="n">
         <f aca="false">K17/D17*F17</f>
-        <v>0.35456493875</v>
+        <v>0.0003234375</v>
       </c>
       <c r="N17" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$21</f>
-        <v>1950.107163125</v>
+        <v>1.859765625</v>
       </c>
       <c r="O17" s="93" t="n">
         <f aca="false">N17/D17*E17</f>
-        <v>0.390021432625</v>
+        <v>0.000371953125</v>
       </c>
       <c r="P17" s="93" t="n">
         <f aca="false">N17/D17*F17</f>
-        <v>0.390021432625</v>
+        <v>0.000371953125</v>
       </c>
       <c r="Q17" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$21</f>
-        <v>2145.1178794375</v>
+        <v>2.13873046875</v>
       </c>
       <c r="R17" s="93" t="n">
         <f aca="false">Q17/D17*E17</f>
-        <v>0.4290235758875</v>
+        <v>0.00042774609375</v>
       </c>
       <c r="S17" s="93" t="n">
         <f aca="false">Q17/D17*F17</f>
-        <v>0.4290235758875</v>
+        <v>0.00042774609375</v>
       </c>
       <c r="T17" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$21</f>
-        <v>2359.62966738125</v>
+        <v>2.4595400390625</v>
       </c>
       <c r="U17" s="93" t="n">
         <f aca="false">T17/D17*E17</f>
-        <v>0.47192593347625</v>
+        <v>0.0004919080078125</v>
       </c>
       <c r="V17" s="93" t="n">
         <f aca="false">T17/D17*F17</f>
-        <v>0.47192593347625</v>
+        <v>0.0004919080078125</v>
       </c>
       <c r="W17" s="94"/>
     </row>
@@ -13798,63 +13798,63 @@
       </c>
       <c r="H18" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$21</f>
-        <v>1611.6588125</v>
+        <v>1.40625</v>
       </c>
       <c r="I18" s="93" t="n">
         <f aca="false">H18/D18*E18</f>
-        <v>0.16116588125</v>
+        <v>0.000140625</v>
       </c>
       <c r="J18" s="93" t="n">
         <f aca="false">H18/D18*F18</f>
-        <v>0.16116588125</v>
+        <v>0.000140625</v>
       </c>
       <c r="K18" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$21</f>
-        <v>1772.82469375</v>
+        <v>1.6171875</v>
       </c>
       <c r="L18" s="93" t="n">
         <f aca="false">K18/D18*E18</f>
-        <v>0.177282469375</v>
+        <v>0.00016171875</v>
       </c>
       <c r="M18" s="93" t="n">
         <f aca="false">K18/D18*F18</f>
-        <v>0.177282469375</v>
+        <v>0.00016171875</v>
       </c>
       <c r="N18" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$21</f>
-        <v>1950.107163125</v>
+        <v>1.859765625</v>
       </c>
       <c r="O18" s="93" t="n">
         <f aca="false">N18/D18*E18</f>
-        <v>0.1950107163125</v>
+        <v>0.0001859765625</v>
       </c>
       <c r="P18" s="93" t="n">
         <f aca="false">N18/D18*F18</f>
-        <v>0.1950107163125</v>
+        <v>0.0001859765625</v>
       </c>
       <c r="Q18" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$21</f>
-        <v>2145.1178794375</v>
+        <v>2.13873046875</v>
       </c>
       <c r="R18" s="93" t="n">
         <f aca="false">Q18/D18*E18</f>
-        <v>0.21451178794375</v>
+        <v>0.000213873046875</v>
       </c>
       <c r="S18" s="93" t="n">
         <f aca="false">Q18/D18*F18</f>
-        <v>0.21451178794375</v>
+        <v>0.000213873046875</v>
       </c>
       <c r="T18" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$21</f>
-        <v>2359.62966738125</v>
+        <v>2.4595400390625</v>
       </c>
       <c r="U18" s="93" t="n">
         <f aca="false">T18/D18*E18</f>
-        <v>0.235962966738125</v>
+        <v>0.00024595400390625</v>
       </c>
       <c r="V18" s="93" t="n">
         <f aca="false">T18/D18*F18</f>
-        <v>0.235962966738125</v>
+        <v>0.00024595400390625</v>
       </c>
       <c r="W18" s="94"/>
     </row>
@@ -13876,63 +13876,63 @@
       </c>
       <c r="H19" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$21</f>
-        <v>1611.6588125</v>
+        <v>1.40625</v>
       </c>
       <c r="I19" s="93" t="n">
         <f aca="false">H19/D19*E19</f>
-        <v>0.16116588125</v>
+        <v>0.000140625</v>
       </c>
       <c r="J19" s="93" t="n">
         <f aca="false">H19/D19*F19</f>
-        <v>0.16116588125</v>
+        <v>0.000140625</v>
       </c>
       <c r="K19" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$21</f>
-        <v>1772.82469375</v>
+        <v>1.6171875</v>
       </c>
       <c r="L19" s="93" t="n">
         <f aca="false">K19/D19*E19</f>
-        <v>0.177282469375</v>
+        <v>0.00016171875</v>
       </c>
       <c r="M19" s="93" t="n">
         <f aca="false">K19/D19*F19</f>
-        <v>0.177282469375</v>
+        <v>0.00016171875</v>
       </c>
       <c r="N19" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$21</f>
-        <v>1950.107163125</v>
+        <v>1.859765625</v>
       </c>
       <c r="O19" s="93" t="n">
         <f aca="false">N19/D19*E19</f>
-        <v>0.1950107163125</v>
+        <v>0.0001859765625</v>
       </c>
       <c r="P19" s="93" t="n">
         <f aca="false">N19/D19*F19</f>
-        <v>0.1950107163125</v>
+        <v>0.0001859765625</v>
       </c>
       <c r="Q19" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$21</f>
-        <v>2145.1178794375</v>
+        <v>2.13873046875</v>
       </c>
       <c r="R19" s="93" t="n">
         <f aca="false">Q19/D19*E19</f>
-        <v>0.21451178794375</v>
+        <v>0.000213873046875</v>
       </c>
       <c r="S19" s="93" t="n">
         <f aca="false">Q19/D19*F19</f>
-        <v>0.21451178794375</v>
+        <v>0.000213873046875</v>
       </c>
       <c r="T19" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$21</f>
-        <v>2359.62966738125</v>
+        <v>2.4595400390625</v>
       </c>
       <c r="U19" s="93" t="n">
         <f aca="false">T19/D19*E19</f>
-        <v>0.235962966738125</v>
+        <v>0.00024595400390625</v>
       </c>
       <c r="V19" s="93" t="n">
         <f aca="false">T19/D19*F19</f>
-        <v>0.235962966738125</v>
+        <v>0.00024595400390625</v>
       </c>
       <c r="W19" s="94"/>
     </row>
@@ -13954,63 +13954,63 @@
       </c>
       <c r="H20" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$21</f>
-        <v>1611.6588125</v>
+        <v>1.40625</v>
       </c>
       <c r="I20" s="93" t="n">
         <f aca="false">H20/D20*E20</f>
-        <v>0.16116588125</v>
+        <v>0.000140625</v>
       </c>
       <c r="J20" s="93" t="n">
         <f aca="false">H20/D20*F20</f>
-        <v>0.16116588125</v>
+        <v>0.000140625</v>
       </c>
       <c r="K20" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$21</f>
-        <v>1772.82469375</v>
+        <v>1.6171875</v>
       </c>
       <c r="L20" s="93" t="n">
         <f aca="false">K20/D20*E20</f>
-        <v>0.177282469375</v>
+        <v>0.00016171875</v>
       </c>
       <c r="M20" s="93" t="n">
         <f aca="false">K20/D20*F20</f>
-        <v>0.177282469375</v>
+        <v>0.00016171875</v>
       </c>
       <c r="N20" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$21</f>
-        <v>1950.107163125</v>
+        <v>1.859765625</v>
       </c>
       <c r="O20" s="93" t="n">
         <f aca="false">N20/D20*E20</f>
-        <v>0.1950107163125</v>
+        <v>0.0001859765625</v>
       </c>
       <c r="P20" s="93" t="n">
         <f aca="false">N20/D20*F20</f>
-        <v>0.1950107163125</v>
+        <v>0.0001859765625</v>
       </c>
       <c r="Q20" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$21</f>
-        <v>2145.1178794375</v>
+        <v>2.13873046875</v>
       </c>
       <c r="R20" s="93" t="n">
         <f aca="false">Q20/D20*E20</f>
-        <v>0.21451178794375</v>
+        <v>0.000213873046875</v>
       </c>
       <c r="S20" s="93" t="n">
         <f aca="false">Q20/D20*F20</f>
-        <v>0.21451178794375</v>
+        <v>0.000213873046875</v>
       </c>
       <c r="T20" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$21</f>
-        <v>2359.62966738125</v>
+        <v>2.4595400390625</v>
       </c>
       <c r="U20" s="93" t="n">
         <f aca="false">T20/D20*E20</f>
-        <v>0.235962966738125</v>
+        <v>0.00024595400390625</v>
       </c>
       <c r="V20" s="93" t="n">
         <f aca="false">T20/D20*F20</f>
-        <v>0.235962966738125</v>
+        <v>0.00024595400390625</v>
       </c>
       <c r="W20" s="94"/>
     </row>
@@ -14235,47 +14235,47 @@
       </c>
       <c r="I24" s="97" t="n">
         <f aca="false">SUM(I4:I23)</f>
-        <v>95.498990575</v>
+        <v>47.57340625</v>
       </c>
       <c r="J24" s="97" t="n">
         <f aca="false">SUM(J4:J23)</f>
-        <v>171.1276541</v>
+        <v>87.65684375</v>
       </c>
       <c r="K24" s="96"/>
       <c r="L24" s="97" t="n">
         <f aca="false">SUM(L4:L23)</f>
-        <v>99.4211083825</v>
+        <v>49.877878125</v>
       </c>
       <c r="M24" s="97" t="n">
         <f aca="false">SUM(M4:M23)</f>
-        <v>178.53731326</v>
+        <v>92.216275</v>
       </c>
       <c r="N24" s="96"/>
       <c r="O24" s="97" t="n">
         <f aca="false">SUM(O4:O23)</f>
-        <v>103.56404890825</v>
+        <v>52.40022546875</v>
       </c>
       <c r="P24" s="97" t="n">
         <f aca="false">SUM(P4:P23)</f>
-        <v>186.3627830235</v>
+        <v>97.181484375</v>
       </c>
       <c r="Q24" s="96"/>
       <c r="R24" s="97" t="n">
         <f aca="false">SUM(R4:R23)</f>
-        <v>107.94132497095</v>
+        <v>55.1616211640625</v>
       </c>
       <c r="S24" s="97" t="n">
         <f aca="false">SUM(S4:S23)</f>
-        <v>194.629386685225</v>
+        <v>102.59057040625</v>
       </c>
       <c r="T24" s="96"/>
       <c r="U24" s="97" t="n">
         <f aca="false">SUM(U4:U23)</f>
-        <v>112.567372198514</v>
+        <v>58.1853273699219</v>
       </c>
       <c r="V24" s="97" t="n">
         <f aca="false">SUM(V4:V23)</f>
-        <v>203.364166981091</v>
+        <v>108.485323223438</v>
       </c>
       <c r="W24" s="94"/>
     </row>
@@ -14315,23 +14315,23 @@
       </c>
       <c r="D28" s="105" t="n">
         <f aca="false">ROUNDUP(I24,0)</f>
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="E28" s="105" t="n">
         <f aca="false">ROUNDUP(L24,0)</f>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F28" s="105" t="n">
         <f aca="false">ROUNDUP(O24,0)</f>
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="G28" s="105" t="n">
         <f aca="false">ROUNDUP(R24,0)</f>
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="H28" s="105" t="n">
         <f aca="false">ROUNDUP(U24,0)</f>
-        <v>113</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14340,23 +14340,23 @@
       </c>
       <c r="D29" s="105" t="n">
         <f aca="false">ROUNDUP(J24,0)</f>
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="E29" s="105" t="n">
         <f aca="false">ROUNDUP(M24,0)</f>
-        <v>179</v>
+        <v>93</v>
       </c>
       <c r="F29" s="105" t="n">
         <f aca="false">ROUNDUP(P24,0)</f>
-        <v>187</v>
+        <v>98</v>
       </c>
       <c r="G29" s="105" t="n">
         <f aca="false">S24</f>
-        <v>194.629386685225</v>
+        <v>102.59057040625</v>
       </c>
       <c r="H29" s="105" t="n">
         <f aca="false">ROUNDUP(V24,0)</f>
-        <v>204</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -17732,11 +17732,11 @@
       </c>
       <c r="C5" s="173" t="n">
         <f aca="false">'Customer Volumes'!D5</f>
-        <v>25786541</v>
+        <v>22500</v>
       </c>
       <c r="D5" s="174" t="n">
         <f aca="false">C5*'Datasize-Parameters'!$J$13/(1024*1024)</f>
-        <v>467.247275352478</v>
+        <v>0.407695770263672</v>
       </c>
       <c r="F5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -17744,11 +17744,11 @@
       </c>
       <c r="G5" s="173" t="n">
         <f aca="false">'Customer Volumes'!E5</f>
-        <v>28365195.1</v>
+        <v>25875</v>
       </c>
       <c r="H5" s="174" t="n">
         <f aca="false">G5*'Datasize-Parameters'!$J$13/(1024*1024)</f>
-        <v>513.972002887726</v>
+        <v>0.468850135803223</v>
       </c>
       <c r="J5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -17756,11 +17756,11 @@
       </c>
       <c r="K5" s="173" t="n">
         <f aca="false">'Customer Volumes'!F5</f>
-        <v>31201714.61</v>
+        <v>29756.25</v>
       </c>
       <c r="L5" s="174" t="n">
         <f aca="false">K5*'Datasize-Parameters'!$J$13/(1024*1024)</f>
-        <v>565.369203176498</v>
+        <v>0.539177656173706</v>
       </c>
       <c r="N5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -17768,11 +17768,11 @@
       </c>
       <c r="O5" s="173" t="n">
         <f aca="false">'Customer Volumes'!G5</f>
-        <v>34321886.071</v>
+        <v>34219.6875</v>
       </c>
       <c r="P5" s="174" t="n">
         <f aca="false">O5*'Datasize-Parameters'!$J$13/(1024*1024)</f>
-        <v>621.906123494149</v>
+        <v>0.620054304599762</v>
       </c>
       <c r="R5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -17780,11 +17780,11 @@
       </c>
       <c r="S5" s="173" t="n">
         <f aca="false">'Customer Volumes'!H5</f>
-        <v>37754074.6781</v>
+        <v>39352.640625</v>
       </c>
       <c r="T5" s="174" t="n">
         <f aca="false">S5*'Datasize-Parameters'!$J$13/(1024*1024)</f>
-        <v>684.096735843563</v>
+        <v>0.713062450289726</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17795,11 +17795,11 @@
       </c>
       <c r="C6" s="173" t="n">
         <f aca="false">'Customer Volumes'!D7</f>
-        <v>10700000</v>
+        <v>240000</v>
       </c>
       <c r="D6" s="174" t="n">
         <f aca="false">C6*'Datasize-Parameters'!$N$13/(1024*1024)</f>
-        <v>408.172607421875</v>
+        <v>9.1552734375</v>
       </c>
       <c r="F6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -17807,11 +17807,11 @@
       </c>
       <c r="G6" s="173" t="n">
         <f aca="false">'Customer Volumes'!E7</f>
-        <v>11770000</v>
+        <v>252000</v>
       </c>
       <c r="H6" s="174" t="n">
         <f aca="false">G6*'Datasize-Parameters'!$N$13/(1024*1024)</f>
-        <v>448.989868164063</v>
+        <v>9.613037109375</v>
       </c>
       <c r="J6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -17819,11 +17819,11 @@
       </c>
       <c r="K6" s="173" t="n">
         <f aca="false">'Customer Volumes'!F7</f>
-        <v>12947000</v>
+        <v>264600</v>
       </c>
       <c r="L6" s="174" t="n">
         <f aca="false">K6*'Datasize-Parameters'!$N$13/(1024*1024)</f>
-        <v>493.888854980469</v>
+        <v>10.0936889648438</v>
       </c>
       <c r="N6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -17831,11 +17831,11 @@
       </c>
       <c r="O6" s="173" t="n">
         <f aca="false">'Customer Volumes'!G7</f>
-        <v>14241700</v>
+        <v>277830</v>
       </c>
       <c r="P6" s="174" t="n">
         <f aca="false">O6*'Datasize-Parameters'!$N$13/(1024*1024)</f>
-        <v>543.277740478516</v>
+        <v>10.5983734130859</v>
       </c>
       <c r="R6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -17843,11 +17843,11 @@
       </c>
       <c r="S6" s="173" t="n">
         <f aca="false">'Customer Volumes'!H7</f>
-        <v>15665870</v>
+        <v>291721.5</v>
       </c>
       <c r="T6" s="174" t="n">
         <f aca="false">S6*'Datasize-Parameters'!$N$13/(1024*1024)</f>
-        <v>597.605514526367</v>
+        <v>11.1282920837402</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17858,11 +17858,11 @@
       </c>
       <c r="C7" s="173" t="n">
         <f aca="false">'Customer Volumes'!D9</f>
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="D7" s="174" t="n">
         <f aca="false">C7*'Datasize-Parameters'!$R$13/(1024*1024)</f>
-        <v>0.715255737304688</v>
+        <v>0.536441802978516</v>
       </c>
       <c r="F7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -17870,11 +17870,11 @@
       </c>
       <c r="G7" s="173" t="n">
         <f aca="false">'Customer Volumes'!E9</f>
-        <v>21000</v>
+        <v>18000</v>
       </c>
       <c r="H7" s="174" t="n">
         <f aca="false">G7*'Datasize-Parameters'!$R$13/(1024*1024)</f>
-        <v>0.751018524169922</v>
+        <v>0.643730163574219</v>
       </c>
       <c r="J7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -17882,11 +17882,11 @@
       </c>
       <c r="K7" s="173" t="n">
         <f aca="false">'Customer Volumes'!F9</f>
-        <v>22050</v>
+        <v>21600</v>
       </c>
       <c r="L7" s="174" t="n">
         <f aca="false">K7*'Datasize-Parameters'!$R$13/(1024*1024)</f>
-        <v>0.788569450378418</v>
+        <v>0.772476196289063</v>
       </c>
       <c r="N7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -17894,11 +17894,11 @@
       </c>
       <c r="O7" s="173" t="n">
         <f aca="false">'Customer Volumes'!G9</f>
-        <v>23152.5</v>
+        <v>25920</v>
       </c>
       <c r="P7" s="174" t="n">
         <f aca="false">O7*'Datasize-Parameters'!$R$13/(1024*1024)</f>
-        <v>0.827997922897339</v>
+        <v>0.926971435546875</v>
       </c>
       <c r="R7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -17906,11 +17906,11 @@
       </c>
       <c r="S7" s="173" t="n">
         <f aca="false">'Customer Volumes'!H9</f>
-        <v>24310.125</v>
+        <v>31104</v>
       </c>
       <c r="T7" s="174" t="n">
         <f aca="false">S7*'Datasize-Parameters'!$R$13/(1024*1024)</f>
-        <v>0.869397819042206</v>
+        <v>1.11236572265625</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18099,11 +18099,11 @@
       </c>
       <c r="C11" s="173" t="n">
         <f aca="false">'Customer Volumes'!D5*'Customer Volumes'!D12</f>
-        <v>25786541</v>
+        <v>22500</v>
       </c>
       <c r="D11" s="174" t="n">
         <f aca="false">C11*'Datasize-Parameters'!$J$39/(1024*1024)</f>
-        <v>196.735694885254</v>
+        <v>0.171661376953125</v>
       </c>
       <c r="F11" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$10</f>
@@ -18111,11 +18111,11 @@
       </c>
       <c r="G11" s="173" t="n">
         <f aca="false">'Customer Volumes'!E5*'Customer Volumes'!E12</f>
-        <v>28365195.1</v>
+        <v>25875</v>
       </c>
       <c r="H11" s="174" t="n">
         <f aca="false">G11*'Datasize-Parameters'!$J$39/(1024*1024)</f>
-        <v>216.409264373779</v>
+        <v>0.197410583496094</v>
       </c>
       <c r="J11" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$10</f>
@@ -18123,11 +18123,11 @@
       </c>
       <c r="K11" s="173" t="n">
         <f aca="false">'Customer Volumes'!F5*'Customer Volumes'!F12</f>
-        <v>31201714.61</v>
+        <v>29756.25</v>
       </c>
       <c r="L11" s="174" t="n">
         <f aca="false">K11*'Datasize-Parameters'!$J$39/(1024*1024)</f>
-        <v>238.050190811157</v>
+        <v>0.227022171020508</v>
       </c>
       <c r="N11" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$10</f>
@@ -18135,11 +18135,11 @@
       </c>
       <c r="O11" s="173" t="n">
         <f aca="false">'Customer Volumes'!G5*'Customer Volumes'!G12</f>
-        <v>34321886.071</v>
+        <v>34219.6875</v>
       </c>
       <c r="P11" s="174" t="n">
         <f aca="false">O11*'Datasize-Parameters'!$J$39/(1024*1024)</f>
-        <v>261.855209892273</v>
+        <v>0.261075496673584</v>
       </c>
       <c r="R11" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$10</f>
@@ -18147,11 +18147,11 @@
       </c>
       <c r="S11" s="173" t="n">
         <f aca="false">'Customer Volumes'!H5*'Customer Volumes'!H12</f>
-        <v>37754074.6781</v>
+        <v>39352.640625</v>
       </c>
       <c r="T11" s="174" t="n">
         <f aca="false">S11*'Datasize-Parameters'!$J$39/(1024*1024)</f>
-        <v>288.0407308815</v>
+        <v>0.300236821174621</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18323,55 +18323,55 @@
       </c>
       <c r="C15" s="173" t="n">
         <f aca="false">C5*0.3+C6*0.3+C7</f>
-        <v>10965962.3</v>
+        <v>93750</v>
       </c>
       <c r="D15" s="174" t="n">
         <f aca="false">C15*'Datasize-Parameters'!$V$13/(1024*1024)</f>
-        <v>5.22897830009461</v>
+        <v>0.044703483581543</v>
       </c>
       <c r="F15" s="172" t="s">
         <v>271</v>
       </c>
       <c r="G15" s="173" t="n">
         <f aca="false">G5*0.3+G6*0.3+G7</f>
-        <v>12061558.53</v>
+        <v>101362.5</v>
       </c>
       <c r="H15" s="174" t="n">
         <f aca="false">G15*'Datasize-Parameters'!$V$13/(1024*1024)</f>
-        <v>5.75139929294586</v>
+        <v>0.0483334064483643</v>
       </c>
       <c r="J15" s="172" t="s">
         <v>271</v>
       </c>
       <c r="K15" s="173" t="n">
         <f aca="false">K5*0.3+K6*0.3+K7</f>
-        <v>13266664.383</v>
+        <v>109906.875</v>
       </c>
       <c r="L15" s="174" t="n">
         <f aca="false">K15*'Datasize-Parameters'!$V$13/(1024*1024)</f>
-        <v>6.32603854322434</v>
+        <v>0.0524076819419861</v>
       </c>
       <c r="N15" s="172" t="s">
         <v>271</v>
       </c>
       <c r="O15" s="173" t="n">
         <f aca="false">O5*0.3+O6*0.3+O7</f>
-        <v>14592228.3213</v>
+        <v>119534.90625</v>
       </c>
       <c r="P15" s="174" t="n">
         <f aca="false">O15*'Datasize-Parameters'!$V$13/(1024*1024)</f>
-        <v>6.95811668457985</v>
+        <v>0.056998685002327</v>
       </c>
       <c r="R15" s="172" t="s">
         <v>271</v>
       </c>
       <c r="S15" s="173" t="n">
         <f aca="false">S5*0.3+S6*0.3+S7</f>
-        <v>16050293.52843</v>
+        <v>130426.2421875</v>
       </c>
       <c r="T15" s="174" t="n">
         <f aca="false">S15*'Datasize-Parameters'!$V$13/(1024*1024)</f>
-        <v>7.65337635442257</v>
+        <v>0.0621920786798</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18400,7 +18400,7 @@
       <c r="C17" s="178"/>
       <c r="D17" s="177" t="n">
         <f aca="false">SUM(D5:D15)</f>
-        <v>1078.1003839016</v>
+        <v>10.3163480758667</v>
       </c>
       <c r="F17" s="178" t="s">
         <v>272</v>
@@ -18408,7 +18408,7 @@
       <c r="G17" s="178"/>
       <c r="H17" s="177" t="n">
         <f aca="false">SUM(H5:H15)</f>
-        <v>1185.87412544727</v>
+        <v>10.9719336032867</v>
       </c>
       <c r="J17" s="178" t="s">
         <v>272</v>
@@ -18416,7 +18416,7 @@
       <c r="K17" s="178"/>
       <c r="L17" s="177" t="n">
         <f aca="false">SUM(L5:L15)</f>
-        <v>1304.42342916632</v>
+        <v>11.6853448748589</v>
       </c>
       <c r="N17" s="178" t="s">
         <v>272</v>
@@ -18424,7 +18424,7 @@
       <c r="O17" s="178"/>
       <c r="P17" s="177" t="n">
         <f aca="false">SUM(P5:P15)</f>
-        <v>1434.825760677</v>
+        <v>12.4640455394983</v>
       </c>
       <c r="Q17" s="179"/>
       <c r="R17" s="178" t="s">
@@ -18433,7 +18433,7 @@
       <c r="S17" s="178"/>
       <c r="T17" s="177" t="n">
         <f aca="false">SUM(T5:T15)</f>
-        <v>1578.2657554249</v>
+        <v>13.3161491565406</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18524,7 +18524,7 @@
       <c r="C22" s="185"/>
       <c r="D22" s="186" t="n">
         <f aca="false">D17</f>
-        <v>1078.1003839016</v>
+        <v>10.3163480758667</v>
       </c>
       <c r="F22" s="182" t="s">
         <v>268</v>
@@ -18532,7 +18532,7 @@
       <c r="G22" s="185"/>
       <c r="H22" s="186" t="n">
         <f aca="false">H17</f>
-        <v>1185.87412544727</v>
+        <v>10.9719336032867</v>
       </c>
       <c r="J22" s="182" t="s">
         <v>268</v>
@@ -18540,7 +18540,7 @@
       <c r="K22" s="185"/>
       <c r="L22" s="186" t="n">
         <f aca="false">L17</f>
-        <v>1304.42342916632</v>
+        <v>11.6853448748589</v>
       </c>
       <c r="N22" s="182" t="s">
         <v>268</v>
@@ -18548,7 +18548,7 @@
       <c r="O22" s="185"/>
       <c r="P22" s="186" t="n">
         <f aca="false">P17</f>
-        <v>1434.825760677</v>
+        <v>12.4640455394983</v>
       </c>
       <c r="R22" s="182" t="s">
         <v>268</v>
@@ -18556,7 +18556,7 @@
       <c r="S22" s="185"/>
       <c r="T22" s="186" t="n">
         <f aca="false">T17</f>
-        <v>1578.2657554249</v>
+        <v>13.3161491565406</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18567,7 +18567,7 @@
       <c r="C23" s="185"/>
       <c r="D23" s="186" t="n">
         <f aca="false">D22*'Datasize-Parameters'!$C$29</f>
-        <v>161.715057585239</v>
+        <v>1.54745221138</v>
       </c>
       <c r="F23" s="182" t="s">
         <v>253</v>
@@ -18575,7 +18575,7 @@
       <c r="G23" s="185"/>
       <c r="H23" s="186" t="n">
         <f aca="false">H22*'Datasize-Parameters'!$C$29</f>
-        <v>177.881118817091</v>
+        <v>1.64579004049301</v>
       </c>
       <c r="J23" s="182" t="s">
         <v>253</v>
@@ -18583,7 +18583,7 @@
       <c r="K23" s="185"/>
       <c r="L23" s="186" t="n">
         <f aca="false">L22*'Datasize-Parameters'!$C$29</f>
-        <v>195.663514374948</v>
+        <v>1.75280173122883</v>
       </c>
       <c r="N23" s="182" t="s">
         <v>253</v>
@@ -18591,7 +18591,7 @@
       <c r="O23" s="185"/>
       <c r="P23" s="186" t="n">
         <f aca="false">P22*'Datasize-Parameters'!$C$29</f>
-        <v>215.223864101551</v>
+        <v>1.86960683092475</v>
       </c>
       <c r="R23" s="182" t="s">
         <v>253</v>
@@ -18599,7 +18599,7 @@
       <c r="S23" s="185"/>
       <c r="T23" s="186" t="n">
         <f aca="false">T22*'Datasize-Parameters'!$C$29</f>
-        <v>236.739863313734</v>
+        <v>1.99742237348109</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18610,7 +18610,7 @@
       <c r="C24" s="185"/>
       <c r="D24" s="186" t="n">
         <f aca="false">D22*'Datasize-Parameters'!$C$30</f>
-        <v>215.620076780319</v>
+        <v>2.06326961517334</v>
       </c>
       <c r="F24" s="182" t="s">
         <v>255</v>
@@ -18618,7 +18618,7 @@
       <c r="G24" s="185"/>
       <c r="H24" s="186" t="n">
         <f aca="false">H22*'Datasize-Parameters'!$C$30</f>
-        <v>237.174825089455</v>
+        <v>2.19438672065735</v>
       </c>
       <c r="J24" s="182" t="s">
         <v>255</v>
@@ -18626,7 +18626,7 @@
       <c r="K24" s="185"/>
       <c r="L24" s="186" t="n">
         <f aca="false">L22*'Datasize-Parameters'!$C$30</f>
-        <v>260.884685833263</v>
+        <v>2.33706897497177</v>
       </c>
       <c r="N24" s="182" t="s">
         <v>255</v>
@@ -18634,7 +18634,7 @@
       <c r="O24" s="185"/>
       <c r="P24" s="186" t="n">
         <f aca="false">P22*'Datasize-Parameters'!$C$30</f>
-        <v>286.965152135401</v>
+        <v>2.49280910789967</v>
       </c>
       <c r="R24" s="182" t="s">
         <v>255</v>
@@ -18642,7 +18642,7 @@
       <c r="S24" s="185"/>
       <c r="T24" s="186" t="n">
         <f aca="false">T22*'Datasize-Parameters'!$C$30</f>
-        <v>315.653151084979</v>
+        <v>2.66322983130813</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18653,7 +18653,7 @@
       <c r="C25" s="185"/>
       <c r="D25" s="186" t="n">
         <f aca="false">D22*'Datasize-Parameters'!$C$31</f>
-        <v>215.620076780319</v>
+        <v>2.06326961517334</v>
       </c>
       <c r="F25" s="182" t="s">
         <v>256</v>
@@ -18661,7 +18661,7 @@
       <c r="G25" s="185"/>
       <c r="H25" s="186" t="n">
         <f aca="false">H22*'Datasize-Parameters'!$C$31</f>
-        <v>237.174825089455</v>
+        <v>2.19438672065735</v>
       </c>
       <c r="J25" s="182" t="s">
         <v>256</v>
@@ -18669,7 +18669,7 @@
       <c r="K25" s="185"/>
       <c r="L25" s="186" t="n">
         <f aca="false">L22*'Datasize-Parameters'!$C$31</f>
-        <v>260.884685833263</v>
+        <v>2.33706897497177</v>
       </c>
       <c r="N25" s="182" t="s">
         <v>256</v>
@@ -18677,7 +18677,7 @@
       <c r="O25" s="185"/>
       <c r="P25" s="186" t="n">
         <f aca="false">P22*'Datasize-Parameters'!$C$31</f>
-        <v>286.965152135401</v>
+        <v>2.49280910789967</v>
       </c>
       <c r="R25" s="182" t="s">
         <v>256</v>
@@ -18685,7 +18685,7 @@
       <c r="S25" s="185"/>
       <c r="T25" s="186" t="n">
         <f aca="false">T22*'Datasize-Parameters'!$C$31</f>
-        <v>315.653151084979</v>
+        <v>2.66322983130813</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18696,7 +18696,7 @@
       <c r="C26" s="185"/>
       <c r="D26" s="186" t="n">
         <f aca="false">D22*'Datasize-Parameters'!$C$32</f>
-        <v>215.620076780319</v>
+        <v>2.06326961517334</v>
       </c>
       <c r="F26" s="181" t="s">
         <v>275</v>
@@ -18704,7 +18704,7 @@
       <c r="G26" s="185"/>
       <c r="H26" s="186" t="n">
         <f aca="false">H22*'Datasize-Parameters'!$C$32</f>
-        <v>237.174825089455</v>
+        <v>2.19438672065735</v>
       </c>
       <c r="J26" s="181" t="s">
         <v>275</v>
@@ -18712,7 +18712,7 @@
       <c r="K26" s="185"/>
       <c r="L26" s="186" t="n">
         <f aca="false">L22*'Datasize-Parameters'!$C$32</f>
-        <v>260.884685833263</v>
+        <v>2.33706897497177</v>
       </c>
       <c r="N26" s="181" t="s">
         <v>275</v>
@@ -18720,7 +18720,7 @@
       <c r="O26" s="185"/>
       <c r="P26" s="186" t="n">
         <f aca="false">P22*'Datasize-Parameters'!$C$32</f>
-        <v>286.965152135401</v>
+        <v>2.49280910789967</v>
       </c>
       <c r="R26" s="181" t="s">
         <v>275</v>
@@ -18728,7 +18728,7 @@
       <c r="S26" s="185"/>
       <c r="T26" s="186" t="n">
         <f aca="false">T22*'Datasize-Parameters'!$C$32</f>
-        <v>315.653151084979</v>
+        <v>2.66322983130813</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18739,7 +18739,7 @@
       <c r="C27" s="185"/>
       <c r="D27" s="186" t="n">
         <f aca="false">D23*'Datasize-Parameters'!$C$33</f>
-        <v>40.4287643963099</v>
+        <v>0.386863052845001</v>
       </c>
       <c r="F27" s="182" t="s">
         <v>276</v>
@@ -18747,7 +18747,7 @@
       <c r="G27" s="185"/>
       <c r="H27" s="186" t="n">
         <f aca="false">H23*'Datasize-Parameters'!$C$33</f>
-        <v>44.4702797042728</v>
+        <v>0.411447510123253</v>
       </c>
       <c r="J27" s="182" t="s">
         <v>276</v>
@@ -18755,7 +18755,7 @@
       <c r="K27" s="185"/>
       <c r="L27" s="186" t="n">
         <f aca="false">L23*'Datasize-Parameters'!$C$33</f>
-        <v>48.9158785937369</v>
+        <v>0.438200432807207</v>
       </c>
       <c r="N27" s="182" t="s">
         <v>276</v>
@@ -18763,7 +18763,7 @@
       <c r="O27" s="185"/>
       <c r="P27" s="186" t="n">
         <f aca="false">P23*'Datasize-Parameters'!$C$33</f>
-        <v>53.8059660253877</v>
+        <v>0.467401707731187</v>
       </c>
       <c r="R27" s="182" t="s">
         <v>276</v>
@@ -18771,7 +18771,7 @@
       <c r="S27" s="185"/>
       <c r="T27" s="186" t="n">
         <f aca="false">T23*'Datasize-Parameters'!$C$33</f>
-        <v>59.1849658284336</v>
+        <v>0.499355593370274</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18782,7 +18782,7 @@
       <c r="C28" s="185"/>
       <c r="D28" s="186" t="n">
         <f aca="false">D22*'Datasize-Parameters'!$C$34</f>
-        <v>107.81003839016</v>
+        <v>1.03163480758667</v>
       </c>
       <c r="F28" s="182" t="s">
         <v>277</v>
@@ -18790,7 +18790,7 @@
       <c r="G28" s="185"/>
       <c r="H28" s="186" t="n">
         <f aca="false">H22*'Datasize-Parameters'!$C$34</f>
-        <v>118.587412544727</v>
+        <v>1.09719336032867</v>
       </c>
       <c r="J28" s="182" t="s">
         <v>277</v>
@@ -18798,7 +18798,7 @@
       <c r="K28" s="185"/>
       <c r="L28" s="186" t="n">
         <f aca="false">L22*'Datasize-Parameters'!$C$34</f>
-        <v>130.442342916632</v>
+        <v>1.16853448748589</v>
       </c>
       <c r="N28" s="182" t="s">
         <v>277</v>
@@ -18806,7 +18806,7 @@
       <c r="O28" s="185"/>
       <c r="P28" s="186" t="n">
         <f aca="false">P22*'Datasize-Parameters'!$C$34</f>
-        <v>143.4825760677</v>
+        <v>1.24640455394983</v>
       </c>
       <c r="R28" s="182" t="s">
         <v>277</v>
@@ -18814,7 +18814,7 @@
       <c r="S28" s="185"/>
       <c r="T28" s="186" t="n">
         <f aca="false">T22*'Datasize-Parameters'!$C$34</f>
-        <v>157.82657554249</v>
+        <v>1.33161491565406</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18843,7 +18843,7 @@
       <c r="C30" s="185"/>
       <c r="D30" s="188" t="n">
         <f aca="false">SUM(D22:D28)</f>
-        <v>2034.91447461426</v>
+        <v>19.4721069931984</v>
       </c>
       <c r="F30" s="187" t="s">
         <v>279</v>
@@ -18851,7 +18851,7 @@
       <c r="G30" s="185"/>
       <c r="H30" s="188" t="n">
         <f aca="false">SUM(H22:H28)</f>
-        <v>2238.33741178173</v>
+        <v>20.7095246762037</v>
       </c>
       <c r="J30" s="187" t="s">
         <v>280</v>
@@ -18859,7 +18859,7 @@
       <c r="K30" s="185"/>
       <c r="L30" s="188" t="n">
         <f aca="false">SUM(L22:L28)</f>
-        <v>2462.09922255142</v>
+        <v>22.0560884512961</v>
       </c>
       <c r="N30" s="187" t="s">
         <v>281</v>
@@ -18867,7 +18867,7 @@
       <c r="O30" s="185"/>
       <c r="P30" s="188" t="n">
         <f aca="false">SUM(P22:P28)</f>
-        <v>2708.23362327785</v>
+        <v>23.5258859558031</v>
       </c>
       <c r="R30" s="187" t="s">
         <v>282</v>
@@ -18875,7 +18875,7 @@
       <c r="S30" s="185"/>
       <c r="T30" s="188" t="n">
         <f aca="false">SUM(T22:T28)</f>
-        <v>2978.97661336449</v>
+        <v>25.1342315329704</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20384,11 +20384,11 @@
       </c>
       <c r="C5" s="173" t="n">
         <f aca="false">'Customer Volumes'!D5*'Customer Volumes'!D14*0.3</f>
-        <v>15471924.6</v>
+        <v>13500</v>
       </c>
       <c r="D5" s="174" t="n">
         <f aca="false">C5*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>3777.32534179688</v>
+        <v>3.2958984375</v>
       </c>
       <c r="F5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -20396,11 +20396,11 @@
       </c>
       <c r="G5" s="173" t="n">
         <f aca="false">'Customer Volumes'!E5*'Customer Volumes'!E14*0.3</f>
-        <v>17019117.06</v>
+        <v>15525</v>
       </c>
       <c r="H5" s="174" t="n">
         <f aca="false">G5*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>4155.05787597656</v>
+        <v>3.790283203125</v>
       </c>
       <c r="J5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -20408,11 +20408,11 @@
       </c>
       <c r="K5" s="173" t="n">
         <f aca="false">'Customer Volumes'!F5*'Customer Volumes'!F14*0.3</f>
-        <v>18721028.766</v>
+        <v>17853.75</v>
       </c>
       <c r="L5" s="174" t="n">
         <f aca="false">K5*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>4570.56366357422</v>
+        <v>4.35882568359375</v>
       </c>
       <c r="N5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -20420,11 +20420,11 @@
       </c>
       <c r="O5" s="173" t="n">
         <f aca="false">'Customer Volumes'!G5*'Customer Volumes'!G14*0.3</f>
-        <v>20593131.6426</v>
+        <v>20531.8125</v>
       </c>
       <c r="P5" s="174" t="n">
         <f aca="false">O5*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>5027.62002993164</v>
+        <v>5.01264953613281</v>
       </c>
       <c r="R5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -20432,11 +20432,11 @@
       </c>
       <c r="S5" s="173" t="n">
         <f aca="false">'Customer Volumes'!H5*'Customer Volumes'!H14*0.3</f>
-        <v>22652444.80686</v>
+        <v>23611.584375</v>
       </c>
       <c r="T5" s="174" t="n">
         <f aca="false">S5*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>5530.38203292481</v>
+        <v>5.76454696655273</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20447,11 +20447,11 @@
       </c>
       <c r="C6" s="173" t="n">
         <f aca="false">'Customer Volumes'!D7*'Customer Volumes'!D15*0.3</f>
-        <v>6420000</v>
+        <v>144000</v>
       </c>
       <c r="D6" s="174" t="n">
         <f aca="false">C6*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>1567.3828125</v>
+        <v>35.15625</v>
       </c>
       <c r="F6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -20459,11 +20459,11 @@
       </c>
       <c r="G6" s="173" t="n">
         <f aca="false">'Customer Volumes'!E7*'Customer Volumes'!E15*0.3</f>
-        <v>7062000</v>
+        <v>151200</v>
       </c>
       <c r="H6" s="174" t="n">
         <f aca="false">G6*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>1724.12109375</v>
+        <v>36.9140625</v>
       </c>
       <c r="J6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -20471,11 +20471,11 @@
       </c>
       <c r="K6" s="173" t="n">
         <f aca="false">'Customer Volumes'!F7*'Customer Volumes'!F15*0.3</f>
-        <v>7768200</v>
+        <v>158760</v>
       </c>
       <c r="L6" s="174" t="n">
         <f aca="false">K6*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>1896.533203125</v>
+        <v>38.759765625</v>
       </c>
       <c r="N6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -20483,11 +20483,11 @@
       </c>
       <c r="O6" s="173" t="n">
         <f aca="false">'Customer Volumes'!G7*'Customer Volumes'!G15*0.3</f>
-        <v>8545020</v>
+        <v>166698</v>
       </c>
       <c r="P6" s="174" t="n">
         <f aca="false">O6*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>2086.1865234375</v>
+        <v>40.69775390625</v>
       </c>
       <c r="R6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -20495,11 +20495,11 @@
       </c>
       <c r="S6" s="173" t="n">
         <f aca="false">'Customer Volumes'!H7*'Customer Volumes'!H15*0.3</f>
-        <v>9399522</v>
+        <v>175032.9</v>
       </c>
       <c r="T6" s="174" t="n">
         <f aca="false">S6*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>2294.80517578125</v>
+        <v>42.7326416015625</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20510,11 +20510,11 @@
       </c>
       <c r="C7" s="173" t="n">
         <f aca="false">'Customer Volumes'!D9*'Customer Volumes'!D16</f>
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="D7" s="174" t="n">
         <f aca="false">C7*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>4.8828125</v>
+        <v>3.662109375</v>
       </c>
       <c r="F7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -20522,11 +20522,11 @@
       </c>
       <c r="G7" s="173" t="n">
         <f aca="false">'Customer Volumes'!E9*'Customer Volumes'!E16</f>
-        <v>21000</v>
+        <v>18000</v>
       </c>
       <c r="H7" s="174" t="n">
         <f aca="false">G7*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>5.126953125</v>
+        <v>4.39453125</v>
       </c>
       <c r="J7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -20534,11 +20534,11 @@
       </c>
       <c r="K7" s="173" t="n">
         <f aca="false">'Customer Volumes'!F9*'Customer Volumes'!F16</f>
-        <v>22050</v>
+        <v>21600</v>
       </c>
       <c r="L7" s="174" t="n">
         <f aca="false">K7*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>5.38330078125</v>
+        <v>5.2734375</v>
       </c>
       <c r="N7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -20546,11 +20546,11 @@
       </c>
       <c r="O7" s="173" t="n">
         <f aca="false">'Customer Volumes'!G9*'Customer Volumes'!G16</f>
-        <v>23152.5</v>
+        <v>25920</v>
       </c>
       <c r="P7" s="174" t="n">
         <f aca="false">O7*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>5.6524658203125</v>
+        <v>6.328125</v>
       </c>
       <c r="R7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -20558,11 +20558,11 @@
       </c>
       <c r="S7" s="173" t="n">
         <f aca="false">'Customer Volumes'!H9*'Customer Volumes'!H16</f>
-        <v>24310.125</v>
+        <v>31104</v>
       </c>
       <c r="T7" s="174" t="n">
         <f aca="false">S7*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>5.93508911132813</v>
+        <v>7.59375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20822,7 +20822,7 @@
       <c r="C13" s="178"/>
       <c r="D13" s="177" t="n">
         <f aca="false">SUM(D5:D11)</f>
-        <v>5349.59096679688</v>
+        <v>42.1142578125</v>
       </c>
       <c r="F13" s="178" t="s">
         <v>289</v>
@@ -20830,7 +20830,7 @@
       <c r="G13" s="178"/>
       <c r="H13" s="177" t="n">
         <f aca="false">SUM(H5:H11)</f>
-        <v>5884.30592285156</v>
+        <v>45.098876953125</v>
       </c>
       <c r="J13" s="178" t="s">
         <v>289</v>
@@ -20838,7 +20838,7 @@
       <c r="K13" s="178"/>
       <c r="L13" s="177" t="n">
         <f aca="false">SUM(L5:L11)</f>
-        <v>6472.48016748047</v>
+        <v>48.3920288085938</v>
       </c>
       <c r="N13" s="178" t="s">
         <v>289</v>
@@ -20846,7 +20846,7 @@
       <c r="O13" s="178"/>
       <c r="P13" s="177" t="n">
         <f aca="false">SUM(P5:P11)</f>
-        <v>7119.45901918946</v>
+        <v>52.0385284423828</v>
       </c>
       <c r="R13" s="178" t="s">
         <v>289</v>
@@ -20854,7 +20854,7 @@
       <c r="S13" s="178"/>
       <c r="T13" s="177" t="n">
         <f aca="false">SUM(T5:T11)</f>
-        <v>7831.12229781739</v>
+        <v>56.0909385681152</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20957,7 +20957,7 @@
       <c r="C18" s="185"/>
       <c r="D18" s="186" t="n">
         <f aca="false">D13</f>
-        <v>5349.59096679688</v>
+        <v>42.1142578125</v>
       </c>
       <c r="F18" s="182" t="s">
         <v>272</v>
@@ -20965,7 +20965,7 @@
       <c r="G18" s="185"/>
       <c r="H18" s="186" t="n">
         <f aca="false">H13</f>
-        <v>5884.30592285156</v>
+        <v>45.098876953125</v>
       </c>
       <c r="J18" s="182" t="s">
         <v>272</v>
@@ -20973,7 +20973,7 @@
       <c r="K18" s="185"/>
       <c r="L18" s="186" t="n">
         <f aca="false">L13</f>
-        <v>6472.48016748047</v>
+        <v>48.3920288085938</v>
       </c>
       <c r="N18" s="182" t="s">
         <v>272</v>
@@ -20981,7 +20981,7 @@
       <c r="O18" s="185"/>
       <c r="P18" s="186" t="n">
         <f aca="false">P13</f>
-        <v>7119.45901918946</v>
+        <v>52.0385284423828</v>
       </c>
       <c r="R18" s="182" t="s">
         <v>272</v>
@@ -20989,7 +20989,7 @@
       <c r="S18" s="185"/>
       <c r="T18" s="186" t="n">
         <f aca="false">T13</f>
-        <v>7831.12229781739</v>
+        <v>56.0909385681152</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21000,7 +21000,7 @@
       <c r="C19" s="185"/>
       <c r="D19" s="186" t="n">
         <f aca="false">D18*10%</f>
-        <v>534.959096679688</v>
+        <v>4.21142578125</v>
       </c>
       <c r="E19" s="179"/>
       <c r="F19" s="182" t="s">
@@ -21009,7 +21009,7 @@
       <c r="G19" s="185"/>
       <c r="H19" s="186" t="n">
         <f aca="false">H18*10%</f>
-        <v>588.430592285156</v>
+        <v>4.5098876953125</v>
       </c>
       <c r="I19" s="179"/>
       <c r="J19" s="182" t="s">
@@ -21018,7 +21018,7 @@
       <c r="K19" s="185"/>
       <c r="L19" s="186" t="n">
         <f aca="false">L18*10%</f>
-        <v>647.248016748047</v>
+        <v>4.83920288085938</v>
       </c>
       <c r="M19" s="179"/>
       <c r="N19" s="182" t="s">
@@ -21027,7 +21027,7 @@
       <c r="O19" s="185"/>
       <c r="P19" s="186" t="n">
         <f aca="false">P18*10%</f>
-        <v>711.945901918946</v>
+        <v>5.20385284423828</v>
       </c>
       <c r="R19" s="182" t="s">
         <v>291</v>
@@ -21035,7 +21035,7 @@
       <c r="S19" s="185"/>
       <c r="T19" s="186" t="n">
         <f aca="false">T18*10%</f>
-        <v>783.112229781739</v>
+        <v>5.60909385681152</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21064,7 +21064,7 @@
       <c r="C21" s="185"/>
       <c r="D21" s="197" t="n">
         <f aca="false">SUM(D18:D19)</f>
-        <v>5884.55006347656</v>
+        <v>46.32568359375</v>
       </c>
       <c r="F21" s="187" t="s">
         <v>292</v>
@@ -21072,7 +21072,7 @@
       <c r="G21" s="185"/>
       <c r="H21" s="197" t="n">
         <f aca="false">SUM(H18:H19)</f>
-        <v>6472.73651513672</v>
+        <v>49.6087646484375</v>
       </c>
       <c r="J21" s="187" t="s">
         <v>280</v>
@@ -21080,7 +21080,7 @@
       <c r="K21" s="185"/>
       <c r="L21" s="197" t="n">
         <f aca="false">SUM(L18:L19)</f>
-        <v>7119.72818422852</v>
+        <v>53.2312316894531</v>
       </c>
       <c r="N21" s="187" t="s">
         <v>281</v>
@@ -21088,7 +21088,7 @@
       <c r="O21" s="185"/>
       <c r="P21" s="197" t="n">
         <f aca="false">SUM(P18:P19)</f>
-        <v>7831.4049211084</v>
+        <v>57.2423812866211</v>
       </c>
       <c r="R21" s="187" t="s">
         <v>282</v>
@@ -21096,7 +21096,7 @@
       <c r="S21" s="185"/>
       <c r="T21" s="197" t="n">
         <f aca="false">SUM(T18:T19)</f>
-        <v>8614.23452759913</v>
+        <v>61.7000324249267</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/reports/updated_estimate.xlsx
+++ b/reports/updated_estimate.xlsx
@@ -4388,15 +4388,15 @@
       </c>
       <c r="D8" s="214" t="n">
         <f aca="false">2*ROUND('Server size'!C22,1)</f>
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="E8" s="214" t="n">
         <f aca="false">ROUNDUP('Data size'!D30/50,0)*50</f>
-        <v>50</v>
+        <v>2050</v>
       </c>
       <c r="F8" s="214" t="n">
         <f aca="false">ROUNDUP('DMS size'!D21/100,0)*100</f>
-        <v>100</v>
+        <v>5900</v>
       </c>
       <c r="H8" s="215" t="n">
         <v>2</v>
@@ -4422,15 +4422,15 @@
       </c>
       <c r="D9" s="214" t="n">
         <f aca="false">2*ROUND('Server size'!D22,1)</f>
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="E9" s="214" t="n">
         <f aca="false">ROUNDUP('Data size'!H30/50,0)*50</f>
-        <v>50</v>
+        <v>2250</v>
       </c>
       <c r="F9" s="214" t="n">
         <f aca="false">ROUNDUP('DMS size'!H21/100,0)*100</f>
-        <v>100</v>
+        <v>6500</v>
       </c>
       <c r="H9" s="215" t="n">
         <v>4</v>
@@ -4456,15 +4456,15 @@
       </c>
       <c r="D10" s="214" t="n">
         <f aca="false">2*'Server size'!E22</f>
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="E10" s="214" t="n">
         <f aca="false">ROUNDUP('Data size'!L30/50,0)*50</f>
-        <v>50</v>
+        <v>2500</v>
       </c>
       <c r="F10" s="214" t="n">
         <f aca="false">ROUNDUP('DMS size'!L21/100,0)*100</f>
-        <v>100</v>
+        <v>7200</v>
       </c>
       <c r="H10" s="215" t="n">
         <v>6</v>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="N10" s="217" t="n">
         <f aca="false">VLOOKUP(E4,B8:F12,3,FALSE())</f>
-        <v>60</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4490,15 +4490,15 @@
       </c>
       <c r="D11" s="214" t="n">
         <f aca="false">2*ROUND('Server size'!F22,1)</f>
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="E11" s="214" t="n">
         <f aca="false">ROUNDUP('Data size'!P30/50,0)*50</f>
-        <v>50</v>
+        <v>2750</v>
       </c>
       <c r="F11" s="214" t="n">
         <f aca="false">ROUNDUP('DMS size'!P21/100,0)*100</f>
-        <v>100</v>
+        <v>7900</v>
       </c>
       <c r="G11" s="219"/>
       <c r="H11" s="215" t="n">
@@ -4511,9 +4511,9 @@
       <c r="M11" s="218" t="s">
         <v>318</v>
       </c>
-      <c r="N11" s="217" t="n">
+      <c r="N11" s="217" t="e">
         <f aca="false">VLOOKUP(N10,H8:I39,2,FALSE())</f>
-        <v>64</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4526,15 +4526,15 @@
       </c>
       <c r="D12" s="214" t="n">
         <f aca="false">2*ROUND('Server size'!G22,1)</f>
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="E12" s="214" t="n">
         <f aca="false">ROUNDUP('Data size'!T30/50,0)*50</f>
-        <v>50</v>
+        <v>3000</v>
       </c>
       <c r="F12" s="214" t="n">
         <f aca="false">ROUNDUP('DMS size'!T21/100,0)*100</f>
-        <v>100</v>
+        <v>8700</v>
       </c>
       <c r="G12" s="219"/>
       <c r="H12" s="215" t="n">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="N12" s="217" t="n">
         <f aca="false">VLOOKUP(E4,B8:F12,4,FALSE())</f>
-        <v>50</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="N13" s="217" t="n">
         <f aca="false">VLOOKUP(E4,B8:F12,5,FALSE())</f>
-        <v>100</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="N17" s="226" t="n">
         <f aca="false">N12/100</f>
-        <v>0.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5619,24 +5619,24 @@
       <c r="E13" s="251" t="s">
         <v>375</v>
       </c>
-      <c r="F13" s="260" t="n">
+      <c r="F13" s="260" t="e">
         <f aca="false">'Cloud sizing inputs'!N11</f>
-        <v>64</v>
-      </c>
-      <c r="G13" s="260" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="G13" s="260" t="e">
         <f aca="false">F13*8</f>
-        <v>512</v>
+        <v>#N/A</v>
       </c>
       <c r="H13" s="260" t="n">
         <v>300</v>
       </c>
-      <c r="I13" s="260" t="n">
+      <c r="I13" s="260" t="e">
         <f aca="false">F13*C13</f>
-        <v>128</v>
-      </c>
-      <c r="J13" s="252" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="J13" s="252" t="e">
         <f aca="false">G13*C13</f>
-        <v>1024</v>
+        <v>#N/A</v>
       </c>
       <c r="K13" s="255" t="n">
         <f aca="false">H13*C13/1024</f>
@@ -5672,20 +5672,20 @@
       </c>
       <c r="D15" s="263" t="n">
         <f aca="false">ROUNDUP('Cloud sizing inputs'!N17/5,0)*5</f>
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E15" s="264"/>
       <c r="F15" s="260"/>
       <c r="G15" s="260"/>
       <c r="H15" s="260" t="n">
         <f aca="false">'Cloud sizing inputs'!N12</f>
-        <v>50</v>
+        <v>3000</v>
       </c>
       <c r="I15" s="260"/>
       <c r="J15" s="252"/>
       <c r="K15" s="255" t="n">
         <f aca="false">H15/1024</f>
-        <v>0.048828125</v>
+        <v>2.9296875</v>
       </c>
     </row>
     <row r="16" s="256" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5732,25 +5732,25 @@
         <f aca="false">E13</f>
         <v>Reserved</v>
       </c>
-      <c r="F18" s="252" t="n">
+      <c r="F18" s="252" t="e">
         <f aca="false">F13</f>
-        <v>64</v>
-      </c>
-      <c r="G18" s="252" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="G18" s="252" t="e">
         <f aca="false">G13</f>
-        <v>512</v>
+        <v>#N/A</v>
       </c>
       <c r="H18" s="252" t="n">
         <f aca="false">H13</f>
         <v>300</v>
       </c>
-      <c r="I18" s="252" t="n">
+      <c r="I18" s="252" t="e">
         <f aca="false">F18*C18</f>
-        <v>64</v>
-      </c>
-      <c r="J18" s="252" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="J18" s="252" t="e">
         <f aca="false">G18*C18</f>
-        <v>512</v>
+        <v>#N/A</v>
       </c>
       <c r="K18" s="255" t="n">
         <f aca="false">H18*C18/1024</f>
@@ -5789,20 +5789,20 @@
       </c>
       <c r="D20" s="263" t="n">
         <f aca="false">D15</f>
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E20" s="266"/>
       <c r="F20" s="260"/>
       <c r="G20" s="252"/>
       <c r="H20" s="252" t="n">
         <f aca="false">H15</f>
-        <v>50</v>
+        <v>3000</v>
       </c>
       <c r="I20" s="260"/>
       <c r="J20" s="252"/>
       <c r="K20" s="255" t="n">
         <f aca="false">H20/1024</f>
-        <v>0.048828125</v>
+        <v>2.9296875</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5849,13 +5849,13 @@
       <c r="G23" s="245"/>
       <c r="H23" s="260" t="n">
         <f aca="false">'Cloud sizing inputs'!N13</f>
-        <v>100</v>
+        <v>8700</v>
       </c>
       <c r="I23" s="245"/>
       <c r="J23" s="245"/>
       <c r="K23" s="255" t="n">
         <f aca="false">H23/1024</f>
-        <v>0.09765625</v>
+        <v>8.49609375</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5899,15 +5899,15 @@
         <v>375</v>
       </c>
       <c r="F26" s="245"/>
-      <c r="G26" s="252" t="n">
+      <c r="G26" s="252" t="e">
         <f aca="false">IF(F13&lt;33,16,32)</f>
-        <v>32</v>
+        <v>#N/A</v>
       </c>
       <c r="H26" s="252"/>
       <c r="I26" s="245"/>
-      <c r="J26" s="245" t="n">
+      <c r="J26" s="245" t="e">
         <f aca="false">G26*C26</f>
-        <v>96</v>
+        <v>#N/A</v>
       </c>
       <c r="K26" s="245"/>
       <c r="L26" s="273"/>
@@ -6084,7 +6084,7 @@
       <c r="J35" s="245"/>
       <c r="K35" s="253" t="n">
         <f aca="false">K15*5/2</f>
-        <v>0.1220703125</v>
+        <v>7.32421875</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6403,23 +6403,23 @@
       </c>
       <c r="C4" s="287" t="n">
         <f aca="false">'Customer Volumes'!D4</f>
-        <v>1500</v>
+        <v>4650</v>
       </c>
       <c r="D4" s="287" t="n">
         <f aca="false">'Customer Volumes'!E4</f>
-        <v>1650</v>
+        <v>4882.5</v>
       </c>
       <c r="E4" s="287" t="n">
         <f aca="false">'Customer Volumes'!F4</f>
-        <v>1815</v>
+        <v>5126.625</v>
       </c>
       <c r="F4" s="287" t="n">
         <f aca="false">'Customer Volumes'!G4</f>
-        <v>1996.5</v>
+        <v>5382.95625</v>
       </c>
       <c r="G4" s="287" t="n">
         <f aca="false">'Customer Volumes'!H4</f>
-        <v>2196.15</v>
+        <v>5652.1040625</v>
       </c>
       <c r="H4" s="215"/>
     </row>
@@ -6442,23 +6442,23 @@
       </c>
       <c r="C6" s="291" t="n">
         <f aca="false">'Services Calculation'!D28</f>
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="D6" s="291" t="n">
         <f aca="false">'Services Calculation'!E28</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E6" s="291" t="n">
         <f aca="false">'Services Calculation'!F28</f>
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="F6" s="291" t="n">
         <f aca="false">'Services Calculation'!G28</f>
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="G6" s="291" t="n">
         <f aca="false">'Services Calculation'!H28</f>
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="H6" s="215"/>
     </row>
@@ -6469,23 +6469,23 @@
       </c>
       <c r="C7" s="291" t="n">
         <f aca="false">'Services Calculation'!D29</f>
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="D7" s="291" t="n">
         <f aca="false">'Services Calculation'!E29</f>
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="E7" s="291" t="n">
         <f aca="false">'Services Calculation'!F29</f>
-        <v>98</v>
+        <v>187</v>
       </c>
       <c r="F7" s="291" t="n">
         <f aca="false">'Services Calculation'!G29</f>
-        <v>102.59057040625</v>
+        <v>194.629386685225</v>
       </c>
       <c r="G7" s="291" t="n">
         <f aca="false">'Services Calculation'!H29</f>
-        <v>109</v>
+        <v>204</v>
       </c>
       <c r="H7" s="215"/>
     </row>
@@ -6496,23 +6496,23 @@
       </c>
       <c r="C8" s="292" t="n">
         <f aca="false">C6/16</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" s="292" t="n">
         <f aca="false">D6/16</f>
-        <v>3.125</v>
+        <v>6.25</v>
       </c>
       <c r="E8" s="292" t="n">
         <f aca="false">E6/16</f>
-        <v>3.3125</v>
+        <v>6.5</v>
       </c>
       <c r="F8" s="292" t="n">
         <f aca="false">F6/16</f>
-        <v>3.5</v>
+        <v>6.75</v>
       </c>
       <c r="G8" s="292" t="n">
         <f aca="false">G6/16</f>
-        <v>3.6875</v>
+        <v>7.0625</v>
       </c>
       <c r="H8" s="215"/>
     </row>
@@ -6523,23 +6523,23 @@
       </c>
       <c r="C9" s="292" t="n">
         <f aca="false">C7/32</f>
-        <v>2.75</v>
+        <v>5.375</v>
       </c>
       <c r="D9" s="292" t="n">
         <f aca="false">D7/32</f>
-        <v>2.90625</v>
+        <v>5.59375</v>
       </c>
       <c r="E9" s="292" t="n">
         <f aca="false">E7/32</f>
-        <v>3.0625</v>
+        <v>5.84375</v>
       </c>
       <c r="F9" s="292" t="n">
         <f aca="false">F7/32</f>
-        <v>3.20595532519531</v>
+        <v>6.08216833391328</v>
       </c>
       <c r="G9" s="292" t="n">
         <f aca="false">G7/32</f>
-        <v>3.40625</v>
+        <v>6.375</v>
       </c>
       <c r="H9" s="215"/>
     </row>
@@ -6588,23 +6588,23 @@
       </c>
       <c r="C12" s="291" t="n">
         <f aca="false">ROUNDUP(C4/C11, 0)</f>
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D12" s="291" t="n">
         <f aca="false">ROUNDUP(D4/D11, 0)</f>
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E12" s="291" t="n">
         <f aca="false">ROUNDUP(E4/E11, 0)</f>
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F12" s="291" t="n">
         <f aca="false">ROUNDUP(F4/F11, 0)</f>
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G12" s="291" t="n">
         <f aca="false">ROUNDUP(G4/G11, 0)</f>
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H12" s="215"/>
     </row>
@@ -6671,23 +6671,23 @@
       </c>
       <c r="C15" s="291" t="n">
         <f aca="false">ROUND(C12+C13+C14,0)</f>
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D15" s="291" t="n">
         <f aca="false">ROUND(D12+D13+D14,0)</f>
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E15" s="291" t="n">
         <f aca="false">ROUND(E12+E13+E14,0)</f>
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F15" s="291" t="n">
         <f aca="false">ROUND(F12+F13+F14,0)</f>
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G15" s="291" t="n">
         <f aca="false">ROUND(G12+G13+G14,0)</f>
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H15" s="215"/>
     </row>
@@ -6717,23 +6717,23 @@
       </c>
       <c r="C18" s="303" t="n">
         <f aca="false">ROUND(ROUND(MAX(C8,C9),0)*1.42,0)</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D18" s="303" t="n">
         <f aca="false">ROUND(ROUND(MAX(D8,D9),0)*1.42,0)</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E18" s="303" t="n">
         <f aca="false">ROUND(ROUND(MAX(E8,E9),0)*1.42,0)</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F18" s="303" t="n">
         <f aca="false">ROUND(ROUND(MAX(F8,F9),0)*1.42,0)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G18" s="303" t="n">
         <f aca="false">ROUND(ROUND(MAX(G8,G9),0)*1.42,0)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H18" s="304" t="s">
         <v>428</v>
@@ -6765,23 +6765,23 @@
       </c>
       <c r="C21" s="313" t="n">
         <f aca="false">C15</f>
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D21" s="313" t="n">
         <f aca="false">D15</f>
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E21" s="313" t="n">
         <f aca="false">E15</f>
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F21" s="313" t="n">
         <f aca="false">F15</f>
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G21" s="313" t="n">
         <f aca="false">G15</f>
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H21" s="215"/>
     </row>
@@ -6791,23 +6791,23 @@
       </c>
       <c r="C22" s="313" t="n">
         <f aca="false">C21*2</f>
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="D22" s="313" t="n">
         <f aca="false">D21*2</f>
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="E22" s="313" t="n">
         <f aca="false">E21*2</f>
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F22" s="313" t="n">
         <f aca="false">F21*2</f>
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="G22" s="313" t="n">
         <f aca="false">G21*2</f>
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="H22" s="215" t="s">
         <v>430</v>
@@ -6819,23 +6819,23 @@
       </c>
       <c r="C23" s="313" t="n">
         <f aca="false">C22*8</f>
-        <v>192</v>
+        <v>448</v>
       </c>
       <c r="D23" s="313" t="n">
         <f aca="false">D22*8</f>
-        <v>208</v>
+        <v>464</v>
       </c>
       <c r="E23" s="313" t="n">
         <f aca="false">E22*8</f>
-        <v>224</v>
+        <v>480</v>
       </c>
       <c r="F23" s="313" t="n">
         <f aca="false">F22*8</f>
-        <v>224</v>
+        <v>496</v>
       </c>
       <c r="G23" s="313" t="n">
         <f aca="false">G22*8</f>
-        <v>240</v>
+        <v>528</v>
       </c>
       <c r="H23" s="215" t="s">
         <v>432</v>
@@ -6847,23 +6847,23 @@
       </c>
       <c r="C24" s="313" t="n">
         <f aca="false">C22*8</f>
-        <v>192</v>
+        <v>448</v>
       </c>
       <c r="D24" s="313" t="n">
         <f aca="false">D22*8</f>
-        <v>208</v>
+        <v>464</v>
       </c>
       <c r="E24" s="313" t="n">
         <f aca="false">E22*8</f>
-        <v>224</v>
+        <v>480</v>
       </c>
       <c r="F24" s="313" t="n">
         <f aca="false">F22*8</f>
-        <v>224</v>
+        <v>496</v>
       </c>
       <c r="G24" s="313" t="n">
         <f aca="false">G22*8</f>
-        <v>240</v>
+        <v>528</v>
       </c>
       <c r="H24" s="215" t="s">
         <v>432</v>
@@ -6875,23 +6875,23 @@
       </c>
       <c r="C25" s="313" t="n">
         <f aca="false">C22*4</f>
-        <v>96</v>
+        <v>224</v>
       </c>
       <c r="D25" s="313" t="n">
         <f aca="false">D22*4</f>
-        <v>104</v>
+        <v>232</v>
       </c>
       <c r="E25" s="313" t="n">
         <f aca="false">E22*4</f>
-        <v>112</v>
+        <v>240</v>
       </c>
       <c r="F25" s="313" t="n">
         <f aca="false">F22*4</f>
-        <v>112</v>
+        <v>248</v>
       </c>
       <c r="G25" s="313" t="n">
         <f aca="false">G22*4</f>
-        <v>120</v>
+        <v>264</v>
       </c>
       <c r="H25" s="215" t="s">
         <v>435</v>
@@ -6926,23 +6926,23 @@
       </c>
       <c r="C28" s="313" t="n">
         <f aca="false">IF(C27="No", 0, C21)</f>
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D28" s="313" t="n">
         <f aca="false">IF(C27="No", 0, D21)</f>
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E28" s="313" t="n">
         <f aca="false">IF(C27="No", 0, E21)</f>
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F28" s="313" t="n">
         <f aca="false">IF(C27="No", 0, F21)</f>
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G28" s="313" t="n">
         <f aca="false">IF(C27="No", 0, G21)</f>
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H28" s="267" t="s">
         <v>437</v>
@@ -6954,23 +6954,23 @@
       </c>
       <c r="C29" s="313" t="n">
         <f aca="false">IF(C27="No", 0, C22)</f>
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="D29" s="313" t="n">
         <f aca="false">IF(C27="No", 0, D22)</f>
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="E29" s="313" t="n">
         <f aca="false">IF(C27="No", 0, E22)</f>
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F29" s="313" t="n">
         <f aca="false">IF(C27="No", 0, F22)</f>
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="G29" s="313" t="n">
         <f aca="false">IF(C27="No", 0, G22)</f>
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="H29" s="267"/>
     </row>
@@ -6980,23 +6980,23 @@
       </c>
       <c r="C30" s="313" t="n">
         <f aca="false">C29*8</f>
-        <v>192</v>
+        <v>448</v>
       </c>
       <c r="D30" s="313" t="n">
         <f aca="false">D29*8</f>
-        <v>208</v>
+        <v>464</v>
       </c>
       <c r="E30" s="313" t="n">
         <f aca="false">E29*8</f>
-        <v>224</v>
+        <v>480</v>
       </c>
       <c r="F30" s="313" t="n">
         <f aca="false">F29*8</f>
-        <v>224</v>
+        <v>496</v>
       </c>
       <c r="G30" s="313" t="n">
         <f aca="false">G29*8</f>
-        <v>240</v>
+        <v>528</v>
       </c>
       <c r="H30" s="267"/>
     </row>
@@ -7006,23 +7006,23 @@
       </c>
       <c r="C31" s="313" t="n">
         <f aca="false">C29*8</f>
-        <v>192</v>
+        <v>448</v>
       </c>
       <c r="D31" s="313" t="n">
         <f aca="false">D29*8</f>
-        <v>208</v>
+        <v>464</v>
       </c>
       <c r="E31" s="313" t="n">
         <f aca="false">E29*8</f>
-        <v>224</v>
+        <v>480</v>
       </c>
       <c r="F31" s="313" t="n">
         <f aca="false">F29*8</f>
-        <v>224</v>
+        <v>496</v>
       </c>
       <c r="G31" s="313" t="n">
         <f aca="false">G29*8</f>
-        <v>240</v>
+        <v>528</v>
       </c>
       <c r="H31" s="267"/>
     </row>
@@ -7032,23 +7032,23 @@
       </c>
       <c r="C32" s="313" t="n">
         <f aca="false">C29*4</f>
-        <v>96</v>
+        <v>224</v>
       </c>
       <c r="D32" s="313" t="n">
         <f aca="false">D29*4</f>
-        <v>104</v>
+        <v>232</v>
       </c>
       <c r="E32" s="313" t="n">
         <f aca="false">E29*4</f>
-        <v>112</v>
+        <v>240</v>
       </c>
       <c r="F32" s="313" t="n">
         <f aca="false">F29*4</f>
-        <v>112</v>
+        <v>248</v>
       </c>
       <c r="G32" s="313" t="n">
         <f aca="false">G29*4</f>
-        <v>120</v>
+        <v>264</v>
       </c>
       <c r="H32" s="267"/>
     </row>
@@ -7072,23 +7072,23 @@
       </c>
       <c r="C35" s="313" t="n">
         <f aca="false">CEILING('Data size'!D30,100)</f>
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="D35" s="313" t="n">
         <f aca="false">CEILING('Data size'!H30,100)</f>
-        <v>100</v>
+        <v>2300</v>
       </c>
       <c r="E35" s="313" t="n">
         <f aca="false">CEILING('Data size'!L30,100)</f>
-        <v>100</v>
+        <v>2500</v>
       </c>
       <c r="F35" s="313" t="n">
         <f aca="false">CEILING('Data size'!P30,100)</f>
-        <v>100</v>
+        <v>2800</v>
       </c>
       <c r="G35" s="313" t="n">
         <f aca="false">CEILING('Data size'!T30,100)</f>
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="H35" s="215" t="s">
         <v>442</v>
@@ -7100,23 +7100,23 @@
       </c>
       <c r="C36" s="313" t="n">
         <f aca="false">CEILING('DMS size'!D21,100)</f>
-        <v>100</v>
+        <v>5900</v>
       </c>
       <c r="D36" s="313" t="n">
         <f aca="false">CEILING('DMS size'!H21,100)</f>
-        <v>100</v>
+        <v>6500</v>
       </c>
       <c r="E36" s="313" t="n">
         <f aca="false">CEILING('DMS size'!L21,100)</f>
-        <v>100</v>
+        <v>7200</v>
       </c>
       <c r="F36" s="313" t="n">
         <f aca="false">CEILING('DMS size'!P21,100)</f>
-        <v>100</v>
+        <v>7900</v>
       </c>
       <c r="G36" s="313" t="n">
         <f aca="false">CEILING('DMS size'!T21,100)</f>
-        <v>100</v>
+        <v>8700</v>
       </c>
       <c r="H36" s="215" t="s">
         <v>442</v>
@@ -7180,23 +7180,23 @@
       </c>
       <c r="C3" s="317" t="n">
         <f aca="false">'Customer Volumes'!D3</f>
-        <v>5000</v>
+        <v>15500</v>
       </c>
       <c r="D3" s="317" t="n">
         <f aca="false">'Customer Volumes'!E3</f>
-        <v>5500</v>
+        <v>16275</v>
       </c>
       <c r="E3" s="317" t="n">
         <f aca="false">'Customer Volumes'!F3</f>
-        <v>6050</v>
+        <v>17088.75</v>
       </c>
       <c r="F3" s="317" t="n">
         <f aca="false">'Customer Volumes'!G3</f>
-        <v>6655</v>
+        <v>17943.1875</v>
       </c>
       <c r="G3" s="317" t="n">
         <f aca="false">'Customer Volumes'!H3</f>
-        <v>7320.5</v>
+        <v>18840.346875</v>
       </c>
     </row>
     <row r="4" s="80" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7205,23 +7205,23 @@
       </c>
       <c r="C4" s="317" t="n">
         <f aca="false">'Customer Volumes'!D4</f>
-        <v>1500</v>
+        <v>4650</v>
       </c>
       <c r="D4" s="317" t="n">
         <f aca="false">'Customer Volumes'!E4</f>
-        <v>1650</v>
+        <v>4882.5</v>
       </c>
       <c r="E4" s="317" t="n">
         <f aca="false">'Customer Volumes'!F4</f>
-        <v>1815</v>
+        <v>5126.625</v>
       </c>
       <c r="F4" s="317" t="n">
         <f aca="false">'Customer Volumes'!G4</f>
-        <v>1996.5</v>
+        <v>5382.95625</v>
       </c>
       <c r="G4" s="317" t="n">
         <f aca="false">'Customer Volumes'!H4</f>
-        <v>2196.15</v>
+        <v>5652.1040625</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7393,23 +7393,23 @@
       </c>
       <c r="C14" s="322" t="n">
         <f aca="false">C3*(1-C13)*C12</f>
-        <v>25000</v>
+        <v>77500.0000000001</v>
       </c>
       <c r="D14" s="322" t="n">
         <f aca="false">D3*(1-D13)*D12</f>
-        <v>27500</v>
+        <v>81375.0000000001</v>
       </c>
       <c r="E14" s="322" t="n">
         <f aca="false">E3*(1-E13)*E12</f>
-        <v>30250</v>
+        <v>85443.7500000001</v>
       </c>
       <c r="F14" s="322" t="n">
         <f aca="false">F3*(1-F13)*F12</f>
-        <v>33275</v>
+        <v>89715.9375000001</v>
       </c>
       <c r="G14" s="322" t="n">
         <f aca="false">G3*(1-G13)*G12</f>
-        <v>36602.5</v>
+        <v>94201.7343750001</v>
       </c>
       <c r="H14" s="320" t="s">
         <v>215</v>
@@ -7421,23 +7421,23 @@
       </c>
       <c r="C15" s="319" t="n">
         <f aca="false">C4*C8+C14</f>
-        <v>100000</v>
+        <v>310000</v>
       </c>
       <c r="D15" s="319" t="n">
         <f aca="false">D4*D8+D14</f>
-        <v>110000</v>
+        <v>325500</v>
       </c>
       <c r="E15" s="319" t="n">
         <f aca="false">E4*E8+E14</f>
-        <v>121000</v>
+        <v>341775</v>
       </c>
       <c r="F15" s="319" t="n">
         <f aca="false">F4*F8+F14</f>
-        <v>133100</v>
+        <v>358863.75</v>
       </c>
       <c r="G15" s="319" t="n">
         <f aca="false">G4*G8+G14</f>
-        <v>146410</v>
+        <v>376806.9375</v>
       </c>
       <c r="H15" s="320" t="s">
         <v>215</v>
@@ -7449,23 +7449,23 @@
       </c>
       <c r="C16" s="323" t="n">
         <f aca="false">C15*8/C11</f>
-        <v>72727.2727272728</v>
+        <v>225454.545454546</v>
       </c>
       <c r="D16" s="323" t="n">
         <f aca="false">D15*8/D11</f>
-        <v>80000</v>
+        <v>236727.272727273</v>
       </c>
       <c r="E16" s="323" t="n">
         <f aca="false">E15*8/E11</f>
-        <v>88000</v>
+        <v>248563.636363636</v>
       </c>
       <c r="F16" s="323" t="n">
         <f aca="false">F15*8/F11</f>
-        <v>96800</v>
+        <v>260991.818181818</v>
       </c>
       <c r="G16" s="323" t="n">
         <f aca="false">G15*8/G11</f>
-        <v>106480</v>
+        <v>274041.409090909</v>
       </c>
       <c r="H16" s="320" t="s">
         <v>455</v>
@@ -7629,23 +7629,23 @@
       </c>
       <c r="C24" s="322" t="n">
         <f aca="false">C22*(1-C23)*C3</f>
-        <v>5000.00000000001</v>
+        <v>15500</v>
       </c>
       <c r="D24" s="322" t="n">
         <f aca="false">D22*(1-D23)*D3</f>
-        <v>5500.00000000001</v>
+        <v>16275</v>
       </c>
       <c r="E24" s="322" t="n">
         <f aca="false">E22*(1-E23)*E3</f>
-        <v>6050.00000000001</v>
+        <v>17088.75</v>
       </c>
       <c r="F24" s="322" t="n">
         <f aca="false">F22*(1-F23)*F3</f>
-        <v>6655.00000000001</v>
+        <v>17943.1875</v>
       </c>
       <c r="G24" s="322" t="n">
         <f aca="false">G22*(1-G23)*G3</f>
-        <v>7320.50000000001</v>
+        <v>18840.346875</v>
       </c>
       <c r="H24" s="320" t="s">
         <v>215</v>
@@ -7657,23 +7657,23 @@
       </c>
       <c r="C25" s="319" t="n">
         <f aca="false">C4*C18+C24</f>
-        <v>3005000</v>
+        <v>9315500</v>
       </c>
       <c r="D25" s="319" t="n">
         <f aca="false">D4*D18+D24</f>
-        <v>3305500</v>
+        <v>9781275</v>
       </c>
       <c r="E25" s="319" t="n">
         <f aca="false">E4*E18+E24</f>
-        <v>3636050</v>
+        <v>10270338.75</v>
       </c>
       <c r="F25" s="319" t="n">
         <f aca="false">F4*F18+F24</f>
-        <v>3999655</v>
+        <v>10783855.6875</v>
       </c>
       <c r="G25" s="319" t="n">
         <f aca="false">G4*G18+G24</f>
-        <v>4399620.5</v>
+        <v>11323048.471875</v>
       </c>
       <c r="H25" s="320" t="s">
         <v>215</v>
@@ -7685,23 +7685,23 @@
       </c>
       <c r="C26" s="323" t="n">
         <f aca="false">C25*8/C21</f>
-        <v>1265263.15789474</v>
+        <v>3922315.78947368</v>
       </c>
       <c r="D26" s="323" t="n">
         <f aca="false">D25*8/D21</f>
-        <v>1391789.47368421</v>
+        <v>4118431.57894737</v>
       </c>
       <c r="E26" s="323" t="n">
         <f aca="false">E25*8/E21</f>
-        <v>1530968.42105263</v>
+        <v>4324353.15789474</v>
       </c>
       <c r="F26" s="323" t="n">
         <f aca="false">F25*8/F21</f>
-        <v>1684065.2631579</v>
+        <v>4540570.81578947</v>
       </c>
       <c r="G26" s="323" t="n">
         <f aca="false">G25*8/G21</f>
-        <v>1852471.78947368</v>
+        <v>4767599.35657895</v>
       </c>
       <c r="H26" s="320" t="s">
         <v>455</v>
@@ -7724,23 +7724,23 @@
       </c>
       <c r="C28" s="325" t="n">
         <f aca="false">C16+C26</f>
-        <v>1337990.43062201</v>
+        <v>4147770.33492823</v>
       </c>
       <c r="D28" s="325" t="n">
         <f aca="false">D16+D26</f>
-        <v>1471789.47368421</v>
+        <v>4355158.85167464</v>
       </c>
       <c r="E28" s="325" t="n">
         <f aca="false">E16+E26</f>
-        <v>1618968.42105263</v>
+        <v>4572916.79425837</v>
       </c>
       <c r="F28" s="325" t="n">
         <f aca="false">F16+F26</f>
-        <v>1780865.2631579</v>
+        <v>4801562.63397129</v>
       </c>
       <c r="G28" s="325" t="n">
         <f aca="false">G16+G26</f>
-        <v>1958951.78947368</v>
+        <v>5041640.76566986</v>
       </c>
       <c r="H28" s="320" t="s">
         <v>455</v>
@@ -7750,23 +7750,23 @@
       <c r="B29" s="324"/>
       <c r="C29" s="325" t="n">
         <f aca="false">C28/1024</f>
-        <v>1306.63127990431</v>
+        <v>4050.55696770335</v>
       </c>
       <c r="D29" s="325" t="n">
         <f aca="false">D28/1024</f>
-        <v>1437.29440789474</v>
+        <v>4253.08481608852</v>
       </c>
       <c r="E29" s="325" t="n">
         <f aca="false">E28/1024</f>
-        <v>1581.02384868421</v>
+        <v>4465.73905689294</v>
       </c>
       <c r="F29" s="325" t="n">
         <f aca="false">F28/1024</f>
-        <v>1739.12623355263</v>
+        <v>4689.02600973759</v>
       </c>
       <c r="G29" s="325" t="n">
         <f aca="false">G28/1024</f>
-        <v>1913.0388569079</v>
+        <v>4923.47731022447</v>
       </c>
       <c r="H29" s="320" t="s">
         <v>457</v>
@@ -7776,23 +7776,23 @@
       <c r="B30" s="324"/>
       <c r="C30" s="325" t="n">
         <f aca="false">C29/1024</f>
-        <v>1.27600710928155</v>
+        <v>3.9556220387728</v>
       </c>
       <c r="D30" s="325" t="n">
         <f aca="false">D29/1024</f>
-        <v>1.4036078202097</v>
+        <v>4.15340314071144</v>
       </c>
       <c r="E30" s="325" t="n">
         <f aca="false">E29/1024</f>
-        <v>1.54396860223067</v>
+        <v>4.36107329774702</v>
       </c>
       <c r="F30" s="325" t="n">
         <f aca="false">F29/1024</f>
-        <v>1.69836546245374</v>
+        <v>4.57912696263437</v>
       </c>
       <c r="G30" s="325" t="n">
         <f aca="false">G29/1024</f>
-        <v>1.86820200869912</v>
+        <v>4.80808331076608</v>
       </c>
       <c r="H30" s="320" t="s">
         <v>458</v>
@@ -10390,26 +10390,26 @@
         <v>78</v>
       </c>
       <c r="D3" s="48" t="n">
-        <v>5000</v>
+        <v>15500</v>
       </c>
       <c r="E3" s="49" t="n">
         <f aca="false">D3*(1+I3)</f>
-        <v>5500</v>
+        <v>16275</v>
       </c>
       <c r="F3" s="49" t="n">
         <f aca="false">E3*(1+$I$3)</f>
-        <v>6050</v>
+        <v>17088.75</v>
       </c>
       <c r="G3" s="49" t="n">
         <f aca="false">F3*(1+$I$3)</f>
-        <v>6655</v>
+        <v>17943.1875</v>
       </c>
       <c r="H3" s="49" t="n">
         <f aca="false">G3*(1+$I$3)</f>
-        <v>7320.5</v>
+        <v>18840.346875</v>
       </c>
       <c r="I3" s="50" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J3" s="51" t="s">
         <v>79</v>
@@ -10424,26 +10424,26 @@
         <v>80</v>
       </c>
       <c r="D4" s="48" t="n">
-        <v>1500</v>
+        <v>4650</v>
       </c>
       <c r="E4" s="53" t="n">
         <f aca="false">E3*0.3</f>
-        <v>1650</v>
+        <v>4882.5</v>
       </c>
       <c r="F4" s="53" t="n">
         <f aca="false">F3*0.3</f>
-        <v>1815</v>
+        <v>5126.625</v>
       </c>
       <c r="G4" s="53" t="n">
         <f aca="false">G3*0.3</f>
-        <v>1996.5</v>
+        <v>5382.95625</v>
       </c>
       <c r="H4" s="53" t="n">
         <f aca="false">H3*0.3</f>
-        <v>2196.15</v>
+        <v>5652.1040625</v>
       </c>
       <c r="I4" s="50" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J4" s="51" t="s">
         <v>79</v>
@@ -10458,26 +10458,26 @@
         <v>81</v>
       </c>
       <c r="D5" s="55" t="n">
-        <v>22500</v>
+        <v>25786541</v>
       </c>
       <c r="E5" s="56" t="n">
         <f aca="false">D5*(1+I5)</f>
-        <v>25875</v>
+        <v>28365195.1</v>
       </c>
       <c r="F5" s="56" t="n">
         <f aca="false">E5*(1+I5)</f>
-        <v>29756.25</v>
+        <v>31201714.61</v>
       </c>
       <c r="G5" s="56" t="n">
         <f aca="false">F5*(1+I5)</f>
-        <v>34219.6875</v>
+        <v>34321886.071</v>
       </c>
       <c r="H5" s="56" t="n">
         <f aca="false">G5*(1+I5)</f>
-        <v>39352.640625</v>
+        <v>37754074.6781</v>
       </c>
       <c r="I5" s="50" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="J5" s="51" t="s">
         <v>79</v>
@@ -10522,26 +10522,26 @@
         <v>84</v>
       </c>
       <c r="D7" s="48" t="n">
-        <v>240000</v>
+        <v>10700000</v>
       </c>
       <c r="E7" s="53" t="n">
         <f aca="false">D7*(1+I7)</f>
-        <v>252000</v>
+        <v>11770000</v>
       </c>
       <c r="F7" s="53" t="n">
         <f aca="false">E7*(1+I7)</f>
-        <v>264600</v>
+        <v>12947000</v>
       </c>
       <c r="G7" s="53" t="n">
         <f aca="false">F7*(1+I7)</f>
-        <v>277830</v>
+        <v>14241700</v>
       </c>
       <c r="H7" s="53" t="n">
         <f aca="false">G7*(1+I7)</f>
-        <v>291721.5</v>
+        <v>15665870</v>
       </c>
       <c r="I7" s="50" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J7" s="51" t="s">
         <v>79</v>
@@ -10586,26 +10586,26 @@
         <v>87</v>
       </c>
       <c r="D9" s="58" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="E9" s="59" t="n">
         <f aca="false">D9*(1+I9)</f>
-        <v>18000</v>
+        <v>21000</v>
       </c>
       <c r="F9" s="59" t="n">
         <f aca="false">E9*(1+I9)</f>
-        <v>21600</v>
+        <v>22050</v>
       </c>
       <c r="G9" s="59" t="n">
         <f aca="false">F9*(1+I9)</f>
-        <v>25920</v>
+        <v>23152.5</v>
       </c>
       <c r="H9" s="59" t="n">
         <f aca="false">G9*(1+I9)</f>
-        <v>31104</v>
+        <v>24310.125</v>
       </c>
       <c r="I9" s="50" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="J9" s="51" t="s">
         <v>79</v>
@@ -10710,26 +10710,26 @@
         <v>94</v>
       </c>
       <c r="D13" s="60" t="n">
-        <v>750</v>
+        <v>4050</v>
       </c>
       <c r="E13" s="61" t="n">
         <f aca="false">D13*(1+I13)</f>
-        <v>825</v>
+        <v>4252.5</v>
       </c>
       <c r="F13" s="61" t="n">
         <f aca="false">E13*(1+I13)</f>
-        <v>907.5</v>
+        <v>4465.125</v>
       </c>
       <c r="G13" s="61" t="n">
         <f aca="false">F13*(1+I13)</f>
-        <v>998.25</v>
+        <v>4688.38125</v>
       </c>
       <c r="H13" s="61" t="n">
         <f aca="false">G13*(1+I13)</f>
-        <v>1098.075</v>
+        <v>4922.8003125</v>
       </c>
       <c r="I13" s="50" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J13" s="51" t="s">
         <v>79</v>
@@ -10960,23 +10960,23 @@
       </c>
       <c r="D21" s="60" t="n">
         <f aca="false">0.05*(D7+D9)</f>
-        <v>12750</v>
+        <v>536000</v>
       </c>
       <c r="E21" s="61" t="n">
         <f aca="false">0.05*(E7+E9)</f>
-        <v>13500</v>
+        <v>589550</v>
       </c>
       <c r="F21" s="61" t="n">
         <f aca="false">0.05*(F7+F9)</f>
-        <v>14310</v>
+        <v>648452.5</v>
       </c>
       <c r="G21" s="61" t="n">
         <f aca="false">0.05*(G7+G9)</f>
-        <v>15187.5</v>
+        <v>713242.625</v>
       </c>
       <c r="H21" s="61" t="n">
         <f aca="false">0.05*(H7+H9)</f>
-        <v>16141.275</v>
+        <v>784509.00625</v>
       </c>
       <c r="I21" s="61"/>
       <c r="J21" s="63" t="s">
@@ -10995,23 +10995,23 @@
       </c>
       <c r="D22" s="60" t="n">
         <f aca="false">0.1*(D5+D7+D9)</f>
-        <v>27750</v>
+        <v>3650654.1</v>
       </c>
       <c r="E22" s="61" t="n">
         <f aca="false">0.1*(E5+E7+E9)</f>
-        <v>29587.5</v>
+        <v>4015619.51</v>
       </c>
       <c r="F22" s="61" t="n">
         <f aca="false">0.1*(F5+F7+F9)</f>
-        <v>31595.625</v>
+        <v>4417076.461</v>
       </c>
       <c r="G22" s="61" t="n">
         <f aca="false">0.1*(G5+G7+G9)</f>
-        <v>33796.96875</v>
+        <v>4858673.8571</v>
       </c>
       <c r="H22" s="61" t="n">
         <f aca="false">0.1*(H5+H7+H9)</f>
-        <v>36217.8140625</v>
+        <v>5344425.48031</v>
       </c>
       <c r="I22" s="61"/>
       <c r="J22" s="63" t="s">
@@ -11030,23 +11030,23 @@
       </c>
       <c r="D23" s="60" t="n">
         <f aca="false">0.1*(D5+D7+D9)</f>
-        <v>27750</v>
+        <v>3650654.1</v>
       </c>
       <c r="E23" s="61" t="n">
         <f aca="false">0.1*(E5+E7+E9)</f>
-        <v>29587.5</v>
+        <v>4015619.51</v>
       </c>
       <c r="F23" s="61" t="n">
         <f aca="false">0.1*(F5+F7+F9)</f>
-        <v>31595.625</v>
+        <v>4417076.461</v>
       </c>
       <c r="G23" s="61" t="n">
         <f aca="false">0.1*(G5+G7+G9)</f>
-        <v>33796.96875</v>
+        <v>4858673.8571</v>
       </c>
       <c r="H23" s="61" t="n">
         <f aca="false">0.1*(H5+H7+H9)</f>
-        <v>36217.8140625</v>
+        <v>5344425.48031</v>
       </c>
       <c r="I23" s="61"/>
       <c r="J23" s="63" t="s">
@@ -11065,23 +11065,23 @@
       </c>
       <c r="D24" s="60" t="n">
         <f aca="false">D7+D9</f>
-        <v>255000</v>
+        <v>10720000</v>
       </c>
       <c r="E24" s="61" t="n">
         <f aca="false">E7+E9</f>
-        <v>270000</v>
+        <v>11791000</v>
       </c>
       <c r="F24" s="61" t="n">
         <f aca="false">F7+F9</f>
-        <v>286200</v>
+        <v>12969050</v>
       </c>
       <c r="G24" s="61" t="n">
         <f aca="false">G7+G9</f>
-        <v>303750</v>
+        <v>14264852.5</v>
       </c>
       <c r="H24" s="61" t="n">
         <f aca="false">H7+H9</f>
-        <v>322825.5</v>
+        <v>15690180.125</v>
       </c>
       <c r="I24" s="61"/>
       <c r="J24" s="63" t="s">
@@ -11150,23 +11150,23 @@
       </c>
       <c r="D27" s="60" t="n">
         <f aca="false">0.01*(D5+D7+D9)</f>
-        <v>2775</v>
+        <v>365065.41</v>
       </c>
       <c r="E27" s="61" t="n">
         <f aca="false">0.01*(E5+E7+E9)</f>
-        <v>2958.75</v>
+        <v>401561.951</v>
       </c>
       <c r="F27" s="61" t="n">
         <f aca="false">0.01*(F5+F7+F9)</f>
-        <v>3159.5625</v>
+        <v>441707.6461</v>
       </c>
       <c r="G27" s="61" t="n">
         <f aca="false">0.01*(G5+G7+G9)</f>
-        <v>3379.696875</v>
+        <v>485867.38571</v>
       </c>
       <c r="H27" s="61" t="n">
         <f aca="false">0.01*(H5+H7+H9)</f>
-        <v>3621.78140625</v>
+        <v>534442.548031</v>
       </c>
       <c r="I27" s="61"/>
       <c r="J27" s="63" t="s">
@@ -11690,27 +11690,27 @@
       </c>
       <c r="D3" s="51" t="n">
         <f aca="false">'Customer Volumes'!D3</f>
-        <v>5000</v>
+        <v>15500</v>
       </c>
       <c r="E3" s="51" t="n">
         <f aca="false">'Customer Volumes'!E3</f>
-        <v>5500</v>
+        <v>16275</v>
       </c>
       <c r="F3" s="51" t="n">
         <f aca="false">'Customer Volumes'!F3</f>
-        <v>6050</v>
+        <v>17088.75</v>
       </c>
       <c r="G3" s="51" t="n">
         <f aca="false">'Customer Volumes'!G3</f>
-        <v>6655</v>
+        <v>17943.1875</v>
       </c>
       <c r="H3" s="51" t="n">
         <f aca="false">'Customer Volumes'!H3</f>
-        <v>7320.5</v>
+        <v>18840.346875</v>
       </c>
       <c r="I3" s="82" t="n">
         <f aca="false">'Customer Volumes'!I3</f>
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J3" s="51" t="s">
         <v>79</v>
@@ -11726,27 +11726,27 @@
       </c>
       <c r="D4" s="51" t="n">
         <f aca="false">'Customer Volumes'!D4</f>
-        <v>1500</v>
+        <v>4650</v>
       </c>
       <c r="E4" s="51" t="n">
         <f aca="false">'Customer Volumes'!E4</f>
-        <v>1650</v>
+        <v>4882.5</v>
       </c>
       <c r="F4" s="51" t="n">
         <f aca="false">'Customer Volumes'!F4</f>
-        <v>1815</v>
+        <v>5126.625</v>
       </c>
       <c r="G4" s="51" t="n">
         <f aca="false">'Customer Volumes'!G4</f>
-        <v>1996.5</v>
+        <v>5382.95625</v>
       </c>
       <c r="H4" s="51" t="n">
         <f aca="false">'Customer Volumes'!H4</f>
-        <v>2196.15</v>
+        <v>5652.1040625</v>
       </c>
       <c r="I4" s="82" t="n">
         <f aca="false">'Customer Volumes'!I4</f>
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J4" s="51" t="s">
         <v>79</v>
@@ -11762,27 +11762,27 @@
       </c>
       <c r="D5" s="51" t="n">
         <f aca="false">'Customer Volumes'!D5/200/8</f>
-        <v>14.0625</v>
+        <v>16116.588125</v>
       </c>
       <c r="E5" s="51" t="n">
         <f aca="false">'Customer Volumes'!E5/200/8</f>
-        <v>16.171875</v>
+        <v>17728.2469375</v>
       </c>
       <c r="F5" s="51" t="n">
         <f aca="false">'Customer Volumes'!F5/200/8</f>
-        <v>18.59765625</v>
+        <v>19501.07163125</v>
       </c>
       <c r="G5" s="51" t="n">
         <f aca="false">'Customer Volumes'!G5/200/8</f>
-        <v>21.3873046875</v>
+        <v>21451.178794375</v>
       </c>
       <c r="H5" s="51" t="n">
         <f aca="false">'Customer Volumes'!H5/200/8</f>
-        <v>24.595400390625</v>
+        <v>23596.2966738125</v>
       </c>
       <c r="I5" s="82" t="n">
         <f aca="false">'Customer Volumes'!I5</f>
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="J5" s="51" t="s">
         <v>79</v>
@@ -11828,23 +11828,23 @@
       </c>
       <c r="D7" s="51" t="n">
         <f aca="false">'Customer Volumes'!D7/200/8</f>
-        <v>150</v>
+        <v>6687.5</v>
       </c>
       <c r="E7" s="51" t="n">
         <f aca="false">'Customer Volumes'!E7/200/8</f>
-        <v>157.5</v>
+        <v>7356.25</v>
       </c>
       <c r="F7" s="51" t="n">
         <f aca="false">'Customer Volumes'!F7/200/8</f>
-        <v>165.375</v>
+        <v>8091.875</v>
       </c>
       <c r="G7" s="51" t="n">
         <f aca="false">'Customer Volumes'!G7/200/8</f>
-        <v>173.64375</v>
+        <v>8901.0625</v>
       </c>
       <c r="H7" s="51" t="n">
         <f aca="false">'Customer Volumes'!H7/200/8</f>
-        <v>182.3259375</v>
+        <v>9791.16875</v>
       </c>
       <c r="I7" s="85"/>
       <c r="J7" s="51" t="s">
@@ -11891,23 +11891,23 @@
       </c>
       <c r="D9" s="51" t="n">
         <f aca="false">'Customer Volumes'!D9/200/8</f>
-        <v>9.375</v>
+        <v>12.5</v>
       </c>
       <c r="E9" s="51" t="n">
         <f aca="false">'Customer Volumes'!E9/200/8</f>
-        <v>11.25</v>
+        <v>13.125</v>
       </c>
       <c r="F9" s="51" t="n">
         <f aca="false">'Customer Volumes'!F9/200/8</f>
-        <v>13.5</v>
+        <v>13.78125</v>
       </c>
       <c r="G9" s="51" t="n">
         <f aca="false">'Customer Volumes'!G9/200/8</f>
-        <v>16.2</v>
+        <v>14.4703125</v>
       </c>
       <c r="H9" s="51" t="n">
         <f aca="false">'Customer Volumes'!H9/200/8</f>
-        <v>19.44</v>
+        <v>15.193828125</v>
       </c>
       <c r="I9" s="85" t="n">
         <v>0.15</v>
@@ -12140,23 +12140,23 @@
       </c>
       <c r="D17" s="63" t="n">
         <f aca="false">(D5+D7+D9)*2</f>
-        <v>346.875</v>
+        <v>45633.17625</v>
       </c>
       <c r="E17" s="63" t="n">
         <f aca="false">(E5+E7+E9)*2</f>
-        <v>369.84375</v>
+        <v>50195.243875</v>
       </c>
       <c r="F17" s="63" t="n">
         <f aca="false">(F5+F7+F9)*2</f>
-        <v>394.9453125</v>
+        <v>55213.4557625</v>
       </c>
       <c r="G17" s="63" t="n">
         <f aca="false">(G5+G7+G9)*2</f>
-        <v>422.462109375</v>
+        <v>60733.42321375</v>
       </c>
       <c r="H17" s="63" t="n">
         <f aca="false">(H5+H7+H9)*2</f>
-        <v>452.72267578125</v>
+        <v>66805.318503875</v>
       </c>
       <c r="I17" s="63"/>
       <c r="J17" s="63" t="s">
@@ -12205,23 +12205,23 @@
       </c>
       <c r="D19" s="63" t="n">
         <f aca="false">D4</f>
-        <v>1500</v>
+        <v>4650</v>
       </c>
       <c r="E19" s="63" t="n">
         <f aca="false">E4</f>
-        <v>1650</v>
+        <v>4882.5</v>
       </c>
       <c r="F19" s="63" t="n">
         <f aca="false">F4</f>
-        <v>1815</v>
+        <v>5126.625</v>
       </c>
       <c r="G19" s="63" t="n">
         <f aca="false">G4</f>
-        <v>1996.5</v>
+        <v>5382.95625</v>
       </c>
       <c r="H19" s="63" t="n">
         <f aca="false">H4</f>
-        <v>2196.15</v>
+        <v>5652.1040625</v>
       </c>
       <c r="I19" s="63"/>
       <c r="J19" s="63" t="s">
@@ -12270,23 +12270,23 @@
       </c>
       <c r="D21" s="63" t="n">
         <f aca="false">D5/10</f>
-        <v>1.40625</v>
+        <v>1611.6588125</v>
       </c>
       <c r="E21" s="63" t="n">
         <f aca="false">E5/10</f>
-        <v>1.6171875</v>
+        <v>1772.82469375</v>
       </c>
       <c r="F21" s="63" t="n">
         <f aca="false">F5/10</f>
-        <v>1.859765625</v>
+        <v>1950.107163125</v>
       </c>
       <c r="G21" s="63" t="n">
         <f aca="false">G5/10</f>
-        <v>2.13873046875</v>
+        <v>2145.1178794375</v>
       </c>
       <c r="H21" s="63" t="n">
         <f aca="false">H5/10</f>
-        <v>2.4595400390625</v>
+        <v>2359.62966738125</v>
       </c>
       <c r="I21" s="63"/>
       <c r="J21" s="63" t="s">
@@ -12305,23 +12305,23 @@
       </c>
       <c r="D22" s="63" t="n">
         <f aca="false">0.1*(D7+D9+D5)</f>
-        <v>17.34375</v>
+        <v>2281.6588125</v>
       </c>
       <c r="E22" s="63" t="n">
         <f aca="false">0.1*(E7+E9+E5)</f>
-        <v>18.4921875</v>
+        <v>2509.76219375</v>
       </c>
       <c r="F22" s="63" t="n">
         <f aca="false">0.1*(F7+F9+F5)</f>
-        <v>19.747265625</v>
+        <v>2760.672788125</v>
       </c>
       <c r="G22" s="63" t="n">
         <f aca="false">0.1*(G7+G9+G5)</f>
-        <v>21.12310546875</v>
+        <v>3036.6711606875</v>
       </c>
       <c r="H22" s="63" t="n">
         <f aca="false">0.1*(H7+H9+H5)</f>
-        <v>22.6361337890625</v>
+        <v>3340.26592519375</v>
       </c>
       <c r="I22" s="63"/>
       <c r="J22" s="63" t="s">
@@ -12340,23 +12340,23 @@
       </c>
       <c r="D23" s="63" t="n">
         <f aca="false">0.1*(D7+D9+D5)</f>
-        <v>17.34375</v>
+        <v>2281.6588125</v>
       </c>
       <c r="E23" s="63" t="n">
         <f aca="false">0.1*(E7+E9+E5)</f>
-        <v>18.4921875</v>
+        <v>2509.76219375</v>
       </c>
       <c r="F23" s="63" t="n">
         <f aca="false">0.1*(F7+F9+F5)</f>
-        <v>19.747265625</v>
+        <v>2760.672788125</v>
       </c>
       <c r="G23" s="63" t="n">
         <f aca="false">0.1*(G7+G9+G5)</f>
-        <v>21.12310546875</v>
+        <v>3036.6711606875</v>
       </c>
       <c r="H23" s="63" t="n">
         <f aca="false">0.1*(H7+H9+H5)</f>
-        <v>22.6361337890625</v>
+        <v>3340.26592519375</v>
       </c>
       <c r="I23" s="63"/>
       <c r="J23" s="63" t="s">
@@ -12375,23 +12375,23 @@
       </c>
       <c r="D24" s="63" t="n">
         <f aca="false">D7+D9</f>
-        <v>159.375</v>
+        <v>6700</v>
       </c>
       <c r="E24" s="63" t="n">
         <f aca="false">E7+E9</f>
-        <v>168.75</v>
+        <v>7369.375</v>
       </c>
       <c r="F24" s="63" t="n">
         <f aca="false">F7+F9</f>
-        <v>178.875</v>
+        <v>8105.65625</v>
       </c>
       <c r="G24" s="63" t="n">
         <f aca="false">G7+G9</f>
-        <v>189.84375</v>
+        <v>8915.5328125</v>
       </c>
       <c r="H24" s="63" t="n">
         <f aca="false">H7+H9</f>
-        <v>201.7659375</v>
+        <v>9806.36257812501</v>
       </c>
       <c r="I24" s="63"/>
       <c r="J24" s="63" t="s">
@@ -12440,23 +12440,23 @@
       </c>
       <c r="D26" s="63" t="n">
         <f aca="false">D21+D22+D24</f>
-        <v>178.125</v>
+        <v>10593.317625</v>
       </c>
       <c r="E26" s="63" t="n">
         <f aca="false">E21+E22+E24</f>
-        <v>188.859375</v>
+        <v>11651.9618875</v>
       </c>
       <c r="F26" s="63" t="n">
         <f aca="false">F21+F22+F24</f>
-        <v>200.48203125</v>
+        <v>12816.43620125</v>
       </c>
       <c r="G26" s="63" t="n">
         <f aca="false">G21+G22+G24</f>
-        <v>213.1055859375</v>
+        <v>14097.321852625</v>
       </c>
       <c r="H26" s="63" t="n">
         <f aca="false">H21+H22+H24</f>
-        <v>226.861611328125</v>
+        <v>15506.2581707</v>
       </c>
       <c r="I26" s="63"/>
       <c r="J26" s="63" t="s">
@@ -12475,23 +12475,23 @@
       </c>
       <c r="D27" s="63" t="n">
         <f aca="false">0.1*(D7+D9+D5)</f>
-        <v>17.34375</v>
+        <v>2281.6588125</v>
       </c>
       <c r="E27" s="63" t="n">
         <f aca="false">0.1*(E7+E9+E5)</f>
-        <v>18.4921875</v>
+        <v>2509.76219375</v>
       </c>
       <c r="F27" s="63" t="n">
         <f aca="false">0.1*(F7+F9+F5)</f>
-        <v>19.747265625</v>
+        <v>2760.672788125</v>
       </c>
       <c r="G27" s="63" t="n">
         <f aca="false">0.1*(G7+G9+G5)</f>
-        <v>21.12310546875</v>
+        <v>3036.6711606875</v>
       </c>
       <c r="H27" s="63" t="n">
         <f aca="false">0.1*(H7+H9+H5)</f>
-        <v>22.6361337890625</v>
+        <v>3340.26592519375</v>
       </c>
       <c r="I27" s="63"/>
       <c r="J27" s="63" t="s">
@@ -12731,63 +12731,63 @@
       </c>
       <c r="H4" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D4</f>
-        <v>1500</v>
+        <v>4650</v>
       </c>
       <c r="I4" s="93" t="n">
         <f aca="false">H4/D4*E4</f>
-        <v>18</v>
+        <v>55.8</v>
       </c>
       <c r="J4" s="93" t="n">
         <f aca="false">H4/D4*F4</f>
-        <v>33</v>
+        <v>102.3</v>
       </c>
       <c r="K4" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!E4</f>
-        <v>1650</v>
+        <v>4882.5</v>
       </c>
       <c r="L4" s="93" t="n">
         <f aca="false">K4/D4*E4</f>
-        <v>19.8</v>
+        <v>58.59</v>
       </c>
       <c r="M4" s="93" t="n">
         <f aca="false">K4/D4*F4</f>
-        <v>36.3</v>
+        <v>107.415</v>
       </c>
       <c r="N4" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!F4</f>
-        <v>1815</v>
+        <v>5126.625</v>
       </c>
       <c r="O4" s="93" t="n">
         <f aca="false">N4/D4*E4</f>
-        <v>21.78</v>
+        <v>61.5195</v>
       </c>
       <c r="P4" s="93" t="n">
         <f aca="false">N4/D4*F4</f>
-        <v>39.93</v>
+        <v>112.78575</v>
       </c>
       <c r="Q4" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!G4</f>
-        <v>1996.5</v>
+        <v>5382.95625</v>
       </c>
       <c r="R4" s="93" t="n">
         <f aca="false">Q4/D4*E4</f>
-        <v>23.958</v>
+        <v>64.595475</v>
       </c>
       <c r="S4" s="93" t="n">
         <f aca="false">Q4/D4*F4</f>
-        <v>43.923</v>
+        <v>118.4250375</v>
       </c>
       <c r="T4" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!H4</f>
-        <v>2196.15</v>
+        <v>5652.1040625</v>
       </c>
       <c r="U4" s="93" t="n">
         <f aca="false">T4/D4*E4</f>
-        <v>26.3538</v>
+        <v>67.82524875</v>
       </c>
       <c r="V4" s="93" t="n">
         <f aca="false">T4/D4*F4</f>
-        <v>48.3153</v>
+        <v>124.346289375</v>
       </c>
       <c r="W4" s="94"/>
     </row>
@@ -13116,63 +13116,63 @@
       </c>
       <c r="H9" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$19</f>
-        <v>1500</v>
+        <v>4650</v>
       </c>
       <c r="I9" s="93" t="n">
         <f aca="false">H9/D9*E9</f>
-        <v>2.5</v>
+        <v>7.75</v>
       </c>
       <c r="J9" s="93" t="n">
         <f aca="false">H9/D9*F9</f>
-        <v>2.5</v>
+        <v>7.75</v>
       </c>
       <c r="K9" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$19</f>
-        <v>1650</v>
+        <v>4882.5</v>
       </c>
       <c r="L9" s="93" t="n">
         <f aca="false">K9/D9*E9</f>
-        <v>2.75</v>
+        <v>8.1375</v>
       </c>
       <c r="M9" s="93" t="n">
         <f aca="false">K9/D9*F9</f>
-        <v>2.75</v>
+        <v>8.1375</v>
       </c>
       <c r="N9" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$19</f>
-        <v>1815</v>
+        <v>5126.625</v>
       </c>
       <c r="O9" s="93" t="n">
         <f aca="false">N9/D9*E9</f>
-        <v>3.025</v>
+        <v>8.544375</v>
       </c>
       <c r="P9" s="93" t="n">
         <f aca="false">N9/D9*F9</f>
-        <v>3.025</v>
+        <v>8.544375</v>
       </c>
       <c r="Q9" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$19</f>
-        <v>1996.5</v>
+        <v>5382.95625</v>
       </c>
       <c r="R9" s="93" t="n">
         <f aca="false">Q9/D9*E9</f>
-        <v>3.3275</v>
+        <v>8.97159375</v>
       </c>
       <c r="S9" s="93" t="n">
         <f aca="false">Q9/D9*F9</f>
-        <v>3.3275</v>
+        <v>8.97159375</v>
       </c>
       <c r="T9" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$19</f>
-        <v>2196.15</v>
+        <v>5652.1040625</v>
       </c>
       <c r="U9" s="93" t="n">
         <f aca="false">T9/D9*E9</f>
-        <v>3.66025</v>
+        <v>9.4201734375</v>
       </c>
       <c r="V9" s="93" t="n">
         <f aca="false">T9/D9*F9</f>
-        <v>3.66025</v>
+        <v>9.4201734375</v>
       </c>
       <c r="W9" s="94"/>
     </row>
@@ -13267,63 +13267,63 @@
       </c>
       <c r="H11" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$27</f>
-        <v>17.34375</v>
+        <v>2281.6588125</v>
       </c>
       <c r="I11" s="93" t="n">
         <f aca="false">H11/D11*E11</f>
-        <v>0.001734375</v>
+        <v>0.22816588125</v>
       </c>
       <c r="J11" s="93" t="n">
         <f aca="false">H11/D11*F11</f>
-        <v>0.001734375</v>
+        <v>0.22816588125</v>
       </c>
       <c r="K11" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$27</f>
-        <v>18.4921875</v>
+        <v>2509.76219375</v>
       </c>
       <c r="L11" s="93" t="n">
         <f aca="false">K11/D11*E11</f>
-        <v>0.00184921875</v>
+        <v>0.250976219375</v>
       </c>
       <c r="M11" s="93" t="n">
         <f aca="false">K11/D11*F11</f>
-        <v>0.00184921875</v>
+        <v>0.250976219375</v>
       </c>
       <c r="N11" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$27</f>
-        <v>19.747265625</v>
+        <v>2760.672788125</v>
       </c>
       <c r="O11" s="93" t="n">
         <f aca="false">N11/D11*E11</f>
-        <v>0.0019747265625</v>
+        <v>0.2760672788125</v>
       </c>
       <c r="P11" s="93" t="n">
         <f aca="false">N11/D11*F11</f>
-        <v>0.0019747265625</v>
+        <v>0.2760672788125</v>
       </c>
       <c r="Q11" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$27</f>
-        <v>21.12310546875</v>
+        <v>3036.6711606875</v>
       </c>
       <c r="R11" s="93" t="n">
         <f aca="false">Q11/D11*E11</f>
-        <v>0.002112310546875</v>
+        <v>0.30366711606875</v>
       </c>
       <c r="S11" s="93" t="n">
         <f aca="false">Q11/D11*F11</f>
-        <v>0.002112310546875</v>
+        <v>0.30366711606875</v>
       </c>
       <c r="T11" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$27</f>
-        <v>22.6361337890625</v>
+        <v>3340.26592519375</v>
       </c>
       <c r="U11" s="93" t="n">
         <f aca="false">T11/D11*E11</f>
-        <v>0.00226361337890625</v>
+        <v>0.334026592519375</v>
       </c>
       <c r="V11" s="93" t="n">
         <f aca="false">T11/D11*F11</f>
-        <v>0.00226361337890625</v>
+        <v>0.334026592519375</v>
       </c>
       <c r="W11" s="94"/>
     </row>
@@ -13408,63 +13408,63 @@
       </c>
       <c r="H13" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$22</f>
-        <v>17.34375</v>
+        <v>2281.6588125</v>
       </c>
       <c r="I13" s="93" t="n">
         <f aca="false">H13/D13*E13</f>
-        <v>0.001734375</v>
+        <v>0.22816588125</v>
       </c>
       <c r="J13" s="93" t="n">
         <f aca="false">H13/D13*F13</f>
-        <v>0.001734375</v>
+        <v>0.22816588125</v>
       </c>
       <c r="K13" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$22</f>
-        <v>18.4921875</v>
+        <v>2509.76219375</v>
       </c>
       <c r="L13" s="93" t="n">
         <f aca="false">K13/D13*E13</f>
-        <v>0.00184921875</v>
+        <v>0.250976219375</v>
       </c>
       <c r="M13" s="93" t="n">
         <f aca="false">K13/D13*F13</f>
-        <v>0.00184921875</v>
+        <v>0.250976219375</v>
       </c>
       <c r="N13" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$22</f>
-        <v>19.747265625</v>
+        <v>2760.672788125</v>
       </c>
       <c r="O13" s="93" t="n">
         <f aca="false">N13/D13*E13</f>
-        <v>0.0019747265625</v>
+        <v>0.2760672788125</v>
       </c>
       <c r="P13" s="93" t="n">
         <f aca="false">N13/D13*F13</f>
-        <v>0.0019747265625</v>
+        <v>0.2760672788125</v>
       </c>
       <c r="Q13" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$22</f>
-        <v>21.12310546875</v>
+        <v>3036.6711606875</v>
       </c>
       <c r="R13" s="93" t="n">
         <f aca="false">Q13/D13*E13</f>
-        <v>0.002112310546875</v>
+        <v>0.30366711606875</v>
       </c>
       <c r="S13" s="93" t="n">
         <f aca="false">Q13/D13*F13</f>
-        <v>0.002112310546875</v>
+        <v>0.30366711606875</v>
       </c>
       <c r="T13" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$22</f>
-        <v>22.6361337890625</v>
+        <v>3340.26592519375</v>
       </c>
       <c r="U13" s="93" t="n">
         <f aca="false">T13/D13*E13</f>
-        <v>0.00226361337890625</v>
+        <v>0.334026592519375</v>
       </c>
       <c r="V13" s="93" t="n">
         <f aca="false">T13/D13*F13</f>
-        <v>0.00226361337890625</v>
+        <v>0.334026592519375</v>
       </c>
       <c r="W13" s="94"/>
     </row>
@@ -13486,63 +13486,63 @@
       </c>
       <c r="H14" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$24</f>
-        <v>159.375</v>
+        <v>6700</v>
       </c>
       <c r="I14" s="93" t="n">
         <f aca="false">H14/D14*E14</f>
-        <v>0.031875</v>
+        <v>1.34</v>
       </c>
       <c r="J14" s="93" t="n">
         <f aca="false">H14/D14*F14</f>
-        <v>0.0796875</v>
+        <v>3.35</v>
       </c>
       <c r="K14" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$24</f>
-        <v>168.75</v>
+        <v>7369.375</v>
       </c>
       <c r="L14" s="93" t="n">
         <f aca="false">K14/D14*E14</f>
-        <v>0.03375</v>
+        <v>1.473875</v>
       </c>
       <c r="M14" s="93" t="n">
         <f aca="false">K14/D14*F14</f>
-        <v>0.084375</v>
+        <v>3.6846875</v>
       </c>
       <c r="N14" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$24</f>
-        <v>178.875</v>
+        <v>8105.65625</v>
       </c>
       <c r="O14" s="93" t="n">
         <f aca="false">N14/D14*E14</f>
-        <v>0.035775</v>
+        <v>1.62113125</v>
       </c>
       <c r="P14" s="93" t="n">
         <f aca="false">N14/D14*F14</f>
-        <v>0.0894375</v>
+        <v>4.052828125</v>
       </c>
       <c r="Q14" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$24</f>
-        <v>189.84375</v>
+        <v>8915.5328125</v>
       </c>
       <c r="R14" s="93" t="n">
         <f aca="false">Q14/D14*E14</f>
-        <v>0.03796875</v>
+        <v>1.7831065625</v>
       </c>
       <c r="S14" s="93" t="n">
         <f aca="false">Q14/D14*F14</f>
-        <v>0.094921875</v>
+        <v>4.45776640625</v>
       </c>
       <c r="T14" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$24</f>
-        <v>201.7659375</v>
+        <v>9806.36257812501</v>
       </c>
       <c r="U14" s="93" t="n">
         <f aca="false">T14/D14*E14</f>
-        <v>0.0403531875</v>
+        <v>1.961272515625</v>
       </c>
       <c r="V14" s="93" t="n">
         <f aca="false">T14/D14*F14</f>
-        <v>0.10088296875</v>
+        <v>4.9031812890625</v>
       </c>
       <c r="W14" s="94"/>
     </row>
@@ -13564,63 +13564,63 @@
       </c>
       <c r="H15" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$22</f>
-        <v>17.34375</v>
+        <v>2281.6588125</v>
       </c>
       <c r="I15" s="93" t="n">
         <f aca="false">H15/D15*E15</f>
-        <v>0.001734375</v>
+        <v>0.22816588125</v>
       </c>
       <c r="J15" s="93" t="n">
         <f aca="false">H15/D15*F15</f>
-        <v>0.001734375</v>
+        <v>0.22816588125</v>
       </c>
       <c r="K15" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$22</f>
-        <v>18.4921875</v>
+        <v>2509.76219375</v>
       </c>
       <c r="L15" s="93" t="n">
         <f aca="false">K15/D15*E15</f>
-        <v>0.00184921875</v>
+        <v>0.250976219375</v>
       </c>
       <c r="M15" s="93" t="n">
         <f aca="false">K15/D15*F15</f>
-        <v>0.00184921875</v>
+        <v>0.250976219375</v>
       </c>
       <c r="N15" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$22</f>
-        <v>19.747265625</v>
+        <v>2760.672788125</v>
       </c>
       <c r="O15" s="93" t="n">
         <f aca="false">N15/D15*E15</f>
-        <v>0.0019747265625</v>
+        <v>0.2760672788125</v>
       </c>
       <c r="P15" s="93" t="n">
         <f aca="false">N15/D15*F15</f>
-        <v>0.0019747265625</v>
+        <v>0.2760672788125</v>
       </c>
       <c r="Q15" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$22</f>
-        <v>21.12310546875</v>
+        <v>3036.6711606875</v>
       </c>
       <c r="R15" s="93" t="n">
         <f aca="false">Q15/D15*E15</f>
-        <v>0.002112310546875</v>
+        <v>0.30366711606875</v>
       </c>
       <c r="S15" s="93" t="n">
         <f aca="false">Q15/D15*F15</f>
-        <v>0.002112310546875</v>
+        <v>0.30366711606875</v>
       </c>
       <c r="T15" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$22</f>
-        <v>22.6361337890625</v>
+        <v>3340.26592519375</v>
       </c>
       <c r="U15" s="93" t="n">
         <f aca="false">T15/D15*E15</f>
-        <v>0.00226361337890625</v>
+        <v>0.334026592519375</v>
       </c>
       <c r="V15" s="93" t="n">
         <f aca="false">T15/D15*F15</f>
-        <v>0.00226361337890625</v>
+        <v>0.334026592519375</v>
       </c>
       <c r="W15" s="94"/>
     </row>
@@ -13642,63 +13642,63 @@
       </c>
       <c r="H16" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$26</f>
-        <v>178.125</v>
+        <v>10593.317625</v>
       </c>
       <c r="I16" s="93" t="n">
         <f aca="false">H16/D16*E16</f>
-        <v>0.035625</v>
+        <v>2.118663525</v>
       </c>
       <c r="J16" s="93" t="n">
         <f aca="false">H16/D16*F16</f>
-        <v>0.07125</v>
+        <v>4.23732705</v>
       </c>
       <c r="K16" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$26</f>
-        <v>188.859375</v>
+        <v>11651.9618875</v>
       </c>
       <c r="L16" s="93" t="n">
         <f aca="false">K16/D16*E16</f>
-        <v>0.037771875</v>
+        <v>2.3303923775</v>
       </c>
       <c r="M16" s="93" t="n">
         <f aca="false">K16/D16*F16</f>
-        <v>0.07554375</v>
+        <v>4.660784755</v>
       </c>
       <c r="N16" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$26</f>
-        <v>200.48203125</v>
+        <v>12816.43620125</v>
       </c>
       <c r="O16" s="93" t="n">
         <f aca="false">N16/D16*E16</f>
-        <v>0.04009640625</v>
+        <v>2.56328724025</v>
       </c>
       <c r="P16" s="93" t="n">
         <f aca="false">N16/D16*F16</f>
-        <v>0.0801928125</v>
+        <v>5.1265744805</v>
       </c>
       <c r="Q16" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$26</f>
-        <v>213.1055859375</v>
+        <v>14097.321852625</v>
       </c>
       <c r="R16" s="93" t="n">
         <f aca="false">Q16/D16*E16</f>
-        <v>0.0426211171875</v>
+        <v>2.819464370525</v>
       </c>
       <c r="S16" s="93" t="n">
         <f aca="false">Q16/D16*F16</f>
-        <v>0.085242234375</v>
+        <v>5.63892874105</v>
       </c>
       <c r="T16" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$26</f>
-        <v>226.861611328125</v>
+        <v>15506.2581707</v>
       </c>
       <c r="U16" s="93" t="n">
         <f aca="false">T16/D16*E16</f>
-        <v>0.045372322265625</v>
+        <v>3.10125163414</v>
       </c>
       <c r="V16" s="93" t="n">
         <f aca="false">T16/D16*F16</f>
-        <v>0.09074464453125</v>
+        <v>6.20250326828</v>
       </c>
       <c r="W16" s="94"/>
     </row>
@@ -13720,63 +13720,63 @@
       </c>
       <c r="H17" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$21</f>
-        <v>1.40625</v>
+        <v>1611.6588125</v>
       </c>
       <c r="I17" s="93" t="n">
         <f aca="false">H17/D17*E17</f>
-        <v>0.00028125</v>
+        <v>0.3223317625</v>
       </c>
       <c r="J17" s="93" t="n">
         <f aca="false">H17/D17*F17</f>
-        <v>0.00028125</v>
+        <v>0.3223317625</v>
       </c>
       <c r="K17" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$21</f>
-        <v>1.6171875</v>
+        <v>1772.82469375</v>
       </c>
       <c r="L17" s="93" t="n">
         <f aca="false">K17/D17*E17</f>
-        <v>0.0003234375</v>
+        <v>0.35456493875</v>
       </c>
       <c r="M17" s="93" t="n">
         <f aca="false">K17/D17*F17</f>
-        <v>0.0003234375</v>
+        <v>0.35456493875</v>
       </c>
       <c r="N17" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$21</f>
-        <v>1.859765625</v>
+        <v>1950.107163125</v>
       </c>
       <c r="O17" s="93" t="n">
         <f aca="false">N17/D17*E17</f>
-        <v>0.000371953125</v>
+        <v>0.390021432625</v>
       </c>
       <c r="P17" s="93" t="n">
         <f aca="false">N17/D17*F17</f>
-        <v>0.000371953125</v>
+        <v>0.390021432625</v>
       </c>
       <c r="Q17" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$21</f>
-        <v>2.13873046875</v>
+        <v>2145.1178794375</v>
       </c>
       <c r="R17" s="93" t="n">
         <f aca="false">Q17/D17*E17</f>
-        <v>0.00042774609375</v>
+        <v>0.4290235758875</v>
       </c>
       <c r="S17" s="93" t="n">
         <f aca="false">Q17/D17*F17</f>
-        <v>0.00042774609375</v>
+        <v>0.4290235758875</v>
       </c>
       <c r="T17" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$21</f>
-        <v>2.4595400390625</v>
+        <v>2359.62966738125</v>
       </c>
       <c r="U17" s="93" t="n">
         <f aca="false">T17/D17*E17</f>
-        <v>0.0004919080078125</v>
+        <v>0.47192593347625</v>
       </c>
       <c r="V17" s="93" t="n">
         <f aca="false">T17/D17*F17</f>
-        <v>0.0004919080078125</v>
+        <v>0.47192593347625</v>
       </c>
       <c r="W17" s="94"/>
     </row>
@@ -13798,63 +13798,63 @@
       </c>
       <c r="H18" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$21</f>
-        <v>1.40625</v>
+        <v>1611.6588125</v>
       </c>
       <c r="I18" s="93" t="n">
         <f aca="false">H18/D18*E18</f>
-        <v>0.000140625</v>
+        <v>0.16116588125</v>
       </c>
       <c r="J18" s="93" t="n">
         <f aca="false">H18/D18*F18</f>
-        <v>0.000140625</v>
+        <v>0.16116588125</v>
       </c>
       <c r="K18" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$21</f>
-        <v>1.6171875</v>
+        <v>1772.82469375</v>
       </c>
       <c r="L18" s="93" t="n">
         <f aca="false">K18/D18*E18</f>
-        <v>0.00016171875</v>
+        <v>0.177282469375</v>
       </c>
       <c r="M18" s="93" t="n">
         <f aca="false">K18/D18*F18</f>
-        <v>0.00016171875</v>
+        <v>0.177282469375</v>
       </c>
       <c r="N18" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$21</f>
-        <v>1.859765625</v>
+        <v>1950.107163125</v>
       </c>
       <c r="O18" s="93" t="n">
         <f aca="false">N18/D18*E18</f>
-        <v>0.0001859765625</v>
+        <v>0.1950107163125</v>
       </c>
       <c r="P18" s="93" t="n">
         <f aca="false">N18/D18*F18</f>
-        <v>0.0001859765625</v>
+        <v>0.1950107163125</v>
       </c>
       <c r="Q18" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$21</f>
-        <v>2.13873046875</v>
+        <v>2145.1178794375</v>
       </c>
       <c r="R18" s="93" t="n">
         <f aca="false">Q18/D18*E18</f>
-        <v>0.000213873046875</v>
+        <v>0.21451178794375</v>
       </c>
       <c r="S18" s="93" t="n">
         <f aca="false">Q18/D18*F18</f>
-        <v>0.000213873046875</v>
+        <v>0.21451178794375</v>
       </c>
       <c r="T18" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$21</f>
-        <v>2.4595400390625</v>
+        <v>2359.62966738125</v>
       </c>
       <c r="U18" s="93" t="n">
         <f aca="false">T18/D18*E18</f>
-        <v>0.00024595400390625</v>
+        <v>0.235962966738125</v>
       </c>
       <c r="V18" s="93" t="n">
         <f aca="false">T18/D18*F18</f>
-        <v>0.00024595400390625</v>
+        <v>0.235962966738125</v>
       </c>
       <c r="W18" s="94"/>
     </row>
@@ -13876,63 +13876,63 @@
       </c>
       <c r="H19" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$21</f>
-        <v>1.40625</v>
+        <v>1611.6588125</v>
       </c>
       <c r="I19" s="93" t="n">
         <f aca="false">H19/D19*E19</f>
-        <v>0.000140625</v>
+        <v>0.16116588125</v>
       </c>
       <c r="J19" s="93" t="n">
         <f aca="false">H19/D19*F19</f>
-        <v>0.000140625</v>
+        <v>0.16116588125</v>
       </c>
       <c r="K19" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$21</f>
-        <v>1.6171875</v>
+        <v>1772.82469375</v>
       </c>
       <c r="L19" s="93" t="n">
         <f aca="false">K19/D19*E19</f>
-        <v>0.00016171875</v>
+        <v>0.177282469375</v>
       </c>
       <c r="M19" s="93" t="n">
         <f aca="false">K19/D19*F19</f>
-        <v>0.00016171875</v>
+        <v>0.177282469375</v>
       </c>
       <c r="N19" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$21</f>
-        <v>1.859765625</v>
+        <v>1950.107163125</v>
       </c>
       <c r="O19" s="93" t="n">
         <f aca="false">N19/D19*E19</f>
-        <v>0.0001859765625</v>
+        <v>0.1950107163125</v>
       </c>
       <c r="P19" s="93" t="n">
         <f aca="false">N19/D19*F19</f>
-        <v>0.0001859765625</v>
+        <v>0.1950107163125</v>
       </c>
       <c r="Q19" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$21</f>
-        <v>2.13873046875</v>
+        <v>2145.1178794375</v>
       </c>
       <c r="R19" s="93" t="n">
         <f aca="false">Q19/D19*E19</f>
-        <v>0.000213873046875</v>
+        <v>0.21451178794375</v>
       </c>
       <c r="S19" s="93" t="n">
         <f aca="false">Q19/D19*F19</f>
-        <v>0.000213873046875</v>
+        <v>0.21451178794375</v>
       </c>
       <c r="T19" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$21</f>
-        <v>2.4595400390625</v>
+        <v>2359.62966738125</v>
       </c>
       <c r="U19" s="93" t="n">
         <f aca="false">T19/D19*E19</f>
-        <v>0.00024595400390625</v>
+        <v>0.235962966738125</v>
       </c>
       <c r="V19" s="93" t="n">
         <f aca="false">T19/D19*F19</f>
-        <v>0.00024595400390625</v>
+        <v>0.235962966738125</v>
       </c>
       <c r="W19" s="94"/>
     </row>
@@ -13954,63 +13954,63 @@
       </c>
       <c r="H20" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$D$21</f>
-        <v>1.40625</v>
+        <v>1611.6588125</v>
       </c>
       <c r="I20" s="93" t="n">
         <f aca="false">H20/D20*E20</f>
-        <v>0.000140625</v>
+        <v>0.16116588125</v>
       </c>
       <c r="J20" s="93" t="n">
         <f aca="false">H20/D20*F20</f>
-        <v>0.000140625</v>
+        <v>0.16116588125</v>
       </c>
       <c r="K20" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$E$21</f>
-        <v>1.6171875</v>
+        <v>1772.82469375</v>
       </c>
       <c r="L20" s="93" t="n">
         <f aca="false">K20/D20*E20</f>
-        <v>0.00016171875</v>
+        <v>0.177282469375</v>
       </c>
       <c r="M20" s="93" t="n">
         <f aca="false">K20/D20*F20</f>
-        <v>0.00016171875</v>
+        <v>0.177282469375</v>
       </c>
       <c r="N20" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$F$21</f>
-        <v>1.859765625</v>
+        <v>1950.107163125</v>
       </c>
       <c r="O20" s="93" t="n">
         <f aca="false">N20/D20*E20</f>
-        <v>0.0001859765625</v>
+        <v>0.1950107163125</v>
       </c>
       <c r="P20" s="93" t="n">
         <f aca="false">N20/D20*F20</f>
-        <v>0.0001859765625</v>
+        <v>0.1950107163125</v>
       </c>
       <c r="Q20" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$G$21</f>
-        <v>2.13873046875</v>
+        <v>2145.1178794375</v>
       </c>
       <c r="R20" s="93" t="n">
         <f aca="false">Q20/D20*E20</f>
-        <v>0.000213873046875</v>
+        <v>0.21451178794375</v>
       </c>
       <c r="S20" s="93" t="n">
         <f aca="false">Q20/D20*F20</f>
-        <v>0.000213873046875</v>
+        <v>0.21451178794375</v>
       </c>
       <c r="T20" s="92" t="n">
         <f aca="false">'Per Hour Volumes'!$H$21</f>
-        <v>2.4595400390625</v>
+        <v>2359.62966738125</v>
       </c>
       <c r="U20" s="93" t="n">
         <f aca="false">T20/D20*E20</f>
-        <v>0.00024595400390625</v>
+        <v>0.235962966738125</v>
       </c>
       <c r="V20" s="93" t="n">
         <f aca="false">T20/D20*F20</f>
-        <v>0.00024595400390625</v>
+        <v>0.235962966738125</v>
       </c>
       <c r="W20" s="94"/>
     </row>
@@ -14235,47 +14235,47 @@
       </c>
       <c r="I24" s="97" t="n">
         <f aca="false">SUM(I4:I23)</f>
-        <v>47.57340625</v>
+        <v>95.498990575</v>
       </c>
       <c r="J24" s="97" t="n">
         <f aca="false">SUM(J4:J23)</f>
-        <v>87.65684375</v>
+        <v>171.1276541</v>
       </c>
       <c r="K24" s="96"/>
       <c r="L24" s="97" t="n">
         <f aca="false">SUM(L4:L23)</f>
-        <v>49.877878125</v>
+        <v>99.4211083825</v>
       </c>
       <c r="M24" s="97" t="n">
         <f aca="false">SUM(M4:M23)</f>
-        <v>92.216275</v>
+        <v>178.53731326</v>
       </c>
       <c r="N24" s="96"/>
       <c r="O24" s="97" t="n">
         <f aca="false">SUM(O4:O23)</f>
-        <v>52.40022546875</v>
+        <v>103.56404890825</v>
       </c>
       <c r="P24" s="97" t="n">
         <f aca="false">SUM(P4:P23)</f>
-        <v>97.181484375</v>
+        <v>186.3627830235</v>
       </c>
       <c r="Q24" s="96"/>
       <c r="R24" s="97" t="n">
         <f aca="false">SUM(R4:R23)</f>
-        <v>55.1616211640625</v>
+        <v>107.94132497095</v>
       </c>
       <c r="S24" s="97" t="n">
         <f aca="false">SUM(S4:S23)</f>
-        <v>102.59057040625</v>
+        <v>194.629386685225</v>
       </c>
       <c r="T24" s="96"/>
       <c r="U24" s="97" t="n">
         <f aca="false">SUM(U4:U23)</f>
-        <v>58.1853273699219</v>
+        <v>112.567372198514</v>
       </c>
       <c r="V24" s="97" t="n">
         <f aca="false">SUM(V4:V23)</f>
-        <v>108.485323223438</v>
+        <v>203.364166981091</v>
       </c>
       <c r="W24" s="94"/>
     </row>
@@ -14315,23 +14315,23 @@
       </c>
       <c r="D28" s="105" t="n">
         <f aca="false">ROUNDUP(I24,0)</f>
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="E28" s="105" t="n">
         <f aca="false">ROUNDUP(L24,0)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F28" s="105" t="n">
         <f aca="false">ROUNDUP(O24,0)</f>
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="G28" s="105" t="n">
         <f aca="false">ROUNDUP(R24,0)</f>
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="H28" s="105" t="n">
         <f aca="false">ROUNDUP(U24,0)</f>
-        <v>59</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14340,23 +14340,23 @@
       </c>
       <c r="D29" s="105" t="n">
         <f aca="false">ROUNDUP(J24,0)</f>
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="E29" s="105" t="n">
         <f aca="false">ROUNDUP(M24,0)</f>
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="F29" s="105" t="n">
         <f aca="false">ROUNDUP(P24,0)</f>
-        <v>98</v>
+        <v>187</v>
       </c>
       <c r="G29" s="105" t="n">
         <f aca="false">S24</f>
-        <v>102.59057040625</v>
+        <v>194.629386685225</v>
       </c>
       <c r="H29" s="105" t="n">
         <f aca="false">ROUNDUP(V24,0)</f>
-        <v>109</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -17732,11 +17732,11 @@
       </c>
       <c r="C5" s="173" t="n">
         <f aca="false">'Customer Volumes'!D5</f>
-        <v>22500</v>
+        <v>25786541</v>
       </c>
       <c r="D5" s="174" t="n">
         <f aca="false">C5*'Datasize-Parameters'!$J$13/(1024*1024)</f>
-        <v>0.407695770263672</v>
+        <v>467.247275352478</v>
       </c>
       <c r="F5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -17744,11 +17744,11 @@
       </c>
       <c r="G5" s="173" t="n">
         <f aca="false">'Customer Volumes'!E5</f>
-        <v>25875</v>
+        <v>28365195.1</v>
       </c>
       <c r="H5" s="174" t="n">
         <f aca="false">G5*'Datasize-Parameters'!$J$13/(1024*1024)</f>
-        <v>0.468850135803223</v>
+        <v>513.972002887726</v>
       </c>
       <c r="J5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -17756,11 +17756,11 @@
       </c>
       <c r="K5" s="173" t="n">
         <f aca="false">'Customer Volumes'!F5</f>
-        <v>29756.25</v>
+        <v>31201714.61</v>
       </c>
       <c r="L5" s="174" t="n">
         <f aca="false">K5*'Datasize-Parameters'!$J$13/(1024*1024)</f>
-        <v>0.539177656173706</v>
+        <v>565.369203176498</v>
       </c>
       <c r="N5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -17768,11 +17768,11 @@
       </c>
       <c r="O5" s="173" t="n">
         <f aca="false">'Customer Volumes'!G5</f>
-        <v>34219.6875</v>
+        <v>34321886.071</v>
       </c>
       <c r="P5" s="174" t="n">
         <f aca="false">O5*'Datasize-Parameters'!$J$13/(1024*1024)</f>
-        <v>0.620054304599762</v>
+        <v>621.906123494149</v>
       </c>
       <c r="R5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -17780,11 +17780,11 @@
       </c>
       <c r="S5" s="173" t="n">
         <f aca="false">'Customer Volumes'!H5</f>
-        <v>39352.640625</v>
+        <v>37754074.6781</v>
       </c>
       <c r="T5" s="174" t="n">
         <f aca="false">S5*'Datasize-Parameters'!$J$13/(1024*1024)</f>
-        <v>0.713062450289726</v>
+        <v>684.096735843563</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17795,11 +17795,11 @@
       </c>
       <c r="C6" s="173" t="n">
         <f aca="false">'Customer Volumes'!D7</f>
-        <v>240000</v>
+        <v>10700000</v>
       </c>
       <c r="D6" s="174" t="n">
         <f aca="false">C6*'Datasize-Parameters'!$N$13/(1024*1024)</f>
-        <v>9.1552734375</v>
+        <v>408.172607421875</v>
       </c>
       <c r="F6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -17807,11 +17807,11 @@
       </c>
       <c r="G6" s="173" t="n">
         <f aca="false">'Customer Volumes'!E7</f>
-        <v>252000</v>
+        <v>11770000</v>
       </c>
       <c r="H6" s="174" t="n">
         <f aca="false">G6*'Datasize-Parameters'!$N$13/(1024*1024)</f>
-        <v>9.613037109375</v>
+        <v>448.989868164063</v>
       </c>
       <c r="J6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -17819,11 +17819,11 @@
       </c>
       <c r="K6" s="173" t="n">
         <f aca="false">'Customer Volumes'!F7</f>
-        <v>264600</v>
+        <v>12947000</v>
       </c>
       <c r="L6" s="174" t="n">
         <f aca="false">K6*'Datasize-Parameters'!$N$13/(1024*1024)</f>
-        <v>10.0936889648438</v>
+        <v>493.888854980469</v>
       </c>
       <c r="N6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -17831,11 +17831,11 @@
       </c>
       <c r="O6" s="173" t="n">
         <f aca="false">'Customer Volumes'!G7</f>
-        <v>277830</v>
+        <v>14241700</v>
       </c>
       <c r="P6" s="174" t="n">
         <f aca="false">O6*'Datasize-Parameters'!$N$13/(1024*1024)</f>
-        <v>10.5983734130859</v>
+        <v>543.277740478516</v>
       </c>
       <c r="R6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -17843,11 +17843,11 @@
       </c>
       <c r="S6" s="173" t="n">
         <f aca="false">'Customer Volumes'!H7</f>
-        <v>291721.5</v>
+        <v>15665870</v>
       </c>
       <c r="T6" s="174" t="n">
         <f aca="false">S6*'Datasize-Parameters'!$N$13/(1024*1024)</f>
-        <v>11.1282920837402</v>
+        <v>597.605514526367</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17858,11 +17858,11 @@
       </c>
       <c r="C7" s="173" t="n">
         <f aca="false">'Customer Volumes'!D9</f>
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="D7" s="174" t="n">
         <f aca="false">C7*'Datasize-Parameters'!$R$13/(1024*1024)</f>
-        <v>0.536441802978516</v>
+        <v>0.715255737304688</v>
       </c>
       <c r="F7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -17870,11 +17870,11 @@
       </c>
       <c r="G7" s="173" t="n">
         <f aca="false">'Customer Volumes'!E9</f>
-        <v>18000</v>
+        <v>21000</v>
       </c>
       <c r="H7" s="174" t="n">
         <f aca="false">G7*'Datasize-Parameters'!$R$13/(1024*1024)</f>
-        <v>0.643730163574219</v>
+        <v>0.751018524169922</v>
       </c>
       <c r="J7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -17882,11 +17882,11 @@
       </c>
       <c r="K7" s="173" t="n">
         <f aca="false">'Customer Volumes'!F9</f>
-        <v>21600</v>
+        <v>22050</v>
       </c>
       <c r="L7" s="174" t="n">
         <f aca="false">K7*'Datasize-Parameters'!$R$13/(1024*1024)</f>
-        <v>0.772476196289063</v>
+        <v>0.788569450378418</v>
       </c>
       <c r="N7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -17894,11 +17894,11 @@
       </c>
       <c r="O7" s="173" t="n">
         <f aca="false">'Customer Volumes'!G9</f>
-        <v>25920</v>
+        <v>23152.5</v>
       </c>
       <c r="P7" s="174" t="n">
         <f aca="false">O7*'Datasize-Parameters'!$R$13/(1024*1024)</f>
-        <v>0.926971435546875</v>
+        <v>0.827997922897339</v>
       </c>
       <c r="R7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -17906,11 +17906,11 @@
       </c>
       <c r="S7" s="173" t="n">
         <f aca="false">'Customer Volumes'!H9</f>
-        <v>31104</v>
+        <v>24310.125</v>
       </c>
       <c r="T7" s="174" t="n">
         <f aca="false">S7*'Datasize-Parameters'!$R$13/(1024*1024)</f>
-        <v>1.11236572265625</v>
+        <v>0.869397819042206</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18099,11 +18099,11 @@
       </c>
       <c r="C11" s="173" t="n">
         <f aca="false">'Customer Volumes'!D5*'Customer Volumes'!D12</f>
-        <v>22500</v>
+        <v>25786541</v>
       </c>
       <c r="D11" s="174" t="n">
         <f aca="false">C11*'Datasize-Parameters'!$J$39/(1024*1024)</f>
-        <v>0.171661376953125</v>
+        <v>196.735694885254</v>
       </c>
       <c r="F11" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$10</f>
@@ -18111,11 +18111,11 @@
       </c>
       <c r="G11" s="173" t="n">
         <f aca="false">'Customer Volumes'!E5*'Customer Volumes'!E12</f>
-        <v>25875</v>
+        <v>28365195.1</v>
       </c>
       <c r="H11" s="174" t="n">
         <f aca="false">G11*'Datasize-Parameters'!$J$39/(1024*1024)</f>
-        <v>0.197410583496094</v>
+        <v>216.409264373779</v>
       </c>
       <c r="J11" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$10</f>
@@ -18123,11 +18123,11 @@
       </c>
       <c r="K11" s="173" t="n">
         <f aca="false">'Customer Volumes'!F5*'Customer Volumes'!F12</f>
-        <v>29756.25</v>
+        <v>31201714.61</v>
       </c>
       <c r="L11" s="174" t="n">
         <f aca="false">K11*'Datasize-Parameters'!$J$39/(1024*1024)</f>
-        <v>0.227022171020508</v>
+        <v>238.050190811157</v>
       </c>
       <c r="N11" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$10</f>
@@ -18135,11 +18135,11 @@
       </c>
       <c r="O11" s="173" t="n">
         <f aca="false">'Customer Volumes'!G5*'Customer Volumes'!G12</f>
-        <v>34219.6875</v>
+        <v>34321886.071</v>
       </c>
       <c r="P11" s="174" t="n">
         <f aca="false">O11*'Datasize-Parameters'!$J$39/(1024*1024)</f>
-        <v>0.261075496673584</v>
+        <v>261.855209892273</v>
       </c>
       <c r="R11" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$10</f>
@@ -18147,11 +18147,11 @@
       </c>
       <c r="S11" s="173" t="n">
         <f aca="false">'Customer Volumes'!H5*'Customer Volumes'!H12</f>
-        <v>39352.640625</v>
+        <v>37754074.6781</v>
       </c>
       <c r="T11" s="174" t="n">
         <f aca="false">S11*'Datasize-Parameters'!$J$39/(1024*1024)</f>
-        <v>0.300236821174621</v>
+        <v>288.0407308815</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18323,55 +18323,55 @@
       </c>
       <c r="C15" s="173" t="n">
         <f aca="false">C5*0.3+C6*0.3+C7</f>
-        <v>93750</v>
+        <v>10965962.3</v>
       </c>
       <c r="D15" s="174" t="n">
         <f aca="false">C15*'Datasize-Parameters'!$V$13/(1024*1024)</f>
-        <v>0.044703483581543</v>
+        <v>5.22897830009461</v>
       </c>
       <c r="F15" s="172" t="s">
         <v>271</v>
       </c>
       <c r="G15" s="173" t="n">
         <f aca="false">G5*0.3+G6*0.3+G7</f>
-        <v>101362.5</v>
+        <v>12061558.53</v>
       </c>
       <c r="H15" s="174" t="n">
         <f aca="false">G15*'Datasize-Parameters'!$V$13/(1024*1024)</f>
-        <v>0.0483334064483643</v>
+        <v>5.75139929294586</v>
       </c>
       <c r="J15" s="172" t="s">
         <v>271</v>
       </c>
       <c r="K15" s="173" t="n">
         <f aca="false">K5*0.3+K6*0.3+K7</f>
-        <v>109906.875</v>
+        <v>13266664.383</v>
       </c>
       <c r="L15" s="174" t="n">
         <f aca="false">K15*'Datasize-Parameters'!$V$13/(1024*1024)</f>
-        <v>0.0524076819419861</v>
+        <v>6.32603854322434</v>
       </c>
       <c r="N15" s="172" t="s">
         <v>271</v>
       </c>
       <c r="O15" s="173" t="n">
         <f aca="false">O5*0.3+O6*0.3+O7</f>
-        <v>119534.90625</v>
+        <v>14592228.3213</v>
       </c>
       <c r="P15" s="174" t="n">
         <f aca="false">O15*'Datasize-Parameters'!$V$13/(1024*1024)</f>
-        <v>0.056998685002327</v>
+        <v>6.95811668457985</v>
       </c>
       <c r="R15" s="172" t="s">
         <v>271</v>
       </c>
       <c r="S15" s="173" t="n">
         <f aca="false">S5*0.3+S6*0.3+S7</f>
-        <v>130426.2421875</v>
+        <v>16050293.52843</v>
       </c>
       <c r="T15" s="174" t="n">
         <f aca="false">S15*'Datasize-Parameters'!$V$13/(1024*1024)</f>
-        <v>0.0621920786798</v>
+        <v>7.65337635442257</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18400,7 +18400,7 @@
       <c r="C17" s="178"/>
       <c r="D17" s="177" t="n">
         <f aca="false">SUM(D5:D15)</f>
-        <v>10.3163480758667</v>
+        <v>1078.1003839016</v>
       </c>
       <c r="F17" s="178" t="s">
         <v>272</v>
@@ -18408,7 +18408,7 @@
       <c r="G17" s="178"/>
       <c r="H17" s="177" t="n">
         <f aca="false">SUM(H5:H15)</f>
-        <v>10.9719336032867</v>
+        <v>1185.87412544727</v>
       </c>
       <c r="J17" s="178" t="s">
         <v>272</v>
@@ -18416,7 +18416,7 @@
       <c r="K17" s="178"/>
       <c r="L17" s="177" t="n">
         <f aca="false">SUM(L5:L15)</f>
-        <v>11.6853448748589</v>
+        <v>1304.42342916632</v>
       </c>
       <c r="N17" s="178" t="s">
         <v>272</v>
@@ -18424,7 +18424,7 @@
       <c r="O17" s="178"/>
       <c r="P17" s="177" t="n">
         <f aca="false">SUM(P5:P15)</f>
-        <v>12.4640455394983</v>
+        <v>1434.825760677</v>
       </c>
       <c r="Q17" s="179"/>
       <c r="R17" s="178" t="s">
@@ -18433,7 +18433,7 @@
       <c r="S17" s="178"/>
       <c r="T17" s="177" t="n">
         <f aca="false">SUM(T5:T15)</f>
-        <v>13.3161491565406</v>
+        <v>1578.2657554249</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18524,7 +18524,7 @@
       <c r="C22" s="185"/>
       <c r="D22" s="186" t="n">
         <f aca="false">D17</f>
-        <v>10.3163480758667</v>
+        <v>1078.1003839016</v>
       </c>
       <c r="F22" s="182" t="s">
         <v>268</v>
@@ -18532,7 +18532,7 @@
       <c r="G22" s="185"/>
       <c r="H22" s="186" t="n">
         <f aca="false">H17</f>
-        <v>10.9719336032867</v>
+        <v>1185.87412544727</v>
       </c>
       <c r="J22" s="182" t="s">
         <v>268</v>
@@ -18540,7 +18540,7 @@
       <c r="K22" s="185"/>
       <c r="L22" s="186" t="n">
         <f aca="false">L17</f>
-        <v>11.6853448748589</v>
+        <v>1304.42342916632</v>
       </c>
       <c r="N22" s="182" t="s">
         <v>268</v>
@@ -18548,7 +18548,7 @@
       <c r="O22" s="185"/>
       <c r="P22" s="186" t="n">
         <f aca="false">P17</f>
-        <v>12.4640455394983</v>
+        <v>1434.825760677</v>
       </c>
       <c r="R22" s="182" t="s">
         <v>268</v>
@@ -18556,7 +18556,7 @@
       <c r="S22" s="185"/>
       <c r="T22" s="186" t="n">
         <f aca="false">T17</f>
-        <v>13.3161491565406</v>
+        <v>1578.2657554249</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18567,7 +18567,7 @@
       <c r="C23" s="185"/>
       <c r="D23" s="186" t="n">
         <f aca="false">D22*'Datasize-Parameters'!$C$29</f>
-        <v>1.54745221138</v>
+        <v>161.715057585239</v>
       </c>
       <c r="F23" s="182" t="s">
         <v>253</v>
@@ -18575,7 +18575,7 @@
       <c r="G23" s="185"/>
       <c r="H23" s="186" t="n">
         <f aca="false">H22*'Datasize-Parameters'!$C$29</f>
-        <v>1.64579004049301</v>
+        <v>177.881118817091</v>
       </c>
       <c r="J23" s="182" t="s">
         <v>253</v>
@@ -18583,7 +18583,7 @@
       <c r="K23" s="185"/>
       <c r="L23" s="186" t="n">
         <f aca="false">L22*'Datasize-Parameters'!$C$29</f>
-        <v>1.75280173122883</v>
+        <v>195.663514374948</v>
       </c>
       <c r="N23" s="182" t="s">
         <v>253</v>
@@ -18591,7 +18591,7 @@
       <c r="O23" s="185"/>
       <c r="P23" s="186" t="n">
         <f aca="false">P22*'Datasize-Parameters'!$C$29</f>
-        <v>1.86960683092475</v>
+        <v>215.223864101551</v>
       </c>
       <c r="R23" s="182" t="s">
         <v>253</v>
@@ -18599,7 +18599,7 @@
       <c r="S23" s="185"/>
       <c r="T23" s="186" t="n">
         <f aca="false">T22*'Datasize-Parameters'!$C$29</f>
-        <v>1.99742237348109</v>
+        <v>236.739863313734</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18610,7 +18610,7 @@
       <c r="C24" s="185"/>
       <c r="D24" s="186" t="n">
         <f aca="false">D22*'Datasize-Parameters'!$C$30</f>
-        <v>2.06326961517334</v>
+        <v>215.620076780319</v>
       </c>
       <c r="F24" s="182" t="s">
         <v>255</v>
@@ -18618,7 +18618,7 @@
       <c r="G24" s="185"/>
       <c r="H24" s="186" t="n">
         <f aca="false">H22*'Datasize-Parameters'!$C$30</f>
-        <v>2.19438672065735</v>
+        <v>237.174825089455</v>
       </c>
       <c r="J24" s="182" t="s">
         <v>255</v>
@@ -18626,7 +18626,7 @@
       <c r="K24" s="185"/>
       <c r="L24" s="186" t="n">
         <f aca="false">L22*'Datasize-Parameters'!$C$30</f>
-        <v>2.33706897497177</v>
+        <v>260.884685833263</v>
       </c>
       <c r="N24" s="182" t="s">
         <v>255</v>
@@ -18634,7 +18634,7 @@
       <c r="O24" s="185"/>
       <c r="P24" s="186" t="n">
         <f aca="false">P22*'Datasize-Parameters'!$C$30</f>
-        <v>2.49280910789967</v>
+        <v>286.965152135401</v>
       </c>
       <c r="R24" s="182" t="s">
         <v>255</v>
@@ -18642,7 +18642,7 @@
       <c r="S24" s="185"/>
       <c r="T24" s="186" t="n">
         <f aca="false">T22*'Datasize-Parameters'!$C$30</f>
-        <v>2.66322983130813</v>
+        <v>315.653151084979</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18653,7 +18653,7 @@
       <c r="C25" s="185"/>
       <c r="D25" s="186" t="n">
         <f aca="false">D22*'Datasize-Parameters'!$C$31</f>
-        <v>2.06326961517334</v>
+        <v>215.620076780319</v>
       </c>
       <c r="F25" s="182" t="s">
         <v>256</v>
@@ -18661,7 +18661,7 @@
       <c r="G25" s="185"/>
       <c r="H25" s="186" t="n">
         <f aca="false">H22*'Datasize-Parameters'!$C$31</f>
-        <v>2.19438672065735</v>
+        <v>237.174825089455</v>
       </c>
       <c r="J25" s="182" t="s">
         <v>256</v>
@@ -18669,7 +18669,7 @@
       <c r="K25" s="185"/>
       <c r="L25" s="186" t="n">
         <f aca="false">L22*'Datasize-Parameters'!$C$31</f>
-        <v>2.33706897497177</v>
+        <v>260.884685833263</v>
       </c>
       <c r="N25" s="182" t="s">
         <v>256</v>
@@ -18677,7 +18677,7 @@
       <c r="O25" s="185"/>
       <c r="P25" s="186" t="n">
         <f aca="false">P22*'Datasize-Parameters'!$C$31</f>
-        <v>2.49280910789967</v>
+        <v>286.965152135401</v>
       </c>
       <c r="R25" s="182" t="s">
         <v>256</v>
@@ -18685,7 +18685,7 @@
       <c r="S25" s="185"/>
       <c r="T25" s="186" t="n">
         <f aca="false">T22*'Datasize-Parameters'!$C$31</f>
-        <v>2.66322983130813</v>
+        <v>315.653151084979</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18696,7 +18696,7 @@
       <c r="C26" s="185"/>
       <c r="D26" s="186" t="n">
         <f aca="false">D22*'Datasize-Parameters'!$C$32</f>
-        <v>2.06326961517334</v>
+        <v>215.620076780319</v>
       </c>
       <c r="F26" s="181" t="s">
         <v>275</v>
@@ -18704,7 +18704,7 @@
       <c r="G26" s="185"/>
       <c r="H26" s="186" t="n">
         <f aca="false">H22*'Datasize-Parameters'!$C$32</f>
-        <v>2.19438672065735</v>
+        <v>237.174825089455</v>
       </c>
       <c r="J26" s="181" t="s">
         <v>275</v>
@@ -18712,7 +18712,7 @@
       <c r="K26" s="185"/>
       <c r="L26" s="186" t="n">
         <f aca="false">L22*'Datasize-Parameters'!$C$32</f>
-        <v>2.33706897497177</v>
+        <v>260.884685833263</v>
       </c>
       <c r="N26" s="181" t="s">
         <v>275</v>
@@ -18720,7 +18720,7 @@
       <c r="O26" s="185"/>
       <c r="P26" s="186" t="n">
         <f aca="false">P22*'Datasize-Parameters'!$C$32</f>
-        <v>2.49280910789967</v>
+        <v>286.965152135401</v>
       </c>
       <c r="R26" s="181" t="s">
         <v>275</v>
@@ -18728,7 +18728,7 @@
       <c r="S26" s="185"/>
       <c r="T26" s="186" t="n">
         <f aca="false">T22*'Datasize-Parameters'!$C$32</f>
-        <v>2.66322983130813</v>
+        <v>315.653151084979</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18739,7 +18739,7 @@
       <c r="C27" s="185"/>
       <c r="D27" s="186" t="n">
         <f aca="false">D23*'Datasize-Parameters'!$C$33</f>
-        <v>0.386863052845001</v>
+        <v>40.4287643963099</v>
       </c>
       <c r="F27" s="182" t="s">
         <v>276</v>
@@ -18747,7 +18747,7 @@
       <c r="G27" s="185"/>
       <c r="H27" s="186" t="n">
         <f aca="false">H23*'Datasize-Parameters'!$C$33</f>
-        <v>0.411447510123253</v>
+        <v>44.4702797042728</v>
       </c>
       <c r="J27" s="182" t="s">
         <v>276</v>
@@ -18755,7 +18755,7 @@
       <c r="K27" s="185"/>
       <c r="L27" s="186" t="n">
         <f aca="false">L23*'Datasize-Parameters'!$C$33</f>
-        <v>0.438200432807207</v>
+        <v>48.9158785937369</v>
       </c>
       <c r="N27" s="182" t="s">
         <v>276</v>
@@ -18763,7 +18763,7 @@
       <c r="O27" s="185"/>
       <c r="P27" s="186" t="n">
         <f aca="false">P23*'Datasize-Parameters'!$C$33</f>
-        <v>0.467401707731187</v>
+        <v>53.8059660253877</v>
       </c>
       <c r="R27" s="182" t="s">
         <v>276</v>
@@ -18771,7 +18771,7 @@
       <c r="S27" s="185"/>
       <c r="T27" s="186" t="n">
         <f aca="false">T23*'Datasize-Parameters'!$C$33</f>
-        <v>0.499355593370274</v>
+        <v>59.1849658284336</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18782,7 +18782,7 @@
       <c r="C28" s="185"/>
       <c r="D28" s="186" t="n">
         <f aca="false">D22*'Datasize-Parameters'!$C$34</f>
-        <v>1.03163480758667</v>
+        <v>107.81003839016</v>
       </c>
       <c r="F28" s="182" t="s">
         <v>277</v>
@@ -18790,7 +18790,7 @@
       <c r="G28" s="185"/>
       <c r="H28" s="186" t="n">
         <f aca="false">H22*'Datasize-Parameters'!$C$34</f>
-        <v>1.09719336032867</v>
+        <v>118.587412544727</v>
       </c>
       <c r="J28" s="182" t="s">
         <v>277</v>
@@ -18798,7 +18798,7 @@
       <c r="K28" s="185"/>
       <c r="L28" s="186" t="n">
         <f aca="false">L22*'Datasize-Parameters'!$C$34</f>
-        <v>1.16853448748589</v>
+        <v>130.442342916632</v>
       </c>
       <c r="N28" s="182" t="s">
         <v>277</v>
@@ -18806,7 +18806,7 @@
       <c r="O28" s="185"/>
       <c r="P28" s="186" t="n">
         <f aca="false">P22*'Datasize-Parameters'!$C$34</f>
-        <v>1.24640455394983</v>
+        <v>143.4825760677</v>
       </c>
       <c r="R28" s="182" t="s">
         <v>277</v>
@@ -18814,7 +18814,7 @@
       <c r="S28" s="185"/>
       <c r="T28" s="186" t="n">
         <f aca="false">T22*'Datasize-Parameters'!$C$34</f>
-        <v>1.33161491565406</v>
+        <v>157.82657554249</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18843,7 +18843,7 @@
       <c r="C30" s="185"/>
       <c r="D30" s="188" t="n">
         <f aca="false">SUM(D22:D28)</f>
-        <v>19.4721069931984</v>
+        <v>2034.91447461426</v>
       </c>
       <c r="F30" s="187" t="s">
         <v>279</v>
@@ -18851,7 +18851,7 @@
       <c r="G30" s="185"/>
       <c r="H30" s="188" t="n">
         <f aca="false">SUM(H22:H28)</f>
-        <v>20.7095246762037</v>
+        <v>2238.33741178173</v>
       </c>
       <c r="J30" s="187" t="s">
         <v>280</v>
@@ -18859,7 +18859,7 @@
       <c r="K30" s="185"/>
       <c r="L30" s="188" t="n">
         <f aca="false">SUM(L22:L28)</f>
-        <v>22.0560884512961</v>
+        <v>2462.09922255142</v>
       </c>
       <c r="N30" s="187" t="s">
         <v>281</v>
@@ -18867,7 +18867,7 @@
       <c r="O30" s="185"/>
       <c r="P30" s="188" t="n">
         <f aca="false">SUM(P22:P28)</f>
-        <v>23.5258859558031</v>
+        <v>2708.23362327785</v>
       </c>
       <c r="R30" s="187" t="s">
         <v>282</v>
@@ -18875,7 +18875,7 @@
       <c r="S30" s="185"/>
       <c r="T30" s="188" t="n">
         <f aca="false">SUM(T22:T28)</f>
-        <v>25.1342315329704</v>
+        <v>2978.97661336449</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20384,11 +20384,11 @@
       </c>
       <c r="C5" s="173" t="n">
         <f aca="false">'Customer Volumes'!D5*'Customer Volumes'!D14*0.3</f>
-        <v>13500</v>
+        <v>15471924.6</v>
       </c>
       <c r="D5" s="174" t="n">
         <f aca="false">C5*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>3.2958984375</v>
+        <v>3777.32534179688</v>
       </c>
       <c r="F5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -20396,11 +20396,11 @@
       </c>
       <c r="G5" s="173" t="n">
         <f aca="false">'Customer Volumes'!E5*'Customer Volumes'!E14*0.3</f>
-        <v>15525</v>
+        <v>17019117.06</v>
       </c>
       <c r="H5" s="174" t="n">
         <f aca="false">G5*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>3.790283203125</v>
+        <v>4155.05787597656</v>
       </c>
       <c r="J5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -20408,11 +20408,11 @@
       </c>
       <c r="K5" s="173" t="n">
         <f aca="false">'Customer Volumes'!F5*'Customer Volumes'!F14*0.3</f>
-        <v>17853.75</v>
+        <v>18721028.766</v>
       </c>
       <c r="L5" s="174" t="n">
         <f aca="false">K5*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>4.35882568359375</v>
+        <v>4570.56366357422</v>
       </c>
       <c r="N5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -20420,11 +20420,11 @@
       </c>
       <c r="O5" s="173" t="n">
         <f aca="false">'Customer Volumes'!G5*'Customer Volumes'!G14*0.3</f>
-        <v>20531.8125</v>
+        <v>20593131.6426</v>
       </c>
       <c r="P5" s="174" t="n">
         <f aca="false">O5*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>5.01264953613281</v>
+        <v>5027.62002993164</v>
       </c>
       <c r="R5" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$4</f>
@@ -20432,11 +20432,11 @@
       </c>
       <c r="S5" s="173" t="n">
         <f aca="false">'Customer Volumes'!H5*'Customer Volumes'!H14*0.3</f>
-        <v>23611.584375</v>
+        <v>22652444.80686</v>
       </c>
       <c r="T5" s="174" t="n">
         <f aca="false">S5*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>5.76454696655273</v>
+        <v>5530.38203292481</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20447,11 +20447,11 @@
       </c>
       <c r="C6" s="173" t="n">
         <f aca="false">'Customer Volumes'!D7*'Customer Volumes'!D15*0.3</f>
-        <v>144000</v>
+        <v>6420000</v>
       </c>
       <c r="D6" s="174" t="n">
         <f aca="false">C6*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>35.15625</v>
+        <v>1567.3828125</v>
       </c>
       <c r="F6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -20459,11 +20459,11 @@
       </c>
       <c r="G6" s="173" t="n">
         <f aca="false">'Customer Volumes'!E7*'Customer Volumes'!E15*0.3</f>
-        <v>151200</v>
+        <v>7062000</v>
       </c>
       <c r="H6" s="174" t="n">
         <f aca="false">G6*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>36.9140625</v>
+        <v>1724.12109375</v>
       </c>
       <c r="J6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -20471,11 +20471,11 @@
       </c>
       <c r="K6" s="173" t="n">
         <f aca="false">'Customer Volumes'!F7*'Customer Volumes'!F15*0.3</f>
-        <v>158760</v>
+        <v>7768200</v>
       </c>
       <c r="L6" s="174" t="n">
         <f aca="false">K6*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>38.759765625</v>
+        <v>1896.533203125</v>
       </c>
       <c r="N6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -20483,11 +20483,11 @@
       </c>
       <c r="O6" s="173" t="n">
         <f aca="false">'Customer Volumes'!G7*'Customer Volumes'!G15*0.3</f>
-        <v>166698</v>
+        <v>8545020</v>
       </c>
       <c r="P6" s="174" t="n">
         <f aca="false">O6*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>40.69775390625</v>
+        <v>2086.1865234375</v>
       </c>
       <c r="R6" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$5</f>
@@ -20495,11 +20495,11 @@
       </c>
       <c r="S6" s="173" t="n">
         <f aca="false">'Customer Volumes'!H7*'Customer Volumes'!H15*0.3</f>
-        <v>175032.9</v>
+        <v>9399522</v>
       </c>
       <c r="T6" s="174" t="n">
         <f aca="false">S6*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>42.7326416015625</v>
+        <v>2294.80517578125</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20510,11 +20510,11 @@
       </c>
       <c r="C7" s="173" t="n">
         <f aca="false">'Customer Volumes'!D9*'Customer Volumes'!D16</f>
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="D7" s="174" t="n">
         <f aca="false">C7*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>3.662109375</v>
+        <v>4.8828125</v>
       </c>
       <c r="F7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -20522,11 +20522,11 @@
       </c>
       <c r="G7" s="173" t="n">
         <f aca="false">'Customer Volumes'!E9*'Customer Volumes'!E16</f>
-        <v>18000</v>
+        <v>21000</v>
       </c>
       <c r="H7" s="174" t="n">
         <f aca="false">G7*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>4.39453125</v>
+        <v>5.126953125</v>
       </c>
       <c r="J7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -20534,11 +20534,11 @@
       </c>
       <c r="K7" s="173" t="n">
         <f aca="false">'Customer Volumes'!F9*'Customer Volumes'!F16</f>
-        <v>21600</v>
+        <v>22050</v>
       </c>
       <c r="L7" s="174" t="n">
         <f aca="false">K7*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>5.2734375</v>
+        <v>5.38330078125</v>
       </c>
       <c r="N7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -20546,11 +20546,11 @@
       </c>
       <c r="O7" s="173" t="n">
         <f aca="false">'Customer Volumes'!G9*'Customer Volumes'!G16</f>
-        <v>25920</v>
+        <v>23152.5</v>
       </c>
       <c r="P7" s="174" t="n">
         <f aca="false">O7*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>6.328125</v>
+        <v>5.6524658203125</v>
       </c>
       <c r="R7" s="172" t="str">
         <f aca="false">'Datasize-Parameters'!$C$6</f>
@@ -20558,11 +20558,11 @@
       </c>
       <c r="S7" s="173" t="n">
         <f aca="false">'Customer Volumes'!H9*'Customer Volumes'!H16</f>
-        <v>31104</v>
+        <v>24310.125</v>
       </c>
       <c r="T7" s="174" t="n">
         <f aca="false">S7*'Datasize-Parameters'!$D$24/(1024*1024)</f>
-        <v>7.59375</v>
+        <v>5.93508911132813</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20822,7 +20822,7 @@
       <c r="C13" s="178"/>
       <c r="D13" s="177" t="n">
         <f aca="false">SUM(D5:D11)</f>
-        <v>42.1142578125</v>
+        <v>5349.59096679688</v>
       </c>
       <c r="F13" s="178" t="s">
         <v>289</v>
@@ -20830,7 +20830,7 @@
       <c r="G13" s="178"/>
       <c r="H13" s="177" t="n">
         <f aca="false">SUM(H5:H11)</f>
-        <v>45.098876953125</v>
+        <v>5884.30592285156</v>
       </c>
       <c r="J13" s="178" t="s">
         <v>289</v>
@@ -20838,7 +20838,7 @@
       <c r="K13" s="178"/>
       <c r="L13" s="177" t="n">
         <f aca="false">SUM(L5:L11)</f>
-        <v>48.3920288085938</v>
+        <v>6472.48016748047</v>
       </c>
       <c r="N13" s="178" t="s">
         <v>289</v>
@@ -20846,7 +20846,7 @@
       <c r="O13" s="178"/>
       <c r="P13" s="177" t="n">
         <f aca="false">SUM(P5:P11)</f>
-        <v>52.0385284423828</v>
+        <v>7119.45901918946</v>
       </c>
       <c r="R13" s="178" t="s">
         <v>289</v>
@@ -20854,7 +20854,7 @@
       <c r="S13" s="178"/>
       <c r="T13" s="177" t="n">
         <f aca="false">SUM(T5:T11)</f>
-        <v>56.0909385681152</v>
+        <v>7831.12229781739</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20957,7 +20957,7 @@
       <c r="C18" s="185"/>
       <c r="D18" s="186" t="n">
         <f aca="false">D13</f>
-        <v>42.1142578125</v>
+        <v>5349.59096679688</v>
       </c>
       <c r="F18" s="182" t="s">
         <v>272</v>
@@ -20965,7 +20965,7 @@
       <c r="G18" s="185"/>
       <c r="H18" s="186" t="n">
         <f aca="false">H13</f>
-        <v>45.098876953125</v>
+        <v>5884.30592285156</v>
       </c>
       <c r="J18" s="182" t="s">
         <v>272</v>
@@ -20973,7 +20973,7 @@
       <c r="K18" s="185"/>
       <c r="L18" s="186" t="n">
         <f aca="false">L13</f>
-        <v>48.3920288085938</v>
+        <v>6472.48016748047</v>
       </c>
       <c r="N18" s="182" t="s">
         <v>272</v>
@@ -20981,7 +20981,7 @@
       <c r="O18" s="185"/>
       <c r="P18" s="186" t="n">
         <f aca="false">P13</f>
-        <v>52.0385284423828</v>
+        <v>7119.45901918946</v>
       </c>
       <c r="R18" s="182" t="s">
         <v>272</v>
@@ -20989,7 +20989,7 @@
       <c r="S18" s="185"/>
       <c r="T18" s="186" t="n">
         <f aca="false">T13</f>
-        <v>56.0909385681152</v>
+        <v>7831.12229781739</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21000,7 +21000,7 @@
       <c r="C19" s="185"/>
       <c r="D19" s="186" t="n">
         <f aca="false">D18*10%</f>
-        <v>4.21142578125</v>
+        <v>534.959096679688</v>
       </c>
       <c r="E19" s="179"/>
       <c r="F19" s="182" t="s">
@@ -21009,7 +21009,7 @@
       <c r="G19" s="185"/>
       <c r="H19" s="186" t="n">
         <f aca="false">H18*10%</f>
-        <v>4.5098876953125</v>
+        <v>588.430592285156</v>
       </c>
       <c r="I19" s="179"/>
       <c r="J19" s="182" t="s">
@@ -21018,7 +21018,7 @@
       <c r="K19" s="185"/>
       <c r="L19" s="186" t="n">
         <f aca="false">L18*10%</f>
-        <v>4.83920288085938</v>
+        <v>647.248016748047</v>
       </c>
       <c r="M19" s="179"/>
       <c r="N19" s="182" t="s">
@@ -21027,7 +21027,7 @@
       <c r="O19" s="185"/>
       <c r="P19" s="186" t="n">
         <f aca="false">P18*10%</f>
-        <v>5.20385284423828</v>
+        <v>711.945901918946</v>
       </c>
       <c r="R19" s="182" t="s">
         <v>291</v>
@@ -21035,7 +21035,7 @@
       <c r="S19" s="185"/>
       <c r="T19" s="186" t="n">
         <f aca="false">T18*10%</f>
-        <v>5.60909385681152</v>
+        <v>783.112229781739</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21064,7 +21064,7 @@
       <c r="C21" s="185"/>
       <c r="D21" s="197" t="n">
         <f aca="false">SUM(D18:D19)</f>
-        <v>46.32568359375</v>
+        <v>5884.55006347656</v>
       </c>
       <c r="F21" s="187" t="s">
         <v>292</v>
@@ -21072,7 +21072,7 @@
       <c r="G21" s="185"/>
       <c r="H21" s="197" t="n">
         <f aca="false">SUM(H18:H19)</f>
-        <v>49.6087646484375</v>
+        <v>6472.73651513672</v>
       </c>
       <c r="J21" s="187" t="s">
         <v>280</v>
@@ -21080,7 +21080,7 @@
       <c r="K21" s="185"/>
       <c r="L21" s="197" t="n">
         <f aca="false">SUM(L18:L19)</f>
-        <v>53.2312316894531</v>
+        <v>7119.72818422852</v>
       </c>
       <c r="N21" s="187" t="s">
         <v>281</v>
@@ -21088,7 +21088,7 @@
       <c r="O21" s="185"/>
       <c r="P21" s="197" t="n">
         <f aca="false">SUM(P18:P19)</f>
-        <v>57.2423812866211</v>
+        <v>7831.4049211084</v>
       </c>
       <c r="R21" s="187" t="s">
         <v>282</v>
@@ -21096,7 +21096,7 @@
       <c r="S21" s="185"/>
       <c r="T21" s="197" t="n">
         <f aca="false">SUM(T18:T19)</f>
-        <v>61.7000324249267</v>
+        <v>8614.23452759913</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
